--- a/30_table/01_테스트버전/Table_Data_Map.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Map.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="336">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1114,6 +1114,107 @@
   </si>
   <si>
     <t>bgm_34</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개발자의 방으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map_s1_005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pf_Map_50045</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개발자와 대화 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개발자와 대화 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시험 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시험 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개발자와 대화 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map_s1_006</t>
+  </si>
+  <si>
+    <t>map_s1_007</t>
+  </si>
+  <si>
+    <t>map_s1_008</t>
+  </si>
+  <si>
+    <t>map_s1_009</t>
+  </si>
+  <si>
+    <t>map_s1_010</t>
+  </si>
+  <si>
+    <t>map_s1_011</t>
+  </si>
+  <si>
+    <t>pf_Map_50046</t>
+  </si>
+  <si>
+    <t>pf_Map_50047</t>
+  </si>
+  <si>
+    <t>pf_Map_50048</t>
+  </si>
+  <si>
+    <t>pf_Map_50049</t>
+  </si>
+  <si>
+    <t>pf_Map_50050</t>
+  </si>
+  <si>
+    <t>pf_Map_50051</t>
+  </si>
+  <si>
+    <t>img_map_0021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0028</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개발자와 대화 4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map_s1_012</t>
+  </si>
+  <si>
+    <t>pf_Map_50052</t>
+  </si>
+  <si>
+    <t>bgm_12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm_13</t>
+  </si>
+  <si>
+    <t>bgm_14</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5096,7 +5197,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:V47"/>
+  <dimension ref="A1:V54"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" style="36" bestFit="1" customWidth="1"/>
@@ -8034,11 +8135,11 @@
         <v>294</v>
       </c>
       <c r="D44" s="34" t="str">
-        <f t="shared" ref="D44:D46" si="22">"STR_"&amp;UPPER(C44)</f>
+        <f t="shared" ref="D44:D47" si="22">"STR_"&amp;UPPER(C44)</f>
         <v>STR_MAP_S3_013</v>
       </c>
       <c r="E44" s="34" t="str">
-        <f t="shared" ref="E44:E46" si="23">D44&amp;"_DESC"</f>
+        <f t="shared" ref="E44:E47" si="23">D44&amp;"_DESC"</f>
         <v>STR_MAP_S3_013_DESC</v>
       </c>
       <c r="F44" s="34">
@@ -8222,7 +8323,516 @@
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="C47" s="34"/>
+      <c r="A47" s="34">
+        <v>50045</v>
+      </c>
+      <c r="B47" s="35" t="s">
+        <v>307</v>
+      </c>
+      <c r="C47" s="34" t="s">
+        <v>308</v>
+      </c>
+      <c r="D47" s="34" t="str">
+        <f t="shared" si="22"/>
+        <v>STR_MAP_S1_005</v>
+      </c>
+      <c r="E47" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>STR_MAP_S1_005_DESC</v>
+      </c>
+      <c r="F47" s="34">
+        <v>1</v>
+      </c>
+      <c r="G47" s="34">
+        <v>99</v>
+      </c>
+      <c r="H47" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="I47" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J47" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K47" s="34">
+        <v>0</v>
+      </c>
+      <c r="L47" s="34" t="s">
+        <v>309</v>
+      </c>
+      <c r="M47" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="N47" s="34" t="s">
+        <v>333</v>
+      </c>
+      <c r="O47" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="P47" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q47" s="34">
+        <v>0</v>
+      </c>
+      <c r="R47" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="S47" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T47" s="36" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A48" s="34">
+        <v>50046</v>
+      </c>
+      <c r="B48" s="36" t="s">
+        <v>310</v>
+      </c>
+      <c r="C48" s="34" t="s">
+        <v>315</v>
+      </c>
+      <c r="D48" s="34" t="str">
+        <f t="shared" ref="D48:D52" si="24">"STR_"&amp;UPPER(C48)</f>
+        <v>STR_MAP_S1_006</v>
+      </c>
+      <c r="E48" s="34" t="str">
+        <f t="shared" ref="E48:E52" si="25">D48&amp;"_DESC"</f>
+        <v>STR_MAP_S1_006_DESC</v>
+      </c>
+      <c r="F48" s="34">
+        <v>1</v>
+      </c>
+      <c r="G48" s="34">
+        <v>99</v>
+      </c>
+      <c r="H48" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="I48" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J48" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K48" s="34">
+        <v>0</v>
+      </c>
+      <c r="L48" s="34" t="s">
+        <v>321</v>
+      </c>
+      <c r="M48" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="N48" s="34" t="s">
+        <v>333</v>
+      </c>
+      <c r="O48" s="36" t="s">
+        <v>328</v>
+      </c>
+      <c r="P48" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q48" s="34">
+        <v>0</v>
+      </c>
+      <c r="R48" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S48" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T48" s="36" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A49" s="34">
+        <v>50047</v>
+      </c>
+      <c r="B49" s="36" t="s">
+        <v>311</v>
+      </c>
+      <c r="C49" s="34" t="s">
+        <v>316</v>
+      </c>
+      <c r="D49" s="34" t="str">
+        <f t="shared" si="24"/>
+        <v>STR_MAP_S1_007</v>
+      </c>
+      <c r="E49" s="34" t="str">
+        <f t="shared" si="25"/>
+        <v>STR_MAP_S1_007_DESC</v>
+      </c>
+      <c r="F49" s="34">
+        <v>1</v>
+      </c>
+      <c r="G49" s="34">
+        <v>99</v>
+      </c>
+      <c r="H49" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="I49" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J49" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K49" s="34">
+        <v>0</v>
+      </c>
+      <c r="L49" s="34" t="s">
+        <v>322</v>
+      </c>
+      <c r="M49" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="N49" s="34" t="s">
+        <v>333</v>
+      </c>
+      <c r="O49" s="36" t="s">
+        <v>328</v>
+      </c>
+      <c r="P49" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q49" s="34">
+        <v>0</v>
+      </c>
+      <c r="R49" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S49" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T49" s="36" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A50" s="34">
+        <v>50048</v>
+      </c>
+      <c r="B50" s="36" t="s">
+        <v>314</v>
+      </c>
+      <c r="C50" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="D50" s="34" t="str">
+        <f t="shared" ref="D50" si="26">"STR_"&amp;UPPER(C50)</f>
+        <v>STR_MAP_S1_008</v>
+      </c>
+      <c r="E50" s="34" t="str">
+        <f t="shared" ref="E50" si="27">D50&amp;"_DESC"</f>
+        <v>STR_MAP_S1_008_DESC</v>
+      </c>
+      <c r="F50" s="34">
+        <v>1</v>
+      </c>
+      <c r="G50" s="34">
+        <v>99</v>
+      </c>
+      <c r="H50" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="I50" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J50" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K50" s="34">
+        <v>0</v>
+      </c>
+      <c r="L50" s="34" t="s">
+        <v>323</v>
+      </c>
+      <c r="M50" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="N50" s="34" t="s">
+        <v>333</v>
+      </c>
+      <c r="O50" s="36" t="s">
+        <v>328</v>
+      </c>
+      <c r="P50" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="34">
+        <v>0</v>
+      </c>
+      <c r="R50" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S50" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T50" s="36" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A51" s="34">
+        <v>50049</v>
+      </c>
+      <c r="B51" s="36" t="s">
+        <v>312</v>
+      </c>
+      <c r="C51" s="34" t="s">
+        <v>318</v>
+      </c>
+      <c r="D51" s="34" t="str">
+        <f t="shared" si="24"/>
+        <v>STR_MAP_S1_009</v>
+      </c>
+      <c r="E51" s="34" t="str">
+        <f t="shared" si="25"/>
+        <v>STR_MAP_S1_009_DESC</v>
+      </c>
+      <c r="F51" s="34">
+        <v>1</v>
+      </c>
+      <c r="G51" s="34">
+        <v>99</v>
+      </c>
+      <c r="H51" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="I51" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J51" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K51" s="34">
+        <v>0</v>
+      </c>
+      <c r="L51" s="34" t="s">
+        <v>324</v>
+      </c>
+      <c r="M51" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="N51" s="34" t="s">
+        <v>334</v>
+      </c>
+      <c r="O51" s="36" t="s">
+        <v>328</v>
+      </c>
+      <c r="P51" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q51" s="34">
+        <v>0</v>
+      </c>
+      <c r="R51" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S51" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T51" s="36" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A52" s="34">
+        <v>50050</v>
+      </c>
+      <c r="B52" s="36" t="s">
+        <v>313</v>
+      </c>
+      <c r="C52" s="34" t="s">
+        <v>319</v>
+      </c>
+      <c r="D52" s="34" t="str">
+        <f t="shared" si="24"/>
+        <v>STR_MAP_S1_010</v>
+      </c>
+      <c r="E52" s="34" t="str">
+        <f t="shared" si="25"/>
+        <v>STR_MAP_S1_010_DESC</v>
+      </c>
+      <c r="F52" s="34">
+        <v>1</v>
+      </c>
+      <c r="G52" s="34">
+        <v>99</v>
+      </c>
+      <c r="H52" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="I52" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J52" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K52" s="34">
+        <v>0</v>
+      </c>
+      <c r="L52" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="M52" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="N52" s="34" t="s">
+        <v>334</v>
+      </c>
+      <c r="O52" s="36" t="s">
+        <v>328</v>
+      </c>
+      <c r="P52" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q52" s="34">
+        <v>0</v>
+      </c>
+      <c r="R52" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S52" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T52" s="36" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A53" s="34">
+        <v>50051</v>
+      </c>
+      <c r="B53" s="36" t="s">
+        <v>313</v>
+      </c>
+      <c r="C53" s="34" t="s">
+        <v>320</v>
+      </c>
+      <c r="D53" s="34" t="str">
+        <f t="shared" ref="D53:D54" si="28">"STR_"&amp;UPPER(C53)</f>
+        <v>STR_MAP_S1_011</v>
+      </c>
+      <c r="E53" s="34" t="str">
+        <f t="shared" ref="E53:E54" si="29">D53&amp;"_DESC"</f>
+        <v>STR_MAP_S1_011_DESC</v>
+      </c>
+      <c r="F53" s="34">
+        <v>1</v>
+      </c>
+      <c r="G53" s="34">
+        <v>99</v>
+      </c>
+      <c r="H53" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="I53" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J53" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K53" s="34">
+        <v>0</v>
+      </c>
+      <c r="L53" s="34" t="s">
+        <v>326</v>
+      </c>
+      <c r="M53" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="N53" s="34" t="s">
+        <v>334</v>
+      </c>
+      <c r="O53" s="36" t="s">
+        <v>328</v>
+      </c>
+      <c r="P53" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q53" s="34">
+        <v>0</v>
+      </c>
+      <c r="R53" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S53" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T53" s="36" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A54" s="34">
+        <v>50052</v>
+      </c>
+      <c r="B54" s="36" t="s">
+        <v>330</v>
+      </c>
+      <c r="C54" s="34" t="s">
+        <v>331</v>
+      </c>
+      <c r="D54" s="34" t="str">
+        <f t="shared" si="28"/>
+        <v>STR_MAP_S1_012</v>
+      </c>
+      <c r="E54" s="34" t="str">
+        <f t="shared" si="29"/>
+        <v>STR_MAP_S1_012_DESC</v>
+      </c>
+      <c r="F54" s="34">
+        <v>1</v>
+      </c>
+      <c r="G54" s="34">
+        <v>99</v>
+      </c>
+      <c r="H54" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="I54" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J54" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K54" s="34">
+        <v>0</v>
+      </c>
+      <c r="L54" s="34" t="s">
+        <v>332</v>
+      </c>
+      <c r="M54" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="N54" s="34" t="s">
+        <v>335</v>
+      </c>
+      <c r="O54" s="36" t="s">
+        <v>328</v>
+      </c>
+      <c r="P54" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q54" s="34">
+        <v>0</v>
+      </c>
+      <c r="R54" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S54" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T54" s="36" t="s">
+        <v>41</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:T2"/>
@@ -8263,7 +8873,7 @@
           <x14:formula2>
             <xm:f>Definition!G12</xm:f>
           </x14:formula2>
-          <xm:sqref>G11 G27 G29:G41</xm:sqref>
+          <xm:sqref>G11 G29:G41 G27</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -8272,7 +8882,7 @@
           <x14:formula2>
             <xm:f>Definition!G10</xm:f>
           </x14:formula2>
-          <xm:sqref>I2:I46</xm:sqref>
+          <xm:sqref>I2:I54</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -8281,7 +8891,7 @@
           <x14:formula2>
             <xm:f>Definition!G8</xm:f>
           </x14:formula2>
-          <xm:sqref>G2:G5</xm:sqref>
+          <xm:sqref>G2:G5 G47:G54</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/30_table/01_테스트버전/Table_Data_Map.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Map.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="469">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1216,6 +1216,412 @@
   <si>
     <t>bgm_14</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pf_Map_50053</t>
+  </si>
+  <si>
+    <t>img_map_0022</t>
+  </si>
+  <si>
+    <t>icon_map_0022</t>
+  </si>
+  <si>
+    <t>pf_Map_50054</t>
+  </si>
+  <si>
+    <t>img_map_0023</t>
+  </si>
+  <si>
+    <t>icon_map_0023</t>
+  </si>
+  <si>
+    <t>pf_Map_50055</t>
+  </si>
+  <si>
+    <t>img_map_0024</t>
+  </si>
+  <si>
+    <t>icon_map_0024</t>
+  </si>
+  <si>
+    <t>pf_Map_50056</t>
+  </si>
+  <si>
+    <t>img_map_0025</t>
+  </si>
+  <si>
+    <t>icon_map_0025</t>
+  </si>
+  <si>
+    <t>pf_Map_50057</t>
+  </si>
+  <si>
+    <t>img_map_0026</t>
+  </si>
+  <si>
+    <t>icon_map_0026</t>
+  </si>
+  <si>
+    <t>pf_Map_50058</t>
+  </si>
+  <si>
+    <t>img_map_0027</t>
+  </si>
+  <si>
+    <t>icon_map_0027</t>
+  </si>
+  <si>
+    <t>pf_Map_50059</t>
+  </si>
+  <si>
+    <t>img_map_0028</t>
+  </si>
+  <si>
+    <t>icon_map_0028</t>
+  </si>
+  <si>
+    <t>pf_Map_50060</t>
+  </si>
+  <si>
+    <t>img_map_0029</t>
+  </si>
+  <si>
+    <t>icon_map_0029</t>
+  </si>
+  <si>
+    <t>pf_Map_50061</t>
+  </si>
+  <si>
+    <t>img_map_0030</t>
+  </si>
+  <si>
+    <t>icon_map_0030</t>
+  </si>
+  <si>
+    <t>pf_Map_50062</t>
+  </si>
+  <si>
+    <t>img_map_0031</t>
+  </si>
+  <si>
+    <t>icon_map_0031</t>
+  </si>
+  <si>
+    <t>pf_Map_50063</t>
+  </si>
+  <si>
+    <t>img_map_0032</t>
+  </si>
+  <si>
+    <t>icon_map_0032</t>
+  </si>
+  <si>
+    <t>pf_Map_50064</t>
+  </si>
+  <si>
+    <t>img_map_0033</t>
+  </si>
+  <si>
+    <t>icon_map_0033</t>
+  </si>
+  <si>
+    <t>pf_Map_50065</t>
+  </si>
+  <si>
+    <t>img_map_0034</t>
+  </si>
+  <si>
+    <t>icon_map_0034</t>
+  </si>
+  <si>
+    <t>pf_Map_50066</t>
+  </si>
+  <si>
+    <t>img_map_0035</t>
+  </si>
+  <si>
+    <t>icon_map_0035</t>
+  </si>
+  <si>
+    <t>pf_Map_50067</t>
+  </si>
+  <si>
+    <t>img_map_0036</t>
+  </si>
+  <si>
+    <t>icon_map_0036</t>
+  </si>
+  <si>
+    <t>pf_Map_50068</t>
+  </si>
+  <si>
+    <t>img_map_0037</t>
+  </si>
+  <si>
+    <t>icon_map_0037</t>
+  </si>
+  <si>
+    <t>pf_Map_50069</t>
+  </si>
+  <si>
+    <t>img_map_0038</t>
+  </si>
+  <si>
+    <t>icon_map_0038</t>
+  </si>
+  <si>
+    <t>pf_Map_50070</t>
+  </si>
+  <si>
+    <t>img_map_0039</t>
+  </si>
+  <si>
+    <t>icon_map_0039</t>
+  </si>
+  <si>
+    <t>pf_Map_50071</t>
+  </si>
+  <si>
+    <t>img_map_0040</t>
+  </si>
+  <si>
+    <t>icon_map_0040</t>
+  </si>
+  <si>
+    <t>pf_Map_50072</t>
+  </si>
+  <si>
+    <t>img_map_0041</t>
+  </si>
+  <si>
+    <t>icon_map_0041</t>
+  </si>
+  <si>
+    <t>pf_Map_50073</t>
+  </si>
+  <si>
+    <t>img_map_0042</t>
+  </si>
+  <si>
+    <t>icon_map_0042</t>
+  </si>
+  <si>
+    <t>pf_Map_50074</t>
+  </si>
+  <si>
+    <t>img_map_0043</t>
+  </si>
+  <si>
+    <t>icon_map_0043</t>
+  </si>
+  <si>
+    <t>pf_Map_50075</t>
+  </si>
+  <si>
+    <t>img_map_0044</t>
+  </si>
+  <si>
+    <t>icon_map_0044</t>
+  </si>
+  <si>
+    <t>pf_Map_50076</t>
+  </si>
+  <si>
+    <t>img_map_0045</t>
+  </si>
+  <si>
+    <t>icon_map_0045</t>
+  </si>
+  <si>
+    <t>욕심</t>
+  </si>
+  <si>
+    <t>죽은 자의 동굴  1층</t>
+  </si>
+  <si>
+    <t>좀비 조심</t>
+  </si>
+  <si>
+    <t>박쥐 사냥</t>
+  </si>
+  <si>
+    <t>좀비방</t>
+  </si>
+  <si>
+    <t>숨겨진 방으로</t>
+  </si>
+  <si>
+    <t>보물방</t>
+  </si>
+  <si>
+    <t>믿음</t>
+  </si>
+  <si>
+    <t>만족</t>
+  </si>
+  <si>
+    <t>지하 2층으로</t>
+  </si>
+  <si>
+    <t>죽은 자의 동굴 2층</t>
+  </si>
+  <si>
+    <t>구울 조심</t>
+  </si>
+  <si>
+    <t>함정 1</t>
+  </si>
+  <si>
+    <t>구울방</t>
+  </si>
+  <si>
+    <t>함정 2</t>
+  </si>
+  <si>
+    <t>라미를 찾아서</t>
+  </si>
+  <si>
+    <t>라미의 부탁</t>
+  </si>
+  <si>
+    <t>좀비의 영혼</t>
+  </si>
+  <si>
+    <t>라미에게 줄 선물</t>
+  </si>
+  <si>
+    <t>라미의 조언</t>
+  </si>
+  <si>
+    <t>서큐버스를 찾아서 1</t>
+  </si>
+  <si>
+    <t>서큐버스를 찾아서 2</t>
+  </si>
+  <si>
+    <t>서큐버스 처치</t>
+  </si>
+  <si>
+    <t>서고로 이동</t>
+  </si>
+  <si>
+    <t>pf_Map_50077</t>
+  </si>
+  <si>
+    <t>img_map_0046</t>
+  </si>
+  <si>
+    <t>icon_map_0046</t>
+  </si>
+  <si>
+    <t>단서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map_s4_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map_s4_002</t>
+  </si>
+  <si>
+    <t>map_s4_003</t>
+  </si>
+  <si>
+    <t>map_s4_004</t>
+  </si>
+  <si>
+    <t>map_s4_005</t>
+  </si>
+  <si>
+    <t>map_s4_006</t>
+  </si>
+  <si>
+    <t>map_s4_007</t>
+  </si>
+  <si>
+    <t>map_s4_008</t>
+  </si>
+  <si>
+    <t>map_s4_009</t>
+  </si>
+  <si>
+    <t>map_s4_010</t>
+  </si>
+  <si>
+    <t>map_s4_011</t>
+  </si>
+  <si>
+    <t>map_s4_012</t>
+  </si>
+  <si>
+    <t>map_s4_013</t>
+  </si>
+  <si>
+    <t>map_s4_014</t>
+  </si>
+  <si>
+    <t>map_s4_015</t>
+  </si>
+  <si>
+    <t>map_s4_016</t>
+  </si>
+  <si>
+    <t>map_s4_017</t>
+  </si>
+  <si>
+    <t>map_s4_018</t>
+  </si>
+  <si>
+    <t>map_s4_019</t>
+  </si>
+  <si>
+    <t>map_s4_020</t>
+  </si>
+  <si>
+    <t>map_s4_021</t>
+  </si>
+  <si>
+    <t>map_s4_022</t>
+  </si>
+  <si>
+    <t>map_s4_023</t>
+  </si>
+  <si>
+    <t>map_s4_024</t>
+  </si>
+  <si>
+    <t>map_s4_025</t>
+  </si>
+  <si>
+    <t>Move</t>
+  </si>
+  <si>
+    <t>bgm_41</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm_42</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm_43</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동굴 1층</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map_s4_026</t>
+  </si>
+  <si>
+    <t>pf_Map_50078</t>
   </si>
 </sst>
 </file>
@@ -5197,7 +5603,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:V54"/>
+  <dimension ref="A1:V80"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" style="36" bestFit="1" customWidth="1"/>
@@ -8450,7 +8856,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49" s="34">
         <v>50047</v>
       </c>
@@ -8514,7 +8920,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A50" s="34">
         <v>50048</v>
       </c>
@@ -8578,7 +8984,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A51" s="34">
         <v>50049</v>
       </c>
@@ -8642,7 +9048,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A52" s="34">
         <v>50050</v>
       </c>
@@ -8706,7 +9112,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A53" s="34">
         <v>50051</v>
       </c>
@@ -8770,7 +9176,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A54" s="34">
         <v>50052</v>
       </c>
@@ -8832,6 +9238,1820 @@
       </c>
       <c r="T54" s="36" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A55" s="34">
+        <v>50053</v>
+      </c>
+      <c r="B55" s="36" t="s">
+        <v>408</v>
+      </c>
+      <c r="C55" s="34" t="s">
+        <v>436</v>
+      </c>
+      <c r="D55" s="34" t="str">
+        <f t="shared" ref="D55:D79" si="30">"STR_"&amp;UPPER(C55)</f>
+        <v>STR_MAP_S4_001</v>
+      </c>
+      <c r="E55" s="34" t="str">
+        <f t="shared" ref="E55:E79" si="31">D55&amp;"_DESC"</f>
+        <v>STR_MAP_S4_001_DESC</v>
+      </c>
+      <c r="F55" s="34">
+        <v>4</v>
+      </c>
+      <c r="G55" s="34">
+        <v>3</v>
+      </c>
+      <c r="H55" s="34" t="s">
+        <v>461</v>
+      </c>
+      <c r="I55" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J55" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K55" s="34">
+        <v>0</v>
+      </c>
+      <c r="L55" s="34" t="s">
+        <v>336</v>
+      </c>
+      <c r="M55" s="34" t="s">
+        <v>337</v>
+      </c>
+      <c r="N55" s="34" t="s">
+        <v>462</v>
+      </c>
+      <c r="O55" s="36" t="s">
+        <v>338</v>
+      </c>
+      <c r="P55" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q55" s="34">
+        <v>0</v>
+      </c>
+      <c r="R55" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S55" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T55" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U55" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V55" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A56" s="34">
+        <v>50054</v>
+      </c>
+      <c r="B56" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="C56" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="D56" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v>STR_MAP_S4_002</v>
+      </c>
+      <c r="E56" s="34" t="str">
+        <f t="shared" si="31"/>
+        <v>STR_MAP_S4_002_DESC</v>
+      </c>
+      <c r="F56" s="34">
+        <v>4</v>
+      </c>
+      <c r="G56" s="34">
+        <v>3</v>
+      </c>
+      <c r="H56" s="34" t="s">
+        <v>461</v>
+      </c>
+      <c r="I56" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J56" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K56" s="34">
+        <v>0</v>
+      </c>
+      <c r="L56" s="34" t="s">
+        <v>339</v>
+      </c>
+      <c r="M56" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="N56" s="34" t="s">
+        <v>462</v>
+      </c>
+      <c r="O56" s="36" t="s">
+        <v>341</v>
+      </c>
+      <c r="P56" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q56" s="34">
+        <v>0</v>
+      </c>
+      <c r="R56" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S56" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T56" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U56" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V56" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A57" s="34">
+        <v>50055</v>
+      </c>
+      <c r="B57" s="36" t="s">
+        <v>410</v>
+      </c>
+      <c r="C57" s="34" t="s">
+        <v>438</v>
+      </c>
+      <c r="D57" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v>STR_MAP_S4_003</v>
+      </c>
+      <c r="E57" s="34" t="str">
+        <f t="shared" si="31"/>
+        <v>STR_MAP_S4_003_DESC</v>
+      </c>
+      <c r="F57" s="34">
+        <v>4</v>
+      </c>
+      <c r="G57" s="34">
+        <v>3</v>
+      </c>
+      <c r="H57" s="34" t="s">
+        <v>461</v>
+      </c>
+      <c r="I57" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J57" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K57" s="34">
+        <v>0</v>
+      </c>
+      <c r="L57" s="34" t="s">
+        <v>342</v>
+      </c>
+      <c r="M57" s="34" t="s">
+        <v>343</v>
+      </c>
+      <c r="N57" s="34" t="s">
+        <v>462</v>
+      </c>
+      <c r="O57" s="36" t="s">
+        <v>344</v>
+      </c>
+      <c r="P57" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q57" s="34">
+        <v>0</v>
+      </c>
+      <c r="R57" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S57" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T57" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U57" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V57" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A58" s="34">
+        <v>50056</v>
+      </c>
+      <c r="B58" s="36" t="s">
+        <v>411</v>
+      </c>
+      <c r="C58" s="34" t="s">
+        <v>439</v>
+      </c>
+      <c r="D58" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v>STR_MAP_S4_004</v>
+      </c>
+      <c r="E58" s="34" t="str">
+        <f t="shared" si="31"/>
+        <v>STR_MAP_S4_004_DESC</v>
+      </c>
+      <c r="F58" s="34">
+        <v>4</v>
+      </c>
+      <c r="G58" s="34">
+        <v>3</v>
+      </c>
+      <c r="H58" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="I58" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J58" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K58" s="34">
+        <v>0</v>
+      </c>
+      <c r="L58" s="34" t="s">
+        <v>345</v>
+      </c>
+      <c r="M58" s="34" t="s">
+        <v>346</v>
+      </c>
+      <c r="N58" s="34" t="s">
+        <v>463</v>
+      </c>
+      <c r="O58" s="36" t="s">
+        <v>347</v>
+      </c>
+      <c r="P58" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q58" s="34">
+        <v>0</v>
+      </c>
+      <c r="R58" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S58" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T58" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U58" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V58" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A59" s="34">
+        <v>50057</v>
+      </c>
+      <c r="B59" s="36" t="s">
+        <v>412</v>
+      </c>
+      <c r="C59" s="34" t="s">
+        <v>440</v>
+      </c>
+      <c r="D59" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v>STR_MAP_S4_005</v>
+      </c>
+      <c r="E59" s="34" t="str">
+        <f t="shared" si="31"/>
+        <v>STR_MAP_S4_005_DESC</v>
+      </c>
+      <c r="F59" s="34">
+        <v>4</v>
+      </c>
+      <c r="G59" s="34">
+        <v>3</v>
+      </c>
+      <c r="H59" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="I59" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J59" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K59" s="34">
+        <v>0</v>
+      </c>
+      <c r="L59" s="34" t="s">
+        <v>348</v>
+      </c>
+      <c r="M59" s="34" t="s">
+        <v>349</v>
+      </c>
+      <c r="N59" s="34" t="s">
+        <v>463</v>
+      </c>
+      <c r="O59" s="36" t="s">
+        <v>350</v>
+      </c>
+      <c r="P59" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q59" s="34">
+        <v>0</v>
+      </c>
+      <c r="R59" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S59" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T59" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U59" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V59" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A60" s="34">
+        <v>50058</v>
+      </c>
+      <c r="B60" s="36" t="s">
+        <v>413</v>
+      </c>
+      <c r="C60" s="34" t="s">
+        <v>441</v>
+      </c>
+      <c r="D60" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v>STR_MAP_S4_006</v>
+      </c>
+      <c r="E60" s="34" t="str">
+        <f t="shared" si="31"/>
+        <v>STR_MAP_S4_006_DESC</v>
+      </c>
+      <c r="F60" s="34">
+        <v>4</v>
+      </c>
+      <c r="G60" s="34">
+        <v>3</v>
+      </c>
+      <c r="H60" s="34" t="s">
+        <v>461</v>
+      </c>
+      <c r="I60" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J60" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K60" s="34">
+        <v>0</v>
+      </c>
+      <c r="L60" s="34" t="s">
+        <v>351</v>
+      </c>
+      <c r="M60" s="34" t="s">
+        <v>352</v>
+      </c>
+      <c r="N60" s="34" t="s">
+        <v>462</v>
+      </c>
+      <c r="O60" s="36" t="s">
+        <v>353</v>
+      </c>
+      <c r="P60" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q60" s="34">
+        <v>0</v>
+      </c>
+      <c r="R60" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S60" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T60" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U60" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V60" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A61" s="34">
+        <v>50059</v>
+      </c>
+      <c r="B61" s="36" t="s">
+        <v>414</v>
+      </c>
+      <c r="C61" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="D61" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v>STR_MAP_S4_007</v>
+      </c>
+      <c r="E61" s="34" t="str">
+        <f t="shared" si="31"/>
+        <v>STR_MAP_S4_007_DESC</v>
+      </c>
+      <c r="F61" s="34">
+        <v>4</v>
+      </c>
+      <c r="G61" s="34">
+        <v>3</v>
+      </c>
+      <c r="H61" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="I61" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J61" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K61" s="34">
+        <v>0</v>
+      </c>
+      <c r="L61" s="34" t="s">
+        <v>354</v>
+      </c>
+      <c r="M61" s="34" t="s">
+        <v>355</v>
+      </c>
+      <c r="N61" s="34" t="s">
+        <v>464</v>
+      </c>
+      <c r="O61" s="36" t="s">
+        <v>356</v>
+      </c>
+      <c r="P61" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q61" s="34">
+        <v>0</v>
+      </c>
+      <c r="R61" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S61" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T61" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U61" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V61" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A62" s="34">
+        <v>50060</v>
+      </c>
+      <c r="B62" s="36" t="s">
+        <v>466</v>
+      </c>
+      <c r="C62" s="34" t="s">
+        <v>443</v>
+      </c>
+      <c r="D62" s="34" t="str">
+        <f t="shared" ref="D62" si="32">"STR_"&amp;UPPER(C62)</f>
+        <v>STR_MAP_S4_008</v>
+      </c>
+      <c r="E62" s="34" t="str">
+        <f t="shared" ref="E62" si="33">D62&amp;"_DESC"</f>
+        <v>STR_MAP_S4_008_DESC</v>
+      </c>
+      <c r="F62" s="34">
+        <v>4</v>
+      </c>
+      <c r="G62" s="34">
+        <v>3</v>
+      </c>
+      <c r="H62" s="34" t="s">
+        <v>461</v>
+      </c>
+      <c r="I62" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J62" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K62" s="34">
+        <v>0</v>
+      </c>
+      <c r="L62" s="34" t="s">
+        <v>357</v>
+      </c>
+      <c r="M62" s="34" t="s">
+        <v>352</v>
+      </c>
+      <c r="N62" s="34" t="s">
+        <v>462</v>
+      </c>
+      <c r="O62" s="36" t="s">
+        <v>353</v>
+      </c>
+      <c r="P62" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q62" s="34">
+        <v>0</v>
+      </c>
+      <c r="R62" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S62" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T62" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U62" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V62" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A63" s="34">
+        <v>50061</v>
+      </c>
+      <c r="B63" s="36" t="s">
+        <v>415</v>
+      </c>
+      <c r="C63" s="34" t="s">
+        <v>444</v>
+      </c>
+      <c r="D63" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v>STR_MAP_S4_009</v>
+      </c>
+      <c r="E63" s="34" t="str">
+        <f t="shared" si="31"/>
+        <v>STR_MAP_S4_009_DESC</v>
+      </c>
+      <c r="F63" s="34">
+        <v>4</v>
+      </c>
+      <c r="G63" s="34">
+        <v>3</v>
+      </c>
+      <c r="H63" s="34" t="s">
+        <v>461</v>
+      </c>
+      <c r="I63" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J63" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K63" s="34">
+        <v>0</v>
+      </c>
+      <c r="L63" s="34" t="s">
+        <v>360</v>
+      </c>
+      <c r="M63" s="34" t="s">
+        <v>358</v>
+      </c>
+      <c r="N63" s="34" t="s">
+        <v>462</v>
+      </c>
+      <c r="O63" s="36" t="s">
+        <v>359</v>
+      </c>
+      <c r="P63" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q63" s="34">
+        <v>0</v>
+      </c>
+      <c r="R63" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S63" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T63" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U63" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V63" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A64" s="34">
+        <v>50062</v>
+      </c>
+      <c r="B64" s="36" t="s">
+        <v>416</v>
+      </c>
+      <c r="C64" s="34" t="s">
+        <v>445</v>
+      </c>
+      <c r="D64" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v>STR_MAP_S4_010</v>
+      </c>
+      <c r="E64" s="34" t="str">
+        <f t="shared" si="31"/>
+        <v>STR_MAP_S4_010_DESC</v>
+      </c>
+      <c r="F64" s="34">
+        <v>4</v>
+      </c>
+      <c r="G64" s="34">
+        <v>3</v>
+      </c>
+      <c r="H64" s="34" t="s">
+        <v>461</v>
+      </c>
+      <c r="I64" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J64" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K64" s="34">
+        <v>0</v>
+      </c>
+      <c r="L64" s="34" t="s">
+        <v>363</v>
+      </c>
+      <c r="M64" s="34" t="s">
+        <v>361</v>
+      </c>
+      <c r="N64" s="34" t="s">
+        <v>462</v>
+      </c>
+      <c r="O64" s="36" t="s">
+        <v>362</v>
+      </c>
+      <c r="P64" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q64" s="34">
+        <v>0</v>
+      </c>
+      <c r="R64" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S64" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T64" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U64" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V64" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A65" s="34">
+        <v>50063</v>
+      </c>
+      <c r="B65" s="36" t="s">
+        <v>417</v>
+      </c>
+      <c r="C65" s="34" t="s">
+        <v>446</v>
+      </c>
+      <c r="D65" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v>STR_MAP_S4_011</v>
+      </c>
+      <c r="E65" s="34" t="str">
+        <f t="shared" si="31"/>
+        <v>STR_MAP_S4_011_DESC</v>
+      </c>
+      <c r="F65" s="34">
+        <v>4</v>
+      </c>
+      <c r="G65" s="34">
+        <v>3</v>
+      </c>
+      <c r="H65" s="34" t="s">
+        <v>461</v>
+      </c>
+      <c r="I65" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J65" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K65" s="34">
+        <v>0</v>
+      </c>
+      <c r="L65" s="34" t="s">
+        <v>366</v>
+      </c>
+      <c r="M65" s="34" t="s">
+        <v>364</v>
+      </c>
+      <c r="N65" s="34" t="s">
+        <v>462</v>
+      </c>
+      <c r="O65" s="36" t="s">
+        <v>365</v>
+      </c>
+      <c r="P65" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q65" s="34">
+        <v>0</v>
+      </c>
+      <c r="R65" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S65" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T65" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U65" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V65" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A66" s="34">
+        <v>50064</v>
+      </c>
+      <c r="B66" s="36" t="s">
+        <v>418</v>
+      </c>
+      <c r="C66" s="34" t="s">
+        <v>447</v>
+      </c>
+      <c r="D66" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v>STR_MAP_S4_012</v>
+      </c>
+      <c r="E66" s="34" t="str">
+        <f t="shared" si="31"/>
+        <v>STR_MAP_S4_012_DESC</v>
+      </c>
+      <c r="F66" s="34">
+        <v>4</v>
+      </c>
+      <c r="G66" s="34">
+        <v>3</v>
+      </c>
+      <c r="H66" s="34" t="s">
+        <v>461</v>
+      </c>
+      <c r="I66" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J66" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K66" s="34">
+        <v>0</v>
+      </c>
+      <c r="L66" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="M66" s="34" t="s">
+        <v>367</v>
+      </c>
+      <c r="N66" s="34" t="s">
+        <v>462</v>
+      </c>
+      <c r="O66" s="36" t="s">
+        <v>368</v>
+      </c>
+      <c r="P66" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q66" s="34">
+        <v>0</v>
+      </c>
+      <c r="R66" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S66" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T66" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U66" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V66" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A67" s="34">
+        <v>50065</v>
+      </c>
+      <c r="B67" s="36" t="s">
+        <v>419</v>
+      </c>
+      <c r="C67" s="34" t="s">
+        <v>448</v>
+      </c>
+      <c r="D67" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v>STR_MAP_S4_013</v>
+      </c>
+      <c r="E67" s="34" t="str">
+        <f t="shared" si="31"/>
+        <v>STR_MAP_S4_013_DESC</v>
+      </c>
+      <c r="F67" s="34">
+        <v>4</v>
+      </c>
+      <c r="G67" s="34">
+        <v>3</v>
+      </c>
+      <c r="H67" s="34" t="s">
+        <v>461</v>
+      </c>
+      <c r="I67" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J67" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K67" s="34">
+        <v>0</v>
+      </c>
+      <c r="L67" s="34" t="s">
+        <v>372</v>
+      </c>
+      <c r="M67" s="34" t="s">
+        <v>370</v>
+      </c>
+      <c r="N67" s="34" t="s">
+        <v>462</v>
+      </c>
+      <c r="O67" s="36" t="s">
+        <v>371</v>
+      </c>
+      <c r="P67" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q67" s="34">
+        <v>0</v>
+      </c>
+      <c r="R67" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S67" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T67" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U67" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V67" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A68" s="34">
+        <v>50066</v>
+      </c>
+      <c r="B68" s="36" t="s">
+        <v>420</v>
+      </c>
+      <c r="C68" s="34" t="s">
+        <v>449</v>
+      </c>
+      <c r="D68" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v>STR_MAP_S4_014</v>
+      </c>
+      <c r="E68" s="34" t="str">
+        <f t="shared" si="31"/>
+        <v>STR_MAP_S4_014_DESC</v>
+      </c>
+      <c r="F68" s="34">
+        <v>4</v>
+      </c>
+      <c r="G68" s="34">
+        <v>3</v>
+      </c>
+      <c r="H68" s="34" t="s">
+        <v>461</v>
+      </c>
+      <c r="I68" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J68" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K68" s="34">
+        <v>0</v>
+      </c>
+      <c r="L68" s="34" t="s">
+        <v>375</v>
+      </c>
+      <c r="M68" s="34" t="s">
+        <v>373</v>
+      </c>
+      <c r="N68" s="34" t="s">
+        <v>462</v>
+      </c>
+      <c r="O68" s="36" t="s">
+        <v>374</v>
+      </c>
+      <c r="P68" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q68" s="34">
+        <v>0</v>
+      </c>
+      <c r="R68" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S68" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T68" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U68" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V68" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A69" s="34">
+        <v>50067</v>
+      </c>
+      <c r="B69" s="36" t="s">
+        <v>421</v>
+      </c>
+      <c r="C69" s="34" t="s">
+        <v>450</v>
+      </c>
+      <c r="D69" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v>STR_MAP_S4_015</v>
+      </c>
+      <c r="E69" s="34" t="str">
+        <f t="shared" si="31"/>
+        <v>STR_MAP_S4_015_DESC</v>
+      </c>
+      <c r="F69" s="34">
+        <v>4</v>
+      </c>
+      <c r="G69" s="34">
+        <v>3</v>
+      </c>
+      <c r="H69" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="I69" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J69" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K69" s="34">
+        <v>0</v>
+      </c>
+      <c r="L69" s="34" t="s">
+        <v>378</v>
+      </c>
+      <c r="M69" s="34" t="s">
+        <v>376</v>
+      </c>
+      <c r="N69" s="34" t="s">
+        <v>463</v>
+      </c>
+      <c r="O69" s="36" t="s">
+        <v>377</v>
+      </c>
+      <c r="P69" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q69" s="34">
+        <v>0</v>
+      </c>
+      <c r="R69" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S69" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T69" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U69" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V69" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A70" s="34">
+        <v>50068</v>
+      </c>
+      <c r="B70" s="36" t="s">
+        <v>422</v>
+      </c>
+      <c r="C70" s="34" t="s">
+        <v>451</v>
+      </c>
+      <c r="D70" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v>STR_MAP_S4_016</v>
+      </c>
+      <c r="E70" s="34" t="str">
+        <f t="shared" si="31"/>
+        <v>STR_MAP_S4_016_DESC</v>
+      </c>
+      <c r="F70" s="34">
+        <v>4</v>
+      </c>
+      <c r="G70" s="34">
+        <v>3</v>
+      </c>
+      <c r="H70" s="34" t="s">
+        <v>461</v>
+      </c>
+      <c r="I70" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J70" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K70" s="34">
+        <v>0</v>
+      </c>
+      <c r="L70" s="34" t="s">
+        <v>381</v>
+      </c>
+      <c r="M70" s="34" t="s">
+        <v>379</v>
+      </c>
+      <c r="N70" s="34" t="s">
+        <v>462</v>
+      </c>
+      <c r="O70" s="36" t="s">
+        <v>380</v>
+      </c>
+      <c r="P70" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q70" s="34">
+        <v>0</v>
+      </c>
+      <c r="R70" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S70" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T70" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U70" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V70" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A71" s="34">
+        <v>50069</v>
+      </c>
+      <c r="B71" s="36" t="s">
+        <v>423</v>
+      </c>
+      <c r="C71" s="34" t="s">
+        <v>452</v>
+      </c>
+      <c r="D71" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v>STR_MAP_S4_017</v>
+      </c>
+      <c r="E71" s="34" t="str">
+        <f t="shared" si="31"/>
+        <v>STR_MAP_S4_017_DESC</v>
+      </c>
+      <c r="F71" s="34">
+        <v>4</v>
+      </c>
+      <c r="G71" s="34">
+        <v>3</v>
+      </c>
+      <c r="H71" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="I71" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J71" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K71" s="34">
+        <v>0</v>
+      </c>
+      <c r="L71" s="34" t="s">
+        <v>384</v>
+      </c>
+      <c r="M71" s="34" t="s">
+        <v>382</v>
+      </c>
+      <c r="N71" s="34" t="s">
+        <v>465</v>
+      </c>
+      <c r="O71" s="36" t="s">
+        <v>383</v>
+      </c>
+      <c r="P71" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q71" s="34">
+        <v>0</v>
+      </c>
+      <c r="R71" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S71" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T71" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U71" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V71" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A72" s="34">
+        <v>50070</v>
+      </c>
+      <c r="B72" s="36" t="s">
+        <v>424</v>
+      </c>
+      <c r="C72" s="34" t="s">
+        <v>453</v>
+      </c>
+      <c r="D72" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v>STR_MAP_S4_018</v>
+      </c>
+      <c r="E72" s="34" t="str">
+        <f t="shared" si="31"/>
+        <v>STR_MAP_S4_018_DESC</v>
+      </c>
+      <c r="F72" s="34">
+        <v>4</v>
+      </c>
+      <c r="G72" s="34">
+        <v>3</v>
+      </c>
+      <c r="H72" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="I72" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J72" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K72" s="34">
+        <v>0</v>
+      </c>
+      <c r="L72" s="34" t="s">
+        <v>387</v>
+      </c>
+      <c r="M72" s="34" t="s">
+        <v>385</v>
+      </c>
+      <c r="N72" s="34" t="s">
+        <v>465</v>
+      </c>
+      <c r="O72" s="36" t="s">
+        <v>386</v>
+      </c>
+      <c r="P72" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q72" s="34">
+        <v>0</v>
+      </c>
+      <c r="R72" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S72" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T72" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U72" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V72" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A73" s="34">
+        <v>50071</v>
+      </c>
+      <c r="B73" s="36" t="s">
+        <v>425</v>
+      </c>
+      <c r="C73" s="34" t="s">
+        <v>454</v>
+      </c>
+      <c r="D73" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v>STR_MAP_S4_019</v>
+      </c>
+      <c r="E73" s="34" t="str">
+        <f t="shared" si="31"/>
+        <v>STR_MAP_S4_019_DESC</v>
+      </c>
+      <c r="F73" s="34">
+        <v>4</v>
+      </c>
+      <c r="G73" s="34">
+        <v>3</v>
+      </c>
+      <c r="H73" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="I73" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J73" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K73" s="34">
+        <v>0</v>
+      </c>
+      <c r="L73" s="34" t="s">
+        <v>390</v>
+      </c>
+      <c r="M73" s="34" t="s">
+        <v>388</v>
+      </c>
+      <c r="N73" s="34" t="s">
+        <v>463</v>
+      </c>
+      <c r="O73" s="36" t="s">
+        <v>389</v>
+      </c>
+      <c r="P73" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q73" s="34">
+        <v>0</v>
+      </c>
+      <c r="R73" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S73" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T73" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U73" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V73" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A74" s="34">
+        <v>50072</v>
+      </c>
+      <c r="B74" s="36" t="s">
+        <v>426</v>
+      </c>
+      <c r="C74" s="34" t="s">
+        <v>455</v>
+      </c>
+      <c r="D74" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v>STR_MAP_S4_020</v>
+      </c>
+      <c r="E74" s="34" t="str">
+        <f t="shared" si="31"/>
+        <v>STR_MAP_S4_020_DESC</v>
+      </c>
+      <c r="F74" s="34">
+        <v>4</v>
+      </c>
+      <c r="G74" s="34">
+        <v>3</v>
+      </c>
+      <c r="H74" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="I74" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J74" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K74" s="34">
+        <v>0</v>
+      </c>
+      <c r="L74" s="34" t="s">
+        <v>393</v>
+      </c>
+      <c r="M74" s="34" t="s">
+        <v>391</v>
+      </c>
+      <c r="N74" s="34" t="s">
+        <v>465</v>
+      </c>
+      <c r="O74" s="36" t="s">
+        <v>392</v>
+      </c>
+      <c r="P74" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q74" s="34">
+        <v>0</v>
+      </c>
+      <c r="R74" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S74" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T74" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U74" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V74" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A75" s="34">
+        <v>50073</v>
+      </c>
+      <c r="B75" s="36" t="s">
+        <v>427</v>
+      </c>
+      <c r="C75" s="34" t="s">
+        <v>456</v>
+      </c>
+      <c r="D75" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v>STR_MAP_S4_021</v>
+      </c>
+      <c r="E75" s="34" t="str">
+        <f t="shared" si="31"/>
+        <v>STR_MAP_S4_021_DESC</v>
+      </c>
+      <c r="F75" s="34">
+        <v>4</v>
+      </c>
+      <c r="G75" s="34">
+        <v>3</v>
+      </c>
+      <c r="H75" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="I75" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J75" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K75" s="34">
+        <v>0</v>
+      </c>
+      <c r="L75" s="34" t="s">
+        <v>396</v>
+      </c>
+      <c r="M75" s="34" t="s">
+        <v>394</v>
+      </c>
+      <c r="N75" s="34" t="s">
+        <v>465</v>
+      </c>
+      <c r="O75" s="36" t="s">
+        <v>395</v>
+      </c>
+      <c r="P75" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q75" s="34">
+        <v>0</v>
+      </c>
+      <c r="R75" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S75" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T75" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U75" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V75" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A76" s="34">
+        <v>50074</v>
+      </c>
+      <c r="B76" s="36" t="s">
+        <v>428</v>
+      </c>
+      <c r="C76" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="D76" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v>STR_MAP_S4_022</v>
+      </c>
+      <c r="E76" s="34" t="str">
+        <f t="shared" si="31"/>
+        <v>STR_MAP_S4_022_DESC</v>
+      </c>
+      <c r="F76" s="34">
+        <v>4</v>
+      </c>
+      <c r="G76" s="34">
+        <v>3</v>
+      </c>
+      <c r="H76" s="34" t="s">
+        <v>461</v>
+      </c>
+      <c r="I76" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J76" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K76" s="34">
+        <v>0</v>
+      </c>
+      <c r="L76" s="34" t="s">
+        <v>399</v>
+      </c>
+      <c r="M76" s="34" t="s">
+        <v>397</v>
+      </c>
+      <c r="N76" s="34" t="s">
+        <v>462</v>
+      </c>
+      <c r="O76" s="36" t="s">
+        <v>398</v>
+      </c>
+      <c r="P76" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q76" s="34">
+        <v>0</v>
+      </c>
+      <c r="R76" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S76" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T76" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U76" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V76" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A77" s="34">
+        <v>50075</v>
+      </c>
+      <c r="B77" s="36" t="s">
+        <v>429</v>
+      </c>
+      <c r="C77" s="34" t="s">
+        <v>458</v>
+      </c>
+      <c r="D77" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v>STR_MAP_S4_023</v>
+      </c>
+      <c r="E77" s="34" t="str">
+        <f t="shared" si="31"/>
+        <v>STR_MAP_S4_023_DESC</v>
+      </c>
+      <c r="F77" s="34">
+        <v>4</v>
+      </c>
+      <c r="G77" s="34">
+        <v>3</v>
+      </c>
+      <c r="H77" s="34" t="s">
+        <v>461</v>
+      </c>
+      <c r="I77" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J77" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K77" s="34">
+        <v>0</v>
+      </c>
+      <c r="L77" s="34" t="s">
+        <v>402</v>
+      </c>
+      <c r="M77" s="34" t="s">
+        <v>400</v>
+      </c>
+      <c r="N77" s="34" t="s">
+        <v>462</v>
+      </c>
+      <c r="O77" s="36" t="s">
+        <v>401</v>
+      </c>
+      <c r="P77" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q77" s="34">
+        <v>0</v>
+      </c>
+      <c r="R77" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S77" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T77" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U77" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V77" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A78" s="34">
+        <v>50076</v>
+      </c>
+      <c r="B78" s="36" t="s">
+        <v>430</v>
+      </c>
+      <c r="C78" s="34" t="s">
+        <v>459</v>
+      </c>
+      <c r="D78" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v>STR_MAP_S4_024</v>
+      </c>
+      <c r="E78" s="34" t="str">
+        <f t="shared" si="31"/>
+        <v>STR_MAP_S4_024_DESC</v>
+      </c>
+      <c r="F78" s="34">
+        <v>4</v>
+      </c>
+      <c r="G78" s="34">
+        <v>3</v>
+      </c>
+      <c r="H78" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="I78" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J78" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K78" s="34">
+        <v>0</v>
+      </c>
+      <c r="L78" s="34" t="s">
+        <v>405</v>
+      </c>
+      <c r="M78" s="34" t="s">
+        <v>403</v>
+      </c>
+      <c r="N78" s="34" t="s">
+        <v>463</v>
+      </c>
+      <c r="O78" s="36" t="s">
+        <v>404</v>
+      </c>
+      <c r="P78" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q78" s="34">
+        <v>0</v>
+      </c>
+      <c r="R78" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S78" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T78" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U78" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V78" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A79" s="34">
+        <v>50077</v>
+      </c>
+      <c r="B79" s="36" t="s">
+        <v>431</v>
+      </c>
+      <c r="C79" s="34" t="s">
+        <v>460</v>
+      </c>
+      <c r="D79" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v>STR_MAP_S4_025</v>
+      </c>
+      <c r="E79" s="34" t="str">
+        <f t="shared" si="31"/>
+        <v>STR_MAP_S4_025_DESC</v>
+      </c>
+      <c r="F79" s="34">
+        <v>4</v>
+      </c>
+      <c r="G79" s="34">
+        <v>3</v>
+      </c>
+      <c r="H79" s="34" t="s">
+        <v>461</v>
+      </c>
+      <c r="I79" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J79" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K79" s="34">
+        <v>0</v>
+      </c>
+      <c r="L79" s="34" t="s">
+        <v>432</v>
+      </c>
+      <c r="M79" s="34" t="s">
+        <v>406</v>
+      </c>
+      <c r="N79" s="34" t="s">
+        <v>462</v>
+      </c>
+      <c r="O79" s="36" t="s">
+        <v>407</v>
+      </c>
+      <c r="P79" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q79" s="34">
+        <v>0</v>
+      </c>
+      <c r="R79" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="S79" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T79" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U79" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V79" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A80" s="34">
+        <v>50078</v>
+      </c>
+      <c r="B80" s="36" t="s">
+        <v>435</v>
+      </c>
+      <c r="C80" s="34" t="s">
+        <v>467</v>
+      </c>
+      <c r="D80" s="34" t="str">
+        <f t="shared" ref="D80" si="34">"STR_"&amp;UPPER(C80)</f>
+        <v>STR_MAP_S4_026</v>
+      </c>
+      <c r="E80" s="34" t="str">
+        <f t="shared" ref="E80" si="35">D80&amp;"_DESC"</f>
+        <v>STR_MAP_S4_026_DESC</v>
+      </c>
+      <c r="F80" s="34">
+        <v>4</v>
+      </c>
+      <c r="G80" s="34">
+        <v>3</v>
+      </c>
+      <c r="H80" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="I80" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J80" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K80" s="34">
+        <v>0</v>
+      </c>
+      <c r="L80" s="34" t="s">
+        <v>468</v>
+      </c>
+      <c r="M80" s="34" t="s">
+        <v>433</v>
+      </c>
+      <c r="N80" s="34" t="s">
+        <v>465</v>
+      </c>
+      <c r="O80" s="36" t="s">
+        <v>434</v>
+      </c>
+      <c r="P80" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q80" s="34">
+        <v>0</v>
+      </c>
+      <c r="R80" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="U80" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V80" s="36" t="s">
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -8841,7 +11061,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="8">
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Definition!#REF!</xm:f>
@@ -8873,7 +11093,7 @@
           <x14:formula2>
             <xm:f>Definition!G12</xm:f>
           </x14:formula2>
-          <xm:sqref>G11 G29:G41 G27</xm:sqref>
+          <xm:sqref>G11 G27 G29:G41</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -8882,7 +11102,16 @@
           <x14:formula2>
             <xm:f>Definition!G10</xm:f>
           </x14:formula2>
-          <xm:sqref>I2:I54</xm:sqref>
+          <xm:sqref>I2:I62</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>Definition!F70</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>Definition!G70</xm:f>
+          </x14:formula2>
+          <xm:sqref>I63:I80</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -8891,7 +11120,16 @@
           <x14:formula2>
             <xm:f>Definition!G8</xm:f>
           </x14:formula2>
-          <xm:sqref>G2:G5 G47:G54</xm:sqref>
+          <xm:sqref>G2:G5 G47:G62</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>Definition!F68</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>Definition!G68</xm:f>
+          </x14:formula2>
+          <xm:sqref>G63:G80</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/30_table/01_테스트버전/Table_Data_Map.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Map.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="471">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1323,305 +1323,323 @@
     <t>img_map_0033</t>
   </si>
   <si>
+    <t>pf_Map_50065</t>
+  </si>
+  <si>
+    <t>img_map_0034</t>
+  </si>
+  <si>
+    <t>pf_Map_50066</t>
+  </si>
+  <si>
+    <t>img_map_0035</t>
+  </si>
+  <si>
+    <t>pf_Map_50067</t>
+  </si>
+  <si>
+    <t>img_map_0036</t>
+  </si>
+  <si>
+    <t>pf_Map_50068</t>
+  </si>
+  <si>
+    <t>img_map_0037</t>
+  </si>
+  <si>
+    <t>pf_Map_50069</t>
+  </si>
+  <si>
+    <t>img_map_0038</t>
+  </si>
+  <si>
+    <t>pf_Map_50070</t>
+  </si>
+  <si>
+    <t>img_map_0039</t>
+  </si>
+  <si>
+    <t>pf_Map_50071</t>
+  </si>
+  <si>
+    <t>img_map_0040</t>
+  </si>
+  <si>
+    <t>pf_Map_50072</t>
+  </si>
+  <si>
+    <t>img_map_0041</t>
+  </si>
+  <si>
+    <t>pf_Map_50073</t>
+  </si>
+  <si>
+    <t>img_map_0042</t>
+  </si>
+  <si>
+    <t>pf_Map_50074</t>
+  </si>
+  <si>
+    <t>img_map_0043</t>
+  </si>
+  <si>
+    <t>pf_Map_50075</t>
+  </si>
+  <si>
+    <t>img_map_0044</t>
+  </si>
+  <si>
+    <t>pf_Map_50076</t>
+  </si>
+  <si>
+    <t>img_map_0045</t>
+  </si>
+  <si>
+    <t>욕심</t>
+  </si>
+  <si>
+    <t>죽은 자의 동굴  1층</t>
+  </si>
+  <si>
+    <t>좀비 조심</t>
+  </si>
+  <si>
+    <t>박쥐 사냥</t>
+  </si>
+  <si>
+    <t>좀비방</t>
+  </si>
+  <si>
+    <t>숨겨진 방으로</t>
+  </si>
+  <si>
+    <t>보물방</t>
+  </si>
+  <si>
+    <t>믿음</t>
+  </si>
+  <si>
+    <t>만족</t>
+  </si>
+  <si>
+    <t>지하 2층으로</t>
+  </si>
+  <si>
+    <t>죽은 자의 동굴 2층</t>
+  </si>
+  <si>
+    <t>구울 조심</t>
+  </si>
+  <si>
+    <t>함정 1</t>
+  </si>
+  <si>
+    <t>구울방</t>
+  </si>
+  <si>
+    <t>함정 2</t>
+  </si>
+  <si>
+    <t>라미를 찾아서</t>
+  </si>
+  <si>
+    <t>라미의 부탁</t>
+  </si>
+  <si>
+    <t>좀비의 영혼</t>
+  </si>
+  <si>
+    <t>라미에게 줄 선물</t>
+  </si>
+  <si>
+    <t>라미의 조언</t>
+  </si>
+  <si>
+    <t>서큐버스를 찾아서 1</t>
+  </si>
+  <si>
+    <t>서큐버스를 찾아서 2</t>
+  </si>
+  <si>
+    <t>서큐버스 처치</t>
+  </si>
+  <si>
+    <t>서고로 이동</t>
+  </si>
+  <si>
+    <t>pf_Map_50077</t>
+  </si>
+  <si>
+    <t>img_map_0046</t>
+  </si>
+  <si>
+    <t>단서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map_s4_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map_s4_002</t>
+  </si>
+  <si>
+    <t>map_s4_003</t>
+  </si>
+  <si>
+    <t>map_s4_004</t>
+  </si>
+  <si>
+    <t>map_s4_005</t>
+  </si>
+  <si>
+    <t>map_s4_006</t>
+  </si>
+  <si>
+    <t>map_s4_007</t>
+  </si>
+  <si>
+    <t>map_s4_008</t>
+  </si>
+  <si>
+    <t>map_s4_009</t>
+  </si>
+  <si>
+    <t>map_s4_010</t>
+  </si>
+  <si>
+    <t>map_s4_011</t>
+  </si>
+  <si>
+    <t>map_s4_012</t>
+  </si>
+  <si>
+    <t>map_s4_013</t>
+  </si>
+  <si>
+    <t>map_s4_014</t>
+  </si>
+  <si>
+    <t>map_s4_015</t>
+  </si>
+  <si>
+    <t>map_s4_016</t>
+  </si>
+  <si>
+    <t>map_s4_017</t>
+  </si>
+  <si>
+    <t>map_s4_018</t>
+  </si>
+  <si>
+    <t>map_s4_019</t>
+  </si>
+  <si>
+    <t>map_s4_020</t>
+  </si>
+  <si>
+    <t>map_s4_021</t>
+  </si>
+  <si>
+    <t>map_s4_022</t>
+  </si>
+  <si>
+    <t>map_s4_023</t>
+  </si>
+  <si>
+    <t>map_s4_024</t>
+  </si>
+  <si>
+    <t>map_s4_025</t>
+  </si>
+  <si>
+    <t>Move</t>
+  </si>
+  <si>
+    <t>bgm_41</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm_42</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm_43</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동굴 1층</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map_s4_026</t>
+  </si>
+  <si>
+    <t>pf_Map_50078</t>
+  </si>
+  <si>
+    <t>icon_map_0023</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0026</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>icon_map_0033</t>
-  </si>
-  <si>
-    <t>pf_Map_50065</t>
-  </si>
-  <si>
-    <t>img_map_0034</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>icon_map_0034</t>
-  </si>
-  <si>
-    <t>pf_Map_50066</t>
-  </si>
-  <si>
-    <t>img_map_0035</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>icon_map_0035</t>
-  </si>
-  <si>
-    <t>pf_Map_50067</t>
-  </si>
-  <si>
-    <t>img_map_0036</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>icon_map_0036</t>
-  </si>
-  <si>
-    <t>pf_Map_50068</t>
-  </si>
-  <si>
-    <t>img_map_0037</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>icon_map_0037</t>
-  </si>
-  <si>
-    <t>pf_Map_50069</t>
-  </si>
-  <si>
-    <t>img_map_0038</t>
-  </si>
-  <si>
-    <t>icon_map_0038</t>
-  </si>
-  <si>
-    <t>pf_Map_50070</t>
-  </si>
-  <si>
-    <t>img_map_0039</t>
-  </si>
-  <si>
-    <t>icon_map_0039</t>
-  </si>
-  <si>
-    <t>pf_Map_50071</t>
-  </si>
-  <si>
-    <t>img_map_0040</t>
-  </si>
-  <si>
-    <t>icon_map_0040</t>
-  </si>
-  <si>
-    <t>pf_Map_50072</t>
-  </si>
-  <si>
-    <t>img_map_0041</t>
-  </si>
-  <si>
-    <t>icon_map_0041</t>
-  </si>
-  <si>
-    <t>pf_Map_50073</t>
-  </si>
-  <si>
-    <t>img_map_0042</t>
-  </si>
-  <si>
-    <t>icon_map_0042</t>
-  </si>
-  <si>
-    <t>pf_Map_50074</t>
-  </si>
-  <si>
-    <t>img_map_0043</t>
-  </si>
-  <si>
-    <t>icon_map_0043</t>
-  </si>
-  <si>
-    <t>pf_Map_50075</t>
-  </si>
-  <si>
-    <t>img_map_0044</t>
-  </si>
-  <si>
-    <t>icon_map_0044</t>
-  </si>
-  <si>
-    <t>pf_Map_50076</t>
-  </si>
-  <si>
-    <t>img_map_0045</t>
-  </si>
-  <si>
-    <t>icon_map_0045</t>
-  </si>
-  <si>
-    <t>욕심</t>
-  </si>
-  <si>
-    <t>죽은 자의 동굴  1층</t>
-  </si>
-  <si>
-    <t>좀비 조심</t>
-  </si>
-  <si>
-    <t>박쥐 사냥</t>
-  </si>
-  <si>
-    <t>좀비방</t>
-  </si>
-  <si>
-    <t>숨겨진 방으로</t>
-  </si>
-  <si>
-    <t>보물방</t>
-  </si>
-  <si>
-    <t>믿음</t>
-  </si>
-  <si>
-    <t>만족</t>
-  </si>
-  <si>
-    <t>지하 2층으로</t>
-  </si>
-  <si>
-    <t>죽은 자의 동굴 2층</t>
-  </si>
-  <si>
-    <t>구울 조심</t>
-  </si>
-  <si>
-    <t>함정 1</t>
-  </si>
-  <si>
-    <t>구울방</t>
-  </si>
-  <si>
-    <t>함정 2</t>
-  </si>
-  <si>
-    <t>라미를 찾아서</t>
-  </si>
-  <si>
-    <t>라미의 부탁</t>
-  </si>
-  <si>
-    <t>좀비의 영혼</t>
-  </si>
-  <si>
-    <t>라미에게 줄 선물</t>
-  </si>
-  <si>
-    <t>라미의 조언</t>
-  </si>
-  <si>
-    <t>서큐버스를 찾아서 1</t>
-  </si>
-  <si>
-    <t>서큐버스를 찾아서 2</t>
-  </si>
-  <si>
-    <t>서큐버스 처치</t>
-  </si>
-  <si>
-    <t>서고로 이동</t>
-  </si>
-  <si>
-    <t>pf_Map_50077</t>
-  </si>
-  <si>
-    <t>img_map_0046</t>
-  </si>
-  <si>
-    <t>icon_map_0046</t>
-  </si>
-  <si>
-    <t>단서</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>map_s4_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>map_s4_002</t>
-  </si>
-  <si>
-    <t>map_s4_003</t>
-  </si>
-  <si>
-    <t>map_s4_004</t>
-  </si>
-  <si>
-    <t>map_s4_005</t>
-  </si>
-  <si>
-    <t>map_s4_006</t>
-  </si>
-  <si>
-    <t>map_s4_007</t>
-  </si>
-  <si>
-    <t>map_s4_008</t>
-  </si>
-  <si>
-    <t>map_s4_009</t>
-  </si>
-  <si>
-    <t>map_s4_010</t>
-  </si>
-  <si>
-    <t>map_s4_011</t>
-  </si>
-  <si>
-    <t>map_s4_012</t>
-  </si>
-  <si>
-    <t>map_s4_013</t>
-  </si>
-  <si>
-    <t>map_s4_014</t>
-  </si>
-  <si>
-    <t>map_s4_015</t>
-  </si>
-  <si>
-    <t>map_s4_016</t>
-  </si>
-  <si>
-    <t>map_s4_017</t>
-  </si>
-  <si>
-    <t>map_s4_018</t>
-  </si>
-  <si>
-    <t>map_s4_019</t>
-  </si>
-  <si>
-    <t>map_s4_020</t>
-  </si>
-  <si>
-    <t>map_s4_021</t>
-  </si>
-  <si>
-    <t>map_s4_022</t>
-  </si>
-  <si>
-    <t>map_s4_023</t>
-  </si>
-  <si>
-    <t>map_s4_024</t>
-  </si>
-  <si>
-    <t>map_s4_025</t>
-  </si>
-  <si>
-    <t>Move</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map_s4_027</t>
+  </si>
+  <si>
+    <t>pf_Map_50079</t>
   </si>
   <si>
     <t>bgm_41</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>bgm_42</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bgm_02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bgm_43</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>동굴 1층</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>map_s4_026</t>
-  </si>
-  <si>
-    <t>pf_Map_50078</t>
+    <t>비밀 서고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QuestTalk</t>
+  </si>
+  <si>
+    <t>QuestTalk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QuestMob</t>
+  </si>
+  <si>
+    <t>QuestMob</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -5603,7 +5621,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:V80"/>
+  <dimension ref="A1:V81"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" style="36" bestFit="1" customWidth="1"/>
@@ -9245,10 +9263,10 @@
         <v>50053</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="C55" s="34" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="D55" s="34" t="str">
         <f t="shared" ref="D55:D79" si="30">"STR_"&amp;UPPER(C55)</f>
@@ -9265,7 +9283,7 @@
         <v>3</v>
       </c>
       <c r="H55" s="34" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="I55" s="34">
         <v>8.8000000000000007</v>
@@ -9283,7 +9301,7 @@
         <v>337</v>
       </c>
       <c r="N55" s="34" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="O55" s="36" t="s">
         <v>338</v>
@@ -9315,10 +9333,10 @@
         <v>50054</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="C56" s="34" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="D56" s="34" t="str">
         <f t="shared" si="30"/>
@@ -9335,7 +9353,7 @@
         <v>3</v>
       </c>
       <c r="H56" s="34" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="I56" s="34">
         <v>8.8000000000000007</v>
@@ -9353,7 +9371,7 @@
         <v>340</v>
       </c>
       <c r="N56" s="34" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="O56" s="36" t="s">
         <v>341</v>
@@ -9385,10 +9403,10 @@
         <v>50055</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="C57" s="34" t="s">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c r="D57" s="34" t="str">
         <f t="shared" si="30"/>
@@ -9405,7 +9423,7 @@
         <v>3</v>
       </c>
       <c r="H57" s="34" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="I57" s="34">
         <v>8.8000000000000007</v>
@@ -9423,7 +9441,7 @@
         <v>343</v>
       </c>
       <c r="N57" s="34" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="O57" s="36" t="s">
         <v>344</v>
@@ -9455,10 +9473,10 @@
         <v>50056</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="C58" s="34" t="s">
-        <v>439</v>
+        <v>425</v>
       </c>
       <c r="D58" s="34" t="str">
         <f t="shared" si="30"/>
@@ -9493,7 +9511,7 @@
         <v>346</v>
       </c>
       <c r="N58" s="34" t="s">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="O58" s="36" t="s">
         <v>347</v>
@@ -9525,10 +9543,10 @@
         <v>50057</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="C59" s="34" t="s">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="D59" s="34" t="str">
         <f t="shared" si="30"/>
@@ -9563,7 +9581,7 @@
         <v>349</v>
       </c>
       <c r="N59" s="34" t="s">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="O59" s="36" t="s">
         <v>350</v>
@@ -9595,10 +9613,10 @@
         <v>50058</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="C60" s="34" t="s">
-        <v>441</v>
+        <v>427</v>
       </c>
       <c r="D60" s="34" t="str">
         <f t="shared" si="30"/>
@@ -9615,7 +9633,7 @@
         <v>3</v>
       </c>
       <c r="H60" s="34" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="I60" s="34">
         <v>8.8000000000000007</v>
@@ -9633,7 +9651,7 @@
         <v>352</v>
       </c>
       <c r="N60" s="34" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="O60" s="36" t="s">
         <v>353</v>
@@ -9665,10 +9683,10 @@
         <v>50059</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="C61" s="34" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="D61" s="34" t="str">
         <f t="shared" si="30"/>
@@ -9703,7 +9721,7 @@
         <v>355</v>
       </c>
       <c r="N61" s="34" t="s">
-        <v>464</v>
+        <v>450</v>
       </c>
       <c r="O61" s="36" t="s">
         <v>356</v>
@@ -9735,10 +9753,10 @@
         <v>50060</v>
       </c>
       <c r="B62" s="36" t="s">
-        <v>466</v>
+        <v>452</v>
       </c>
       <c r="C62" s="34" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="D62" s="34" t="str">
         <f t="shared" ref="D62" si="32">"STR_"&amp;UPPER(C62)</f>
@@ -9755,7 +9773,7 @@
         <v>3</v>
       </c>
       <c r="H62" s="34" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="I62" s="34">
         <v>8.8000000000000007</v>
@@ -9773,7 +9791,7 @@
         <v>352</v>
       </c>
       <c r="N62" s="34" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="O62" s="36" t="s">
         <v>353</v>
@@ -9805,10 +9823,10 @@
         <v>50061</v>
       </c>
       <c r="B63" s="36" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="C63" s="34" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="D63" s="34" t="str">
         <f t="shared" si="30"/>
@@ -9825,7 +9843,7 @@
         <v>3</v>
       </c>
       <c r="H63" s="34" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="I63" s="34">
         <v>8.8000000000000007</v>
@@ -9843,7 +9861,7 @@
         <v>358</v>
       </c>
       <c r="N63" s="34" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="O63" s="36" t="s">
         <v>359</v>
@@ -9875,10 +9893,10 @@
         <v>50062</v>
       </c>
       <c r="B64" s="36" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="C64" s="34" t="s">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="D64" s="34" t="str">
         <f t="shared" si="30"/>
@@ -9895,7 +9913,7 @@
         <v>3</v>
       </c>
       <c r="H64" s="34" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="I64" s="34">
         <v>8.8000000000000007</v>
@@ -9913,7 +9931,7 @@
         <v>361</v>
       </c>
       <c r="N64" s="34" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="O64" s="36" t="s">
         <v>362</v>
@@ -9945,10 +9963,10 @@
         <v>50063</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="C65" s="34" t="s">
-        <v>446</v>
+        <v>432</v>
       </c>
       <c r="D65" s="34" t="str">
         <f t="shared" si="30"/>
@@ -9965,7 +9983,7 @@
         <v>3</v>
       </c>
       <c r="H65" s="34" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="I65" s="34">
         <v>8.8000000000000007</v>
@@ -9983,7 +10001,7 @@
         <v>364</v>
       </c>
       <c r="N65" s="34" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="O65" s="36" t="s">
         <v>365</v>
@@ -10015,10 +10033,10 @@
         <v>50064</v>
       </c>
       <c r="B66" s="36" t="s">
-        <v>418</v>
+        <v>405</v>
       </c>
       <c r="C66" s="34" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="D66" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10035,7 +10053,7 @@
         <v>3</v>
       </c>
       <c r="H66" s="34" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="I66" s="34">
         <v>8.8000000000000007</v>
@@ -10053,7 +10071,7 @@
         <v>367</v>
       </c>
       <c r="N66" s="34" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="O66" s="36" t="s">
         <v>368</v>
@@ -10085,10 +10103,10 @@
         <v>50065</v>
       </c>
       <c r="B67" s="36" t="s">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="C67" s="34" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="D67" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10105,7 +10123,7 @@
         <v>3</v>
       </c>
       <c r="H67" s="34" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="I67" s="34">
         <v>8.8000000000000007</v>
@@ -10117,16 +10135,16 @@
         <v>0</v>
       </c>
       <c r="L67" s="34" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="M67" s="34" t="s">
         <v>370</v>
       </c>
       <c r="N67" s="34" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="O67" s="36" t="s">
-        <v>371</v>
+        <v>455</v>
       </c>
       <c r="P67" s="36">
         <v>1</v>
@@ -10155,10 +10173,10 @@
         <v>50066</v>
       </c>
       <c r="B68" s="36" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="C68" s="34" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="D68" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10175,7 +10193,7 @@
         <v>3</v>
       </c>
       <c r="H68" s="34" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="I68" s="34">
         <v>8.8000000000000007</v>
@@ -10187,16 +10205,16 @@
         <v>0</v>
       </c>
       <c r="L68" s="34" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="M68" s="34" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="N68" s="34" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="O68" s="36" t="s">
-        <v>374</v>
+        <v>456</v>
       </c>
       <c r="P68" s="36">
         <v>1</v>
@@ -10225,10 +10243,10 @@
         <v>50067</v>
       </c>
       <c r="B69" s="36" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="C69" s="34" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="D69" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10257,16 +10275,16 @@
         <v>0</v>
       </c>
       <c r="L69" s="34" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="M69" s="34" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="N69" s="34" t="s">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="O69" s="36" t="s">
-        <v>377</v>
+        <v>457</v>
       </c>
       <c r="P69" s="36">
         <v>1</v>
@@ -10295,10 +10313,10 @@
         <v>50068</v>
       </c>
       <c r="B70" s="36" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="C70" s="34" t="s">
-        <v>451</v>
+        <v>437</v>
       </c>
       <c r="D70" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10315,7 +10333,7 @@
         <v>3</v>
       </c>
       <c r="H70" s="34" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="I70" s="34">
         <v>8.8000000000000007</v>
@@ -10327,16 +10345,16 @@
         <v>0</v>
       </c>
       <c r="L70" s="34" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="M70" s="34" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="N70" s="34" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="O70" s="36" t="s">
-        <v>380</v>
+        <v>458</v>
       </c>
       <c r="P70" s="36">
         <v>1</v>
@@ -10365,10 +10383,10 @@
         <v>50069</v>
       </c>
       <c r="B71" s="36" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="C71" s="34" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="D71" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10397,16 +10415,16 @@
         <v>0</v>
       </c>
       <c r="L71" s="34" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="M71" s="34" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="N71" s="34" t="s">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="O71" s="36" t="s">
-        <v>383</v>
+        <v>459</v>
       </c>
       <c r="P71" s="36">
         <v>1</v>
@@ -10435,10 +10453,10 @@
         <v>50070</v>
       </c>
       <c r="B72" s="36" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="C72" s="34" t="s">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="D72" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10467,16 +10485,16 @@
         <v>0</v>
       </c>
       <c r="L72" s="34" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="M72" s="34" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="N72" s="34" t="s">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="O72" s="36" t="s">
-        <v>386</v>
+        <v>459</v>
       </c>
       <c r="P72" s="36">
         <v>1</v>
@@ -10505,10 +10523,10 @@
         <v>50071</v>
       </c>
       <c r="B73" s="36" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="C73" s="34" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="D73" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10525,7 +10543,7 @@
         <v>3</v>
       </c>
       <c r="H73" s="34" t="s">
-        <v>134</v>
+        <v>469</v>
       </c>
       <c r="I73" s="34">
         <v>8.8000000000000007</v>
@@ -10537,16 +10555,16 @@
         <v>0</v>
       </c>
       <c r="L73" s="34" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="M73" s="34" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="N73" s="34" t="s">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="O73" s="36" t="s">
-        <v>389</v>
+        <v>460</v>
       </c>
       <c r="P73" s="36">
         <v>1</v>
@@ -10575,10 +10593,10 @@
         <v>50072</v>
       </c>
       <c r="B74" s="36" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="C74" s="34" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="D74" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10595,7 +10613,7 @@
         <v>3</v>
       </c>
       <c r="H74" s="34" t="s">
-        <v>130</v>
+        <v>467</v>
       </c>
       <c r="I74" s="34">
         <v>8.8000000000000007</v>
@@ -10607,16 +10625,16 @@
         <v>0</v>
       </c>
       <c r="L74" s="34" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="M74" s="34" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="N74" s="34" t="s">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="O74" s="36" t="s">
-        <v>392</v>
+        <v>459</v>
       </c>
       <c r="P74" s="36">
         <v>1</v>
@@ -10645,10 +10663,10 @@
         <v>50073</v>
       </c>
       <c r="B75" s="36" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="C75" s="34" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="D75" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10677,16 +10695,16 @@
         <v>0</v>
       </c>
       <c r="L75" s="34" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="M75" s="34" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="N75" s="34" t="s">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="O75" s="36" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="P75" s="36">
         <v>1</v>
@@ -10715,10 +10733,10 @@
         <v>50074</v>
       </c>
       <c r="B76" s="36" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="C76" s="34" t="s">
-        <v>457</v>
+        <v>443</v>
       </c>
       <c r="D76" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10735,7 +10753,7 @@
         <v>3</v>
       </c>
       <c r="H76" s="34" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="I76" s="34">
         <v>8.8000000000000007</v>
@@ -10747,16 +10765,16 @@
         <v>0</v>
       </c>
       <c r="L76" s="34" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="M76" s="34" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="N76" s="34" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="O76" s="36" t="s">
-        <v>398</v>
+        <v>460</v>
       </c>
       <c r="P76" s="36">
         <v>1</v>
@@ -10785,10 +10803,10 @@
         <v>50075</v>
       </c>
       <c r="B77" s="36" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="C77" s="34" t="s">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="D77" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10805,7 +10823,7 @@
         <v>3</v>
       </c>
       <c r="H77" s="34" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="I77" s="34">
         <v>8.8000000000000007</v>
@@ -10817,16 +10835,16 @@
         <v>0</v>
       </c>
       <c r="L77" s="34" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="M77" s="34" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="N77" s="34" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="O77" s="36" t="s">
-        <v>401</v>
+        <v>460</v>
       </c>
       <c r="P77" s="36">
         <v>1</v>
@@ -10855,10 +10873,10 @@
         <v>50076</v>
       </c>
       <c r="B78" s="36" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="C78" s="34" t="s">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="D78" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10887,16 +10905,16 @@
         <v>0</v>
       </c>
       <c r="L78" s="34" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="M78" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="N78" s="34" t="s">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="O78" s="36" t="s">
-        <v>404</v>
+        <v>461</v>
       </c>
       <c r="P78" s="36">
         <v>1</v>
@@ -10925,10 +10943,10 @@
         <v>50077</v>
       </c>
       <c r="B79" s="36" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="C79" s="34" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="D79" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10945,7 +10963,7 @@
         <v>3</v>
       </c>
       <c r="H79" s="34" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="I79" s="34">
         <v>8.8000000000000007</v>
@@ -10957,16 +10975,16 @@
         <v>0</v>
       </c>
       <c r="L79" s="34" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="M79" s="34" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="N79" s="34" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="O79" s="36" t="s">
-        <v>407</v>
+        <v>461</v>
       </c>
       <c r="P79" s="36">
         <v>1</v>
@@ -10995,10 +11013,10 @@
         <v>50078</v>
       </c>
       <c r="B80" s="36" t="s">
-        <v>435</v>
+        <v>466</v>
       </c>
       <c r="C80" s="34" t="s">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="D80" s="34" t="str">
         <f t="shared" ref="D80" si="34">"STR_"&amp;UPPER(C80)</f>
@@ -11015,7 +11033,7 @@
         <v>3</v>
       </c>
       <c r="H80" s="34" t="s">
-        <v>130</v>
+        <v>447</v>
       </c>
       <c r="I80" s="34">
         <v>8.8000000000000007</v>
@@ -11027,16 +11045,16 @@
         <v>0</v>
       </c>
       <c r="L80" s="34" t="s">
-        <v>468</v>
+        <v>454</v>
       </c>
       <c r="M80" s="34" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="N80" s="34" t="s">
         <v>465</v>
       </c>
       <c r="O80" s="36" t="s">
-        <v>434</v>
+        <v>462</v>
       </c>
       <c r="P80" s="36">
         <v>1</v>
@@ -11051,6 +11069,70 @@
         <v>236</v>
       </c>
       <c r="V80" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A81" s="34">
+        <v>50079</v>
+      </c>
+      <c r="B81" s="36" t="s">
+        <v>421</v>
+      </c>
+      <c r="C81" s="34" t="s">
+        <v>463</v>
+      </c>
+      <c r="D81" s="34" t="str">
+        <f t="shared" ref="D81" si="36">"STR_"&amp;UPPER(C81)</f>
+        <v>STR_MAP_S4_027</v>
+      </c>
+      <c r="E81" s="34" t="str">
+        <f t="shared" ref="E81" si="37">D81&amp;"_DESC"</f>
+        <v>STR_MAP_S4_027_DESC</v>
+      </c>
+      <c r="F81" s="34">
+        <v>4</v>
+      </c>
+      <c r="G81" s="34">
+        <v>3</v>
+      </c>
+      <c r="H81" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="I81" s="34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J81" s="34">
+        <v>7.8000000000000007</v>
+      </c>
+      <c r="K81" s="34">
+        <v>0</v>
+      </c>
+      <c r="L81" s="34" t="s">
+        <v>464</v>
+      </c>
+      <c r="M81" s="34" t="s">
+        <v>420</v>
+      </c>
+      <c r="N81" s="34" t="s">
+        <v>451</v>
+      </c>
+      <c r="O81" s="36" t="s">
+        <v>462</v>
+      </c>
+      <c r="P81" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q81" s="34">
+        <v>0</v>
+      </c>
+      <c r="R81" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="U81" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V81" s="36" t="s">
         <v>237</v>
       </c>
     </row>
@@ -11111,7 +11193,7 @@
           <x14:formula2>
             <xm:f>Definition!G70</xm:f>
           </x14:formula2>
-          <xm:sqref>I63:I80</xm:sqref>
+          <xm:sqref>I63:I81</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -11129,7 +11211,7 @@
           <x14:formula2>
             <xm:f>Definition!G68</xm:f>
           </x14:formula2>
-          <xm:sqref>G63:G80</xm:sqref>
+          <xm:sqref>G63:G81</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -11284,7 +11366,9 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
+      <c r="A8" s="1" t="s">
+        <v>468</v>
+      </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -11302,7 +11386,9 @@
       <c r="P8" s="1"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
+      <c r="A9" s="1" t="s">
+        <v>470</v>
+      </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>

--- a/30_table/01_테스트버전/Table_Data_Map.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-165" yWindow="-375" windowWidth="19515" windowHeight="12705" activeTab="2"/>
+    <workbookView xWindow="-165" yWindow="-315" windowWidth="19515" windowHeight="12645" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="DOC History" sheetId="6" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="469">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1320,325 +1320,331 @@
     <t>pf_Map_50064</t>
   </si>
   <si>
+    <t>pf_Map_50065</t>
+  </si>
+  <si>
+    <t>pf_Map_50066</t>
+  </si>
+  <si>
+    <t>pf_Map_50067</t>
+  </si>
+  <si>
+    <t>pf_Map_50068</t>
+  </si>
+  <si>
+    <t>pf_Map_50069</t>
+  </si>
+  <si>
+    <t>pf_Map_50070</t>
+  </si>
+  <si>
+    <t>pf_Map_50071</t>
+  </si>
+  <si>
+    <t>pf_Map_50072</t>
+  </si>
+  <si>
+    <t>pf_Map_50073</t>
+  </si>
+  <si>
+    <t>pf_Map_50074</t>
+  </si>
+  <si>
+    <t>pf_Map_50075</t>
+  </si>
+  <si>
+    <t>pf_Map_50076</t>
+  </si>
+  <si>
+    <t>욕심</t>
+  </si>
+  <si>
+    <t>죽은 자의 동굴  1층</t>
+  </si>
+  <si>
+    <t>좀비 조심</t>
+  </si>
+  <si>
+    <t>박쥐 사냥</t>
+  </si>
+  <si>
+    <t>좀비방</t>
+  </si>
+  <si>
+    <t>숨겨진 방으로</t>
+  </si>
+  <si>
+    <t>보물방</t>
+  </si>
+  <si>
+    <t>믿음</t>
+  </si>
+  <si>
+    <t>만족</t>
+  </si>
+  <si>
+    <t>지하 2층으로</t>
+  </si>
+  <si>
+    <t>죽은 자의 동굴 2층</t>
+  </si>
+  <si>
+    <t>구울 조심</t>
+  </si>
+  <si>
+    <t>함정 1</t>
+  </si>
+  <si>
+    <t>구울방</t>
+  </si>
+  <si>
+    <t>함정 2</t>
+  </si>
+  <si>
+    <t>라미를 찾아서</t>
+  </si>
+  <si>
+    <t>라미의 부탁</t>
+  </si>
+  <si>
+    <t>좀비의 영혼</t>
+  </si>
+  <si>
+    <t>라미에게 줄 선물</t>
+  </si>
+  <si>
+    <t>라미의 조언</t>
+  </si>
+  <si>
+    <t>서큐버스를 찾아서 1</t>
+  </si>
+  <si>
+    <t>서큐버스를 찾아서 2</t>
+  </si>
+  <si>
+    <t>서큐버스 처치</t>
+  </si>
+  <si>
+    <t>서고로 이동</t>
+  </si>
+  <si>
+    <t>pf_Map_50077</t>
+  </si>
+  <si>
+    <t>단서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map_s4_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map_s4_002</t>
+  </si>
+  <si>
+    <t>map_s4_003</t>
+  </si>
+  <si>
+    <t>map_s4_004</t>
+  </si>
+  <si>
+    <t>map_s4_005</t>
+  </si>
+  <si>
+    <t>map_s4_006</t>
+  </si>
+  <si>
+    <t>map_s4_007</t>
+  </si>
+  <si>
+    <t>map_s4_008</t>
+  </si>
+  <si>
+    <t>map_s4_009</t>
+  </si>
+  <si>
+    <t>map_s4_010</t>
+  </si>
+  <si>
+    <t>map_s4_011</t>
+  </si>
+  <si>
+    <t>map_s4_012</t>
+  </si>
+  <si>
+    <t>map_s4_013</t>
+  </si>
+  <si>
+    <t>map_s4_014</t>
+  </si>
+  <si>
+    <t>map_s4_015</t>
+  </si>
+  <si>
+    <t>map_s4_016</t>
+  </si>
+  <si>
+    <t>map_s4_017</t>
+  </si>
+  <si>
+    <t>map_s4_018</t>
+  </si>
+  <si>
+    <t>map_s4_019</t>
+  </si>
+  <si>
+    <t>map_s4_020</t>
+  </si>
+  <si>
+    <t>map_s4_021</t>
+  </si>
+  <si>
+    <t>map_s4_022</t>
+  </si>
+  <si>
+    <t>map_s4_023</t>
+  </si>
+  <si>
+    <t>map_s4_024</t>
+  </si>
+  <si>
+    <t>map_s4_025</t>
+  </si>
+  <si>
+    <t>Move</t>
+  </si>
+  <si>
+    <t>bgm_41</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm_42</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm_43</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동굴 1층</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map_s4_026</t>
+  </si>
+  <si>
+    <t>pf_Map_50078</t>
+  </si>
+  <si>
+    <t>icon_map_0023</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0026</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0033</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0034</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0035</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0036</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0037</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map_s4_027</t>
+  </si>
+  <si>
+    <t>pf_Map_50079</t>
+  </si>
+  <si>
+    <t>QuestTalk</t>
+  </si>
+  <si>
+    <t>QuestTalk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QuestMob</t>
+  </si>
+  <si>
+    <t>QuestMob</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm_44</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0016</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0017</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0029</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리바이의 서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>img_map_0023</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>img_map_0024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>img_map_0026</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>img_map_0033</t>
-  </si>
-  <si>
-    <t>pf_Map_50065</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>img_map_0034</t>
-  </si>
-  <si>
-    <t>pf_Map_50066</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>img_map_0035</t>
-  </si>
-  <si>
-    <t>pf_Map_50067</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>img_map_0036</t>
-  </si>
-  <si>
-    <t>pf_Map_50068</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>img_map_0037</t>
-  </si>
-  <si>
-    <t>pf_Map_50069</t>
-  </si>
-  <si>
-    <t>img_map_0038</t>
-  </si>
-  <si>
-    <t>pf_Map_50070</t>
-  </si>
-  <si>
-    <t>img_map_0039</t>
-  </si>
-  <si>
-    <t>pf_Map_50071</t>
-  </si>
-  <si>
-    <t>img_map_0040</t>
-  </si>
-  <si>
-    <t>pf_Map_50072</t>
-  </si>
-  <si>
-    <t>img_map_0041</t>
-  </si>
-  <si>
-    <t>pf_Map_50073</t>
-  </si>
-  <si>
-    <t>img_map_0042</t>
-  </si>
-  <si>
-    <t>pf_Map_50074</t>
-  </si>
-  <si>
-    <t>img_map_0043</t>
-  </si>
-  <si>
-    <t>pf_Map_50075</t>
-  </si>
-  <si>
-    <t>img_map_0044</t>
-  </si>
-  <si>
-    <t>pf_Map_50076</t>
-  </si>
-  <si>
-    <t>img_map_0045</t>
-  </si>
-  <si>
-    <t>욕심</t>
-  </si>
-  <si>
-    <t>죽은 자의 동굴  1층</t>
-  </si>
-  <si>
-    <t>좀비 조심</t>
-  </si>
-  <si>
-    <t>박쥐 사냥</t>
-  </si>
-  <si>
-    <t>좀비방</t>
-  </si>
-  <si>
-    <t>숨겨진 방으로</t>
-  </si>
-  <si>
-    <t>보물방</t>
-  </si>
-  <si>
-    <t>믿음</t>
-  </si>
-  <si>
-    <t>만족</t>
-  </si>
-  <si>
-    <t>지하 2층으로</t>
-  </si>
-  <si>
-    <t>죽은 자의 동굴 2층</t>
-  </si>
-  <si>
-    <t>구울 조심</t>
-  </si>
-  <si>
-    <t>함정 1</t>
-  </si>
-  <si>
-    <t>구울방</t>
-  </si>
-  <si>
-    <t>함정 2</t>
-  </si>
-  <si>
-    <t>라미를 찾아서</t>
-  </si>
-  <si>
-    <t>라미의 부탁</t>
-  </si>
-  <si>
-    <t>좀비의 영혼</t>
-  </si>
-  <si>
-    <t>라미에게 줄 선물</t>
-  </si>
-  <si>
-    <t>라미의 조언</t>
-  </si>
-  <si>
-    <t>서큐버스를 찾아서 1</t>
-  </si>
-  <si>
-    <t>서큐버스를 찾아서 2</t>
-  </si>
-  <si>
-    <t>서큐버스 처치</t>
-  </si>
-  <si>
-    <t>서고로 이동</t>
-  </si>
-  <si>
-    <t>pf_Map_50077</t>
-  </si>
-  <si>
-    <t>img_map_0046</t>
-  </si>
-  <si>
-    <t>단서</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>map_s4_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>map_s4_002</t>
-  </si>
-  <si>
-    <t>map_s4_003</t>
-  </si>
-  <si>
-    <t>map_s4_004</t>
-  </si>
-  <si>
-    <t>map_s4_005</t>
-  </si>
-  <si>
-    <t>map_s4_006</t>
-  </si>
-  <si>
-    <t>map_s4_007</t>
-  </si>
-  <si>
-    <t>map_s4_008</t>
-  </si>
-  <si>
-    <t>map_s4_009</t>
-  </si>
-  <si>
-    <t>map_s4_010</t>
-  </si>
-  <si>
-    <t>map_s4_011</t>
-  </si>
-  <si>
-    <t>map_s4_012</t>
-  </si>
-  <si>
-    <t>map_s4_013</t>
-  </si>
-  <si>
-    <t>map_s4_014</t>
-  </si>
-  <si>
-    <t>map_s4_015</t>
-  </si>
-  <si>
-    <t>map_s4_016</t>
-  </si>
-  <si>
-    <t>map_s4_017</t>
-  </si>
-  <si>
-    <t>map_s4_018</t>
-  </si>
-  <si>
-    <t>map_s4_019</t>
-  </si>
-  <si>
-    <t>map_s4_020</t>
-  </si>
-  <si>
-    <t>map_s4_021</t>
-  </si>
-  <si>
-    <t>map_s4_022</t>
-  </si>
-  <si>
-    <t>map_s4_023</t>
-  </si>
-  <si>
-    <t>map_s4_024</t>
-  </si>
-  <si>
-    <t>map_s4_025</t>
-  </si>
-  <si>
-    <t>Move</t>
-  </si>
-  <si>
-    <t>bgm_41</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bgm_42</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bgm_02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bgm_43</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>동굴 1층</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>map_s4_026</t>
-  </si>
-  <si>
-    <t>pf_Map_50078</t>
-  </si>
-  <si>
-    <t>icon_map_0023</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon_map_0024</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon_map_0026</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon_map_0033</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon_map_0034</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon_map_0035</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon_map_0036</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon_map_0037</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>map_s4_027</t>
-  </si>
-  <si>
-    <t>pf_Map_50079</t>
-  </si>
-  <si>
-    <t>bgm_41</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>비밀 서고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>QuestTalk</t>
-  </si>
-  <si>
-    <t>QuestTalk</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>QuestMob</t>
-  </si>
-  <si>
-    <t>QuestMob</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2056,7 +2062,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2172,6 +2178,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -8774,10 +8783,10 @@
         <v>103</v>
       </c>
       <c r="I47" s="34">
-        <v>8.8000000000000007</v>
+        <v>5.3</v>
       </c>
       <c r="J47" s="34">
-        <v>7.8000000000000007</v>
+        <v>4.3</v>
       </c>
       <c r="K47" s="34">
         <v>0</v>
@@ -8789,7 +8798,7 @@
         <v>91</v>
       </c>
       <c r="N47" s="34" t="s">
-        <v>333</v>
+        <v>297</v>
       </c>
       <c r="O47" s="36" t="s">
         <v>90</v>
@@ -8838,10 +8847,10 @@
         <v>130</v>
       </c>
       <c r="I48" s="34">
-        <v>8.8000000000000007</v>
+        <v>5.3</v>
       </c>
       <c r="J48" s="34">
-        <v>7.8000000000000007</v>
+        <v>4.3</v>
       </c>
       <c r="K48" s="34">
         <v>0</v>
@@ -8902,10 +8911,10 @@
         <v>130</v>
       </c>
       <c r="I49" s="34">
-        <v>8.8000000000000007</v>
+        <v>5.3</v>
       </c>
       <c r="J49" s="34">
-        <v>7.8000000000000007</v>
+        <v>4.3</v>
       </c>
       <c r="K49" s="34">
         <v>0</v>
@@ -8966,10 +8975,10 @@
         <v>130</v>
       </c>
       <c r="I50" s="34">
-        <v>8.8000000000000007</v>
+        <v>5.3</v>
       </c>
       <c r="J50" s="34">
-        <v>7.8000000000000007</v>
+        <v>4.3</v>
       </c>
       <c r="K50" s="34">
         <v>0</v>
@@ -9030,10 +9039,10 @@
         <v>103</v>
       </c>
       <c r="I51" s="34">
-        <v>8.8000000000000007</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="J51" s="34">
-        <v>7.8000000000000007</v>
+        <v>7.2</v>
       </c>
       <c r="K51" s="34">
         <v>0</v>
@@ -9094,10 +9103,10 @@
         <v>103</v>
       </c>
       <c r="I52" s="34">
-        <v>8.8000000000000007</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="J52" s="34">
-        <v>7.8000000000000007</v>
+        <v>7.2</v>
       </c>
       <c r="K52" s="34">
         <v>0</v>
@@ -9158,10 +9167,10 @@
         <v>103</v>
       </c>
       <c r="I53" s="34">
-        <v>8.8000000000000007</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="J53" s="34">
-        <v>7.8000000000000007</v>
+        <v>7.2</v>
       </c>
       <c r="K53" s="34">
         <v>0</v>
@@ -9222,10 +9231,10 @@
         <v>130</v>
       </c>
       <c r="I54" s="34">
-        <v>8.8000000000000007</v>
+        <v>7</v>
       </c>
       <c r="J54" s="34">
-        <v>7.8000000000000007</v>
+        <v>6</v>
       </c>
       <c r="K54" s="34">
         <v>0</v>
@@ -9263,10 +9272,10 @@
         <v>50053</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="C55" s="34" t="s">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="D55" s="34" t="str">
         <f t="shared" ref="D55:D79" si="30">"STR_"&amp;UPPER(C55)</f>
@@ -9283,13 +9292,13 @@
         <v>3</v>
       </c>
       <c r="H55" s="34" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="I55" s="34">
-        <v>8.8000000000000007</v>
+        <v>6.2</v>
       </c>
       <c r="J55" s="34">
-        <v>7.8000000000000007</v>
+        <v>5.2</v>
       </c>
       <c r="K55" s="34">
         <v>0</v>
@@ -9301,7 +9310,7 @@
         <v>337</v>
       </c>
       <c r="N55" s="34" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="O55" s="36" t="s">
         <v>338</v>
@@ -9313,7 +9322,7 @@
         <v>0</v>
       </c>
       <c r="R55" s="36" t="s">
-        <v>329</v>
+        <v>456</v>
       </c>
       <c r="S55" s="36" t="s">
         <v>41</v>
@@ -9322,10 +9331,10 @@
         <v>41</v>
       </c>
       <c r="U55" s="36" t="s">
-        <v>236</v>
+        <v>457</v>
       </c>
       <c r="V55" s="36" t="s">
-        <v>237</v>
+        <v>458</v>
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.3">
@@ -9333,10 +9342,10 @@
         <v>50054</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="C56" s="34" t="s">
-        <v>423</v>
+        <v>409</v>
       </c>
       <c r="D56" s="34" t="str">
         <f t="shared" si="30"/>
@@ -9353,13 +9362,13 @@
         <v>3</v>
       </c>
       <c r="H56" s="34" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="I56" s="34">
-        <v>8.8000000000000007</v>
+        <v>5.5</v>
       </c>
       <c r="J56" s="34">
-        <v>7.8000000000000007</v>
+        <v>4.5</v>
       </c>
       <c r="K56" s="34">
         <v>0</v>
@@ -9371,7 +9380,7 @@
         <v>340</v>
       </c>
       <c r="N56" s="34" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="O56" s="36" t="s">
         <v>341</v>
@@ -9383,7 +9392,7 @@
         <v>0</v>
       </c>
       <c r="R56" s="36" t="s">
-        <v>329</v>
+        <v>456</v>
       </c>
       <c r="S56" s="36" t="s">
         <v>41</v>
@@ -9392,10 +9401,10 @@
         <v>41</v>
       </c>
       <c r="U56" s="36" t="s">
-        <v>236</v>
+        <v>457</v>
       </c>
       <c r="V56" s="36" t="s">
-        <v>237</v>
+        <v>458</v>
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.3">
@@ -9403,10 +9412,10 @@
         <v>50055</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="C57" s="34" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="D57" s="34" t="str">
         <f t="shared" si="30"/>
@@ -9423,13 +9432,13 @@
         <v>3</v>
       </c>
       <c r="H57" s="34" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="I57" s="34">
-        <v>8.8000000000000007</v>
+        <v>3.8000000000000003</v>
       </c>
       <c r="J57" s="34">
-        <v>7.8000000000000007</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="K57" s="34">
         <v>0</v>
@@ -9441,7 +9450,7 @@
         <v>343</v>
       </c>
       <c r="N57" s="34" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="O57" s="36" t="s">
         <v>344</v>
@@ -9453,7 +9462,7 @@
         <v>0</v>
       </c>
       <c r="R57" s="36" t="s">
-        <v>329</v>
+        <v>456</v>
       </c>
       <c r="S57" s="36" t="s">
         <v>41</v>
@@ -9462,10 +9471,10 @@
         <v>41</v>
       </c>
       <c r="U57" s="36" t="s">
-        <v>236</v>
+        <v>457</v>
       </c>
       <c r="V57" s="36" t="s">
-        <v>237</v>
+        <v>458</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.3">
@@ -9473,10 +9482,10 @@
         <v>50056</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="C58" s="34" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="D58" s="34" t="str">
         <f t="shared" si="30"/>
@@ -9496,10 +9505,10 @@
         <v>134</v>
       </c>
       <c r="I58" s="34">
-        <v>8.8000000000000007</v>
+        <v>2.5</v>
       </c>
       <c r="J58" s="34">
-        <v>7.8000000000000007</v>
+        <v>1.5</v>
       </c>
       <c r="K58" s="34">
         <v>0</v>
@@ -9511,7 +9520,7 @@
         <v>346</v>
       </c>
       <c r="N58" s="34" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="O58" s="36" t="s">
         <v>347</v>
@@ -9523,7 +9532,7 @@
         <v>0</v>
       </c>
       <c r="R58" s="36" t="s">
-        <v>329</v>
+        <v>456</v>
       </c>
       <c r="S58" s="36" t="s">
         <v>41</v>
@@ -9532,10 +9541,10 @@
         <v>41</v>
       </c>
       <c r="U58" s="36" t="s">
-        <v>236</v>
+        <v>457</v>
       </c>
       <c r="V58" s="36" t="s">
-        <v>237</v>
+        <v>458</v>
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.3">
@@ -9543,10 +9552,10 @@
         <v>50057</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="C59" s="34" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="D59" s="34" t="str">
         <f t="shared" si="30"/>
@@ -9566,10 +9575,10 @@
         <v>134</v>
       </c>
       <c r="I59" s="34">
-        <v>8.8000000000000007</v>
+        <v>2.7</v>
       </c>
       <c r="J59" s="34">
-        <v>7.8000000000000007</v>
+        <v>1.7000000000000002</v>
       </c>
       <c r="K59" s="34">
         <v>0</v>
@@ -9581,7 +9590,7 @@
         <v>349</v>
       </c>
       <c r="N59" s="34" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="O59" s="36" t="s">
         <v>350</v>
@@ -9593,7 +9602,7 @@
         <v>0</v>
       </c>
       <c r="R59" s="36" t="s">
-        <v>329</v>
+        <v>456</v>
       </c>
       <c r="S59" s="36" t="s">
         <v>41</v>
@@ -9602,10 +9611,10 @@
         <v>41</v>
       </c>
       <c r="U59" s="36" t="s">
-        <v>236</v>
+        <v>457</v>
       </c>
       <c r="V59" s="36" t="s">
-        <v>237</v>
+        <v>458</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.3">
@@ -9613,10 +9622,10 @@
         <v>50058</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="C60" s="34" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="D60" s="34" t="str">
         <f t="shared" si="30"/>
@@ -9633,13 +9642,13 @@
         <v>3</v>
       </c>
       <c r="H60" s="34" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="I60" s="34">
-        <v>8.8000000000000007</v>
+        <v>7.7</v>
       </c>
       <c r="J60" s="34">
-        <v>7.8000000000000007</v>
+        <v>6.7</v>
       </c>
       <c r="K60" s="34">
         <v>0</v>
@@ -9651,7 +9660,7 @@
         <v>352</v>
       </c>
       <c r="N60" s="34" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="O60" s="36" t="s">
         <v>353</v>
@@ -9663,7 +9672,7 @@
         <v>0</v>
       </c>
       <c r="R60" s="36" t="s">
-        <v>329</v>
+        <v>456</v>
       </c>
       <c r="S60" s="36" t="s">
         <v>41</v>
@@ -9672,10 +9681,10 @@
         <v>41</v>
       </c>
       <c r="U60" s="36" t="s">
-        <v>236</v>
+        <v>457</v>
       </c>
       <c r="V60" s="36" t="s">
-        <v>237</v>
+        <v>458</v>
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.3">
@@ -9683,10 +9692,10 @@
         <v>50059</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="C61" s="34" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="D61" s="34" t="str">
         <f t="shared" si="30"/>
@@ -9706,10 +9715,10 @@
         <v>179</v>
       </c>
       <c r="I61" s="34">
-        <v>8.8000000000000007</v>
+        <v>1</v>
       </c>
       <c r="J61" s="34">
-        <v>7.8000000000000007</v>
+        <v>10</v>
       </c>
       <c r="K61" s="34">
         <v>0</v>
@@ -9721,7 +9730,7 @@
         <v>355</v>
       </c>
       <c r="N61" s="34" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="O61" s="36" t="s">
         <v>356</v>
@@ -9733,7 +9742,7 @@
         <v>0</v>
       </c>
       <c r="R61" s="36" t="s">
-        <v>329</v>
+        <v>456</v>
       </c>
       <c r="S61" s="36" t="s">
         <v>41</v>
@@ -9742,10 +9751,10 @@
         <v>41</v>
       </c>
       <c r="U61" s="36" t="s">
-        <v>236</v>
+        <v>457</v>
       </c>
       <c r="V61" s="36" t="s">
-        <v>237</v>
+        <v>458</v>
       </c>
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.3">
@@ -9753,10 +9762,10 @@
         <v>50060</v>
       </c>
       <c r="B62" s="36" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="C62" s="34" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="D62" s="34" t="str">
         <f t="shared" ref="D62" si="32">"STR_"&amp;UPPER(C62)</f>
@@ -9773,13 +9782,13 @@
         <v>3</v>
       </c>
       <c r="H62" s="34" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="I62" s="34">
-        <v>8.8000000000000007</v>
+        <v>8.4</v>
       </c>
       <c r="J62" s="34">
-        <v>7.8000000000000007</v>
+        <v>7.4</v>
       </c>
       <c r="K62" s="34">
         <v>0</v>
@@ -9791,7 +9800,7 @@
         <v>352</v>
       </c>
       <c r="N62" s="34" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="O62" s="36" t="s">
         <v>353</v>
@@ -9803,7 +9812,7 @@
         <v>0</v>
       </c>
       <c r="R62" s="36" t="s">
-        <v>329</v>
+        <v>456</v>
       </c>
       <c r="S62" s="36" t="s">
         <v>41</v>
@@ -9812,10 +9821,10 @@
         <v>41</v>
       </c>
       <c r="U62" s="36" t="s">
-        <v>236</v>
+        <v>457</v>
       </c>
       <c r="V62" s="36" t="s">
-        <v>237</v>
+        <v>458</v>
       </c>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.3">
@@ -9823,10 +9832,10 @@
         <v>50061</v>
       </c>
       <c r="B63" s="36" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="C63" s="34" t="s">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="D63" s="34" t="str">
         <f t="shared" si="30"/>
@@ -9843,13 +9852,13 @@
         <v>3</v>
       </c>
       <c r="H63" s="34" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="I63" s="34">
-        <v>8.8000000000000007</v>
+        <v>8.4</v>
       </c>
       <c r="J63" s="34">
-        <v>7.8000000000000007</v>
+        <v>7.4</v>
       </c>
       <c r="K63" s="34">
         <v>0</v>
@@ -9861,7 +9870,7 @@
         <v>358</v>
       </c>
       <c r="N63" s="34" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="O63" s="36" t="s">
         <v>359</v>
@@ -9873,7 +9882,7 @@
         <v>0</v>
       </c>
       <c r="R63" s="36" t="s">
-        <v>329</v>
+        <v>456</v>
       </c>
       <c r="S63" s="36" t="s">
         <v>41</v>
@@ -9882,10 +9891,10 @@
         <v>41</v>
       </c>
       <c r="U63" s="36" t="s">
-        <v>236</v>
+        <v>457</v>
       </c>
       <c r="V63" s="36" t="s">
-        <v>237</v>
+        <v>458</v>
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.3">
@@ -9893,10 +9902,10 @@
         <v>50062</v>
       </c>
       <c r="B64" s="36" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="C64" s="34" t="s">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="D64" s="34" t="str">
         <f t="shared" si="30"/>
@@ -9913,13 +9922,13 @@
         <v>3</v>
       </c>
       <c r="H64" s="34" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="I64" s="34">
-        <v>8.8000000000000007</v>
+        <v>6.7</v>
       </c>
       <c r="J64" s="34">
-        <v>7.8000000000000007</v>
+        <v>5.7</v>
       </c>
       <c r="K64" s="34">
         <v>0</v>
@@ -9931,7 +9940,7 @@
         <v>361</v>
       </c>
       <c r="N64" s="34" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="O64" s="36" t="s">
         <v>362</v>
@@ -9943,7 +9952,7 @@
         <v>0</v>
       </c>
       <c r="R64" s="36" t="s">
-        <v>329</v>
+        <v>456</v>
       </c>
       <c r="S64" s="36" t="s">
         <v>41</v>
@@ -9952,10 +9961,10 @@
         <v>41</v>
       </c>
       <c r="U64" s="36" t="s">
-        <v>236</v>
+        <v>457</v>
       </c>
       <c r="V64" s="36" t="s">
-        <v>237</v>
+        <v>458</v>
       </c>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.3">
@@ -9963,10 +9972,10 @@
         <v>50063</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="C65" s="34" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
       <c r="D65" s="34" t="str">
         <f t="shared" si="30"/>
@@ -9983,13 +9992,13 @@
         <v>3</v>
       </c>
       <c r="H65" s="34" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="I65" s="34">
-        <v>8.8000000000000007</v>
+        <v>6.2</v>
       </c>
       <c r="J65" s="34">
-        <v>7.8000000000000007</v>
+        <v>5.2</v>
       </c>
       <c r="K65" s="34">
         <v>0</v>
@@ -10001,7 +10010,7 @@
         <v>364</v>
       </c>
       <c r="N65" s="34" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="O65" s="36" t="s">
         <v>365</v>
@@ -10013,7 +10022,7 @@
         <v>0</v>
       </c>
       <c r="R65" s="36" t="s">
-        <v>329</v>
+        <v>456</v>
       </c>
       <c r="S65" s="36" t="s">
         <v>41</v>
@@ -10022,10 +10031,10 @@
         <v>41</v>
       </c>
       <c r="U65" s="36" t="s">
-        <v>236</v>
+        <v>457</v>
       </c>
       <c r="V65" s="36" t="s">
-        <v>237</v>
+        <v>458</v>
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.3">
@@ -10033,10 +10042,10 @@
         <v>50064</v>
       </c>
       <c r="B66" s="36" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="C66" s="34" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="D66" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10053,13 +10062,13 @@
         <v>3</v>
       </c>
       <c r="H66" s="34" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="I66" s="34">
-        <v>8.8000000000000007</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="J66" s="34">
-        <v>7.8000000000000007</v>
+        <v>3.6</v>
       </c>
       <c r="K66" s="34">
         <v>0</v>
@@ -10071,7 +10080,7 @@
         <v>367</v>
       </c>
       <c r="N66" s="34" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="O66" s="36" t="s">
         <v>368</v>
@@ -10083,7 +10092,7 @@
         <v>0</v>
       </c>
       <c r="R66" s="36" t="s">
-        <v>329</v>
+        <v>456</v>
       </c>
       <c r="S66" s="36" t="s">
         <v>41</v>
@@ -10092,10 +10101,10 @@
         <v>41</v>
       </c>
       <c r="U66" s="36" t="s">
-        <v>236</v>
+        <v>457</v>
       </c>
       <c r="V66" s="36" t="s">
-        <v>237</v>
+        <v>458</v>
       </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.3">
@@ -10103,10 +10112,10 @@
         <v>50065</v>
       </c>
       <c r="B67" s="36" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="C67" s="34" t="s">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="D67" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10123,28 +10132,28 @@
         <v>3</v>
       </c>
       <c r="H67" s="34" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="I67" s="34">
-        <v>8.8000000000000007</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="J67" s="34">
-        <v>7.8000000000000007</v>
+        <v>3.8000000000000003</v>
       </c>
       <c r="K67" s="34">
         <v>0</v>
       </c>
       <c r="L67" s="34" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="M67" s="34" t="s">
-        <v>370</v>
+        <v>461</v>
       </c>
       <c r="N67" s="34" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="O67" s="36" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="P67" s="36">
         <v>1</v>
@@ -10153,7 +10162,7 @@
         <v>0</v>
       </c>
       <c r="R67" s="36" t="s">
-        <v>329</v>
+        <v>456</v>
       </c>
       <c r="S67" s="36" t="s">
         <v>41</v>
@@ -10162,10 +10171,10 @@
         <v>41</v>
       </c>
       <c r="U67" s="36" t="s">
-        <v>236</v>
+        <v>457</v>
       </c>
       <c r="V67" s="36" t="s">
-        <v>237</v>
+        <v>458</v>
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.3">
@@ -10173,10 +10182,10 @@
         <v>50066</v>
       </c>
       <c r="B68" s="36" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="C68" s="34" t="s">
-        <v>435</v>
+        <v>421</v>
       </c>
       <c r="D68" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10193,38 +10202,38 @@
         <v>3</v>
       </c>
       <c r="H68" s="34" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="I68" s="34">
-        <v>8.8000000000000007</v>
+        <v>6.8000000000000007</v>
       </c>
       <c r="J68" s="34">
-        <v>7.8000000000000007</v>
+        <v>5.8000000000000007</v>
       </c>
       <c r="K68" s="34">
         <v>0</v>
       </c>
       <c r="L68" s="34" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="M68" s="34" t="s">
-        <v>372</v>
+        <v>462</v>
       </c>
       <c r="N68" s="34" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="O68" s="36" t="s">
+        <v>442</v>
+      </c>
+      <c r="P68" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q68" s="34">
+        <v>0</v>
+      </c>
+      <c r="R68" s="36" t="s">
         <v>456</v>
       </c>
-      <c r="P68" s="36">
-        <v>1</v>
-      </c>
-      <c r="Q68" s="34">
-        <v>0</v>
-      </c>
-      <c r="R68" s="36" t="s">
-        <v>329</v>
-      </c>
       <c r="S68" s="36" t="s">
         <v>41</v>
       </c>
@@ -10232,10 +10241,10 @@
         <v>41</v>
       </c>
       <c r="U68" s="36" t="s">
-        <v>236</v>
+        <v>457</v>
       </c>
       <c r="V68" s="36" t="s">
-        <v>237</v>
+        <v>458</v>
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.3">
@@ -10243,10 +10252,10 @@
         <v>50067</v>
       </c>
       <c r="B69" s="36" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="C69" s="34" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="D69" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10266,46 +10275,46 @@
         <v>134</v>
       </c>
       <c r="I69" s="34">
-        <v>8.8000000000000007</v>
+        <v>2.7</v>
       </c>
       <c r="J69" s="34">
-        <v>7.8000000000000007</v>
+        <v>1.7000000000000002</v>
       </c>
       <c r="K69" s="34">
         <v>0</v>
       </c>
       <c r="L69" s="34" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="M69" s="34" t="s">
-        <v>374</v>
+        <v>463</v>
       </c>
       <c r="N69" s="34" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="O69" s="36" t="s">
+        <v>443</v>
+      </c>
+      <c r="P69" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q69" s="34">
+        <v>0</v>
+      </c>
+      <c r="R69" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="S69" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T69" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U69" s="36" t="s">
         <v>457</v>
       </c>
-      <c r="P69" s="36">
-        <v>1</v>
-      </c>
-      <c r="Q69" s="34">
-        <v>0</v>
-      </c>
-      <c r="R69" s="36" t="s">
-        <v>329</v>
-      </c>
-      <c r="S69" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="T69" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="U69" s="36" t="s">
-        <v>236</v>
-      </c>
       <c r="V69" s="36" t="s">
-        <v>237</v>
+        <v>458</v>
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.3">
@@ -10313,10 +10322,10 @@
         <v>50068</v>
       </c>
       <c r="B70" s="36" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="C70" s="34" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="D70" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10333,60 +10342,60 @@
         <v>3</v>
       </c>
       <c r="H70" s="34" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="I70" s="34">
-        <v>8.8000000000000007</v>
+        <v>5.8000000000000007</v>
       </c>
       <c r="J70" s="34">
-        <v>7.8000000000000007</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="K70" s="34">
         <v>0</v>
       </c>
       <c r="L70" s="34" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M70" s="34" t="s">
-        <v>376</v>
+        <v>464</v>
       </c>
       <c r="N70" s="34" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="O70" s="36" t="s">
+        <v>444</v>
+      </c>
+      <c r="P70" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q70" s="34">
+        <v>0</v>
+      </c>
+      <c r="R70" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="S70" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T70" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U70" s="36" t="s">
+        <v>457</v>
+      </c>
+      <c r="V70" s="36" t="s">
         <v>458</v>
       </c>
-      <c r="P70" s="36">
-        <v>1</v>
-      </c>
-      <c r="Q70" s="34">
-        <v>0</v>
-      </c>
-      <c r="R70" s="36" t="s">
-        <v>329</v>
-      </c>
-      <c r="S70" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="T70" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="U70" s="36" t="s">
-        <v>236</v>
-      </c>
-      <c r="V70" s="36" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:22" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="34">
         <v>50069</v>
       </c>
-      <c r="B71" s="36" t="s">
-        <v>410</v>
+      <c r="B71" s="34" t="s">
+        <v>397</v>
       </c>
       <c r="C71" s="34" t="s">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c r="D71" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10406,57 +10415,53 @@
         <v>130</v>
       </c>
       <c r="I71" s="34">
-        <v>8.8000000000000007</v>
+        <v>7.4</v>
       </c>
       <c r="J71" s="34">
-        <v>7.8000000000000007</v>
+        <v>6.4</v>
       </c>
       <c r="K71" s="34">
         <v>0</v>
       </c>
       <c r="L71" s="34" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="M71" s="34" t="s">
-        <v>378</v>
+        <v>465</v>
       </c>
       <c r="N71" s="34" t="s">
-        <v>451</v>
-      </c>
-      <c r="O71" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="P71" s="36">
+        <v>437</v>
+      </c>
+      <c r="O71" s="34" t="s">
+        <v>445</v>
+      </c>
+      <c r="P71" s="34">
         <v>1</v>
       </c>
       <c r="Q71" s="34">
         <v>0</v>
       </c>
-      <c r="R71" s="36" t="s">
-        <v>329</v>
-      </c>
-      <c r="S71" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="T71" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="U71" s="36" t="s">
-        <v>236</v>
-      </c>
-      <c r="V71" s="36" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="R71" s="34" t="s">
+        <v>456</v>
+      </c>
+      <c r="S71" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="T71" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="U71" s="34"/>
+      <c r="V71" s="34"/>
+    </row>
+    <row r="72" spans="1:22" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="34">
         <v>50070</v>
       </c>
-      <c r="B72" s="36" t="s">
-        <v>411</v>
+      <c r="B72" s="34" t="s">
+        <v>398</v>
       </c>
       <c r="C72" s="34" t="s">
-        <v>439</v>
+        <v>425</v>
       </c>
       <c r="D72" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10476,57 +10481,53 @@
         <v>130</v>
       </c>
       <c r="I72" s="34">
-        <v>8.8000000000000007</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="J72" s="34">
-        <v>7.8000000000000007</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="K72" s="34">
         <v>0</v>
       </c>
       <c r="L72" s="34" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="M72" s="34" t="s">
-        <v>380</v>
+        <v>465</v>
       </c>
       <c r="N72" s="34" t="s">
-        <v>451</v>
-      </c>
-      <c r="O72" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="P72" s="36">
+        <v>437</v>
+      </c>
+      <c r="O72" s="34" t="s">
+        <v>445</v>
+      </c>
+      <c r="P72" s="34">
         <v>1</v>
       </c>
       <c r="Q72" s="34">
         <v>0</v>
       </c>
-      <c r="R72" s="36" t="s">
-        <v>329</v>
-      </c>
-      <c r="S72" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="T72" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="U72" s="36" t="s">
-        <v>236</v>
-      </c>
-      <c r="V72" s="36" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="R72" s="34" t="s">
+        <v>456</v>
+      </c>
+      <c r="S72" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="T72" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="U72" s="34"/>
+      <c r="V72" s="34"/>
+    </row>
+    <row r="73" spans="1:22" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="34">
         <v>50071</v>
       </c>
-      <c r="B73" s="36" t="s">
-        <v>412</v>
+      <c r="B73" s="34" t="s">
+        <v>399</v>
       </c>
       <c r="C73" s="34" t="s">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="D73" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10543,60 +10544,60 @@
         <v>3</v>
       </c>
       <c r="H73" s="34" t="s">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="I73" s="34">
-        <v>8.8000000000000007</v>
+        <v>6</v>
       </c>
       <c r="J73" s="34">
-        <v>7.8000000000000007</v>
+        <v>5</v>
       </c>
       <c r="K73" s="34">
         <v>0</v>
       </c>
       <c r="L73" s="34" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="M73" s="34" t="s">
-        <v>382</v>
+        <v>466</v>
       </c>
       <c r="N73" s="34" t="s">
-        <v>449</v>
-      </c>
-      <c r="O73" s="36" t="s">
-        <v>460</v>
-      </c>
-      <c r="P73" s="36">
+        <v>435</v>
+      </c>
+      <c r="O73" s="34" t="s">
+        <v>446</v>
+      </c>
+      <c r="P73" s="34">
         <v>1</v>
       </c>
       <c r="Q73" s="34">
         <v>0</v>
       </c>
-      <c r="R73" s="36" t="s">
-        <v>329</v>
-      </c>
-      <c r="S73" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="T73" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="U73" s="36" t="s">
-        <v>236</v>
-      </c>
-      <c r="V73" s="36" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="R73" s="34" t="s">
+        <v>456</v>
+      </c>
+      <c r="S73" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="T73" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="U73" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="V73" s="34" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="34">
         <v>50072</v>
       </c>
-      <c r="B74" s="36" t="s">
-        <v>413</v>
+      <c r="B74" s="34" t="s">
+        <v>400</v>
       </c>
       <c r="C74" s="34" t="s">
-        <v>441</v>
+        <v>427</v>
       </c>
       <c r="D74" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10613,60 +10614,56 @@
         <v>3</v>
       </c>
       <c r="H74" s="34" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="I74" s="34">
-        <v>8.8000000000000007</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="J74" s="34">
-        <v>7.8000000000000007</v>
+        <v>7.7</v>
       </c>
       <c r="K74" s="34">
         <v>0</v>
       </c>
       <c r="L74" s="34" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="M74" s="34" t="s">
-        <v>384</v>
+        <v>465</v>
       </c>
       <c r="N74" s="34" t="s">
-        <v>451</v>
-      </c>
-      <c r="O74" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="P74" s="36">
+        <v>437</v>
+      </c>
+      <c r="O74" s="34" t="s">
+        <v>445</v>
+      </c>
+      <c r="P74" s="34">
         <v>1</v>
       </c>
       <c r="Q74" s="34">
         <v>0</v>
       </c>
-      <c r="R74" s="36" t="s">
-        <v>329</v>
-      </c>
-      <c r="S74" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="T74" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="U74" s="36" t="s">
-        <v>236</v>
-      </c>
-      <c r="V74" s="36" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="R74" s="34" t="s">
+        <v>456</v>
+      </c>
+      <c r="S74" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="T74" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="U74" s="34"/>
+      <c r="V74" s="34"/>
+    </row>
+    <row r="75" spans="1:22" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="34">
         <v>50073</v>
       </c>
-      <c r="B75" s="36" t="s">
-        <v>414</v>
+      <c r="B75" s="34" t="s">
+        <v>401</v>
       </c>
       <c r="C75" s="34" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="D75" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10686,57 +10683,53 @@
         <v>130</v>
       </c>
       <c r="I75" s="34">
-        <v>8.8000000000000007</v>
+        <v>9.1</v>
       </c>
       <c r="J75" s="34">
-        <v>7.8000000000000007</v>
+        <v>8.1</v>
       </c>
       <c r="K75" s="34">
         <v>0</v>
       </c>
       <c r="L75" s="34" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="M75" s="34" t="s">
-        <v>386</v>
+        <v>465</v>
       </c>
       <c r="N75" s="34" t="s">
-        <v>451</v>
-      </c>
-      <c r="O75" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="P75" s="36">
+        <v>437</v>
+      </c>
+      <c r="O75" s="34" t="s">
+        <v>445</v>
+      </c>
+      <c r="P75" s="34">
         <v>1</v>
       </c>
       <c r="Q75" s="34">
         <v>0</v>
       </c>
-      <c r="R75" s="36" t="s">
-        <v>329</v>
-      </c>
-      <c r="S75" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="T75" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="U75" s="36" t="s">
-        <v>236</v>
-      </c>
-      <c r="V75" s="36" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="R75" s="34" t="s">
+        <v>456</v>
+      </c>
+      <c r="S75" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="T75" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="U75" s="34"/>
+      <c r="V75" s="34"/>
+    </row>
+    <row r="76" spans="1:22" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="34">
         <v>50074</v>
       </c>
-      <c r="B76" s="36" t="s">
-        <v>415</v>
+      <c r="B76" s="34" t="s">
+        <v>402</v>
       </c>
       <c r="C76" s="34" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="D76" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10753,60 +10746,60 @@
         <v>3</v>
       </c>
       <c r="H76" s="34" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="I76" s="34">
-        <v>8.8000000000000007</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="J76" s="34">
-        <v>7.8000000000000007</v>
+        <v>3.8000000000000003</v>
       </c>
       <c r="K76" s="34">
         <v>0</v>
       </c>
       <c r="L76" s="34" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="M76" s="34" t="s">
-        <v>388</v>
+        <v>466</v>
       </c>
       <c r="N76" s="34" t="s">
-        <v>448</v>
-      </c>
-      <c r="O76" s="36" t="s">
-        <v>460</v>
-      </c>
-      <c r="P76" s="36">
+        <v>434</v>
+      </c>
+      <c r="O76" s="34" t="s">
+        <v>446</v>
+      </c>
+      <c r="P76" s="34">
         <v>1</v>
       </c>
       <c r="Q76" s="34">
         <v>0</v>
       </c>
-      <c r="R76" s="36" t="s">
-        <v>329</v>
-      </c>
-      <c r="S76" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="T76" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="U76" s="36" t="s">
-        <v>236</v>
-      </c>
-      <c r="V76" s="36" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="R76" s="34" t="s">
+        <v>456</v>
+      </c>
+      <c r="S76" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="T76" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="U76" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="V76" s="34" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="34">
         <v>50075</v>
       </c>
-      <c r="B77" s="36" t="s">
-        <v>416</v>
+      <c r="B77" s="34" t="s">
+        <v>403</v>
       </c>
       <c r="C77" s="34" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="D77" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10823,60 +10816,60 @@
         <v>3</v>
       </c>
       <c r="H77" s="34" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="I77" s="34">
-        <v>8.8000000000000007</v>
+        <v>3.4000000000000004</v>
       </c>
       <c r="J77" s="34">
-        <v>7.8000000000000007</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="K77" s="34">
         <v>0</v>
       </c>
       <c r="L77" s="34" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="M77" s="34" t="s">
-        <v>390</v>
+        <v>466</v>
       </c>
       <c r="N77" s="34" t="s">
-        <v>448</v>
-      </c>
-      <c r="O77" s="36" t="s">
-        <v>460</v>
-      </c>
-      <c r="P77" s="36">
+        <v>434</v>
+      </c>
+      <c r="O77" s="34" t="s">
+        <v>446</v>
+      </c>
+      <c r="P77" s="34">
         <v>1</v>
       </c>
       <c r="Q77" s="34">
         <v>0</v>
       </c>
-      <c r="R77" s="36" t="s">
-        <v>329</v>
-      </c>
-      <c r="S77" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="T77" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="U77" s="36" t="s">
-        <v>236</v>
-      </c>
-      <c r="V77" s="36" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="R77" s="34" t="s">
+        <v>456</v>
+      </c>
+      <c r="S77" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="T77" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="U77" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="V77" s="34" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="34">
         <v>50076</v>
       </c>
-      <c r="B78" s="36" t="s">
-        <v>417</v>
+      <c r="B78" s="34" t="s">
+        <v>404</v>
       </c>
       <c r="C78" s="34" t="s">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="D78" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10896,57 +10889,57 @@
         <v>134</v>
       </c>
       <c r="I78" s="34">
-        <v>8.8000000000000007</v>
+        <v>2.7</v>
       </c>
       <c r="J78" s="34">
-        <v>7.8000000000000007</v>
+        <v>1.7000000000000002</v>
       </c>
       <c r="K78" s="34">
         <v>0</v>
       </c>
       <c r="L78" s="34" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="M78" s="34" t="s">
-        <v>392</v>
+        <v>467</v>
       </c>
       <c r="N78" s="34" t="s">
-        <v>449</v>
-      </c>
-      <c r="O78" s="36" t="s">
-        <v>461</v>
-      </c>
-      <c r="P78" s="36">
+        <v>455</v>
+      </c>
+      <c r="O78" s="34" t="s">
+        <v>447</v>
+      </c>
+      <c r="P78" s="34">
         <v>1</v>
       </c>
       <c r="Q78" s="34">
         <v>0</v>
       </c>
-      <c r="R78" s="36" t="s">
-        <v>329</v>
-      </c>
-      <c r="S78" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="T78" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="U78" s="36" t="s">
-        <v>236</v>
-      </c>
-      <c r="V78" s="36" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="R78" s="34" t="s">
+        <v>456</v>
+      </c>
+      <c r="S78" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="T78" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="U78" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="V78" s="34" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A79" s="34">
         <v>50077</v>
       </c>
-      <c r="B79" s="36" t="s">
-        <v>418</v>
+      <c r="B79" s="34" t="s">
+        <v>405</v>
       </c>
       <c r="C79" s="34" t="s">
-        <v>446</v>
+        <v>432</v>
       </c>
       <c r="D79" s="34" t="str">
         <f t="shared" si="30"/>
@@ -10963,60 +10956,60 @@
         <v>3</v>
       </c>
       <c r="H79" s="34" t="s">
+        <v>433</v>
+      </c>
+      <c r="I79" s="34">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J79" s="34">
+        <v>3.9000000000000004</v>
+      </c>
+      <c r="K79" s="34">
+        <v>0</v>
+      </c>
+      <c r="L79" s="34" t="s">
+        <v>406</v>
+      </c>
+      <c r="M79" s="34" t="s">
+        <v>467</v>
+      </c>
+      <c r="N79" s="34" t="s">
+        <v>434</v>
+      </c>
+      <c r="O79" s="34" t="s">
         <v>447</v>
       </c>
-      <c r="I79" s="34">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="J79" s="34">
-        <v>7.8000000000000007</v>
-      </c>
-      <c r="K79" s="34">
-        <v>0</v>
-      </c>
-      <c r="L79" s="34" t="s">
-        <v>419</v>
-      </c>
-      <c r="M79" s="34" t="s">
-        <v>394</v>
-      </c>
-      <c r="N79" s="34" t="s">
-        <v>448</v>
-      </c>
-      <c r="O79" s="36" t="s">
-        <v>461</v>
-      </c>
-      <c r="P79" s="36">
+      <c r="P79" s="34">
         <v>1</v>
       </c>
       <c r="Q79" s="34">
         <v>0</v>
       </c>
-      <c r="R79" s="36" t="s">
-        <v>329</v>
-      </c>
-      <c r="S79" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="T79" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="U79" s="36" t="s">
-        <v>236</v>
-      </c>
-      <c r="V79" s="36" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="R79" s="34" t="s">
+        <v>456</v>
+      </c>
+      <c r="S79" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="T79" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="U79" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="V79" s="34" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A80" s="34">
         <v>50078</v>
       </c>
-      <c r="B80" s="36" t="s">
-        <v>466</v>
+      <c r="B80" t="s">
+        <v>407</v>
       </c>
       <c r="C80" s="34" t="s">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="D80" s="34" t="str">
         <f t="shared" ref="D80" si="34">"STR_"&amp;UPPER(C80)</f>
@@ -11033,54 +11026,60 @@
         <v>3</v>
       </c>
       <c r="H80" s="34" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="I80" s="34">
-        <v>8.8000000000000007</v>
+        <v>9.4</v>
       </c>
       <c r="J80" s="34">
-        <v>7.8000000000000007</v>
+        <v>8.4</v>
       </c>
       <c r="K80" s="34">
         <v>0</v>
       </c>
       <c r="L80" s="34" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="M80" s="34" t="s">
-        <v>420</v>
+        <v>468</v>
       </c>
       <c r="N80" s="34" t="s">
-        <v>465</v>
-      </c>
-      <c r="O80" s="36" t="s">
-        <v>462</v>
-      </c>
-      <c r="P80" s="36">
+        <v>437</v>
+      </c>
+      <c r="O80" s="34" t="s">
+        <v>448</v>
+      </c>
+      <c r="P80" s="34">
         <v>1</v>
       </c>
       <c r="Q80" s="34">
         <v>0</v>
       </c>
-      <c r="R80" s="36" t="s">
-        <v>329</v>
-      </c>
-      <c r="U80" s="36" t="s">
-        <v>236</v>
-      </c>
-      <c r="V80" s="36" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="R80" s="34" t="s">
+        <v>456</v>
+      </c>
+      <c r="S80" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="T80" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="U80" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="V80" s="34" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A81" s="34">
         <v>50079</v>
       </c>
-      <c r="B81" s="36" t="s">
-        <v>421</v>
+      <c r="B81" t="s">
+        <v>460</v>
       </c>
       <c r="C81" s="34" t="s">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="D81" s="34" t="str">
         <f t="shared" ref="D81" si="36">"STR_"&amp;UPPER(C81)</f>
@@ -11100,41 +11099,43 @@
         <v>130</v>
       </c>
       <c r="I81" s="34">
-        <v>8.8000000000000007</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="J81" s="34">
-        <v>7.8000000000000007</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="K81" s="34">
         <v>0</v>
       </c>
       <c r="L81" s="34" t="s">
-        <v>464</v>
+        <v>450</v>
       </c>
       <c r="M81" s="34" t="s">
-        <v>420</v>
+        <v>468</v>
       </c>
       <c r="N81" s="34" t="s">
-        <v>451</v>
-      </c>
-      <c r="O81" s="36" t="s">
-        <v>462</v>
-      </c>
-      <c r="P81" s="36">
+        <v>437</v>
+      </c>
+      <c r="O81" s="34" t="s">
+        <v>448</v>
+      </c>
+      <c r="P81" s="34">
         <v>1</v>
       </c>
       <c r="Q81" s="34">
         <v>0</v>
       </c>
-      <c r="R81" s="36" t="s">
-        <v>329</v>
-      </c>
-      <c r="U81" s="36" t="s">
-        <v>236</v>
-      </c>
-      <c r="V81" s="36" t="s">
-        <v>237</v>
-      </c>
+      <c r="R81" s="34" t="s">
+        <v>456</v>
+      </c>
+      <c r="S81" s="34" t="s">
+        <v>459</v>
+      </c>
+      <c r="T81" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="U81" s="34"/>
+      <c r="V81" s="34"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:T2"/>
@@ -11367,7 +11368,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -11387,7 +11388,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>

--- a/30_table/01_테스트버전/Table_Data_Map.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Map.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="692">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1645,6 +1645,714 @@
   </si>
   <si>
     <t>img_map_0037</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고고학자</t>
+  </si>
+  <si>
+    <t>작클레의 호출</t>
+  </si>
+  <si>
+    <t>리바이의 서의 비밀 1</t>
+  </si>
+  <si>
+    <t>리바이의 서의 비밀 2</t>
+  </si>
+  <si>
+    <t>민병대원 마르코</t>
+  </si>
+  <si>
+    <t>마법 연구소</t>
+  </si>
+  <si>
+    <t>마법사 작클레</t>
+  </si>
+  <si>
+    <t>여관으로</t>
+  </si>
+  <si>
+    <t>여관 주인 줄리아</t>
+  </si>
+  <si>
+    <t>마법 연구소로</t>
+  </si>
+  <si>
+    <t>광물 조합으로</t>
+  </si>
+  <si>
+    <t>빈 집으로</t>
+  </si>
+  <si>
+    <t>빈집털이</t>
+  </si>
+  <si>
+    <t>파머의 고민</t>
+  </si>
+  <si>
+    <t>호박 수확</t>
+  </si>
+  <si>
+    <t>파머에게 줄 선물</t>
+  </si>
+  <si>
+    <t>광물 조합</t>
+  </si>
+  <si>
+    <t>광물 조합장 코퍼</t>
+  </si>
+  <si>
+    <t>귀신 퇴치</t>
+  </si>
+  <si>
+    <t>도둑</t>
+  </si>
+  <si>
+    <t>귀신 퇴치 보고</t>
+  </si>
+  <si>
+    <t>그들이 노리는 것</t>
+  </si>
+  <si>
+    <t>광산 마을 서쪽으로</t>
+  </si>
+  <si>
+    <t>민병대원 산체스</t>
+  </si>
+  <si>
+    <t>황무지로</t>
+  </si>
+  <si>
+    <t>보물 창고로</t>
+  </si>
+  <si>
+    <t>보물 창고</t>
+  </si>
+  <si>
+    <t>얀센의 전언</t>
+  </si>
+  <si>
+    <t>광산 마을 남쪽으로</t>
+  </si>
+  <si>
+    <t>민병대원 카를로스</t>
+  </si>
+  <si>
+    <t>남쪽 숲으로</t>
+  </si>
+  <si>
+    <t>map_s5_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map_s5_002</t>
+  </si>
+  <si>
+    <t>map_s5_003</t>
+  </si>
+  <si>
+    <t>map_s5_004</t>
+  </si>
+  <si>
+    <t>map_s5_005</t>
+  </si>
+  <si>
+    <t>map_s5_006</t>
+  </si>
+  <si>
+    <t>map_s5_007</t>
+  </si>
+  <si>
+    <t>map_s5_008</t>
+  </si>
+  <si>
+    <t>map_s5_009</t>
+  </si>
+  <si>
+    <t>map_s5_010</t>
+  </si>
+  <si>
+    <t>map_s5_011</t>
+  </si>
+  <si>
+    <t>map_s5_012</t>
+  </si>
+  <si>
+    <t>map_s5_013</t>
+  </si>
+  <si>
+    <t>map_s5_014</t>
+  </si>
+  <si>
+    <t>map_s5_015</t>
+  </si>
+  <si>
+    <t>map_s5_016</t>
+  </si>
+  <si>
+    <t>map_s5_017</t>
+  </si>
+  <si>
+    <t>map_s5_018</t>
+  </si>
+  <si>
+    <t>map_s5_019</t>
+  </si>
+  <si>
+    <t>map_s5_020</t>
+  </si>
+  <si>
+    <t>map_s5_021</t>
+  </si>
+  <si>
+    <t>map_s5_022</t>
+  </si>
+  <si>
+    <t>map_s5_023</t>
+  </si>
+  <si>
+    <t>map_s5_024</t>
+  </si>
+  <si>
+    <t>map_s5_025</t>
+  </si>
+  <si>
+    <t>map_s5_026</t>
+  </si>
+  <si>
+    <t>map_s5_027</t>
+  </si>
+  <si>
+    <t>map_s5_028</t>
+  </si>
+  <si>
+    <t>map_s5_029</t>
+  </si>
+  <si>
+    <t>map_s5_030</t>
+  </si>
+  <si>
+    <t>map_s5_031</t>
+  </si>
+  <si>
+    <t>map_s5_032</t>
+  </si>
+  <si>
+    <t>pf_Map_50080</t>
+  </si>
+  <si>
+    <t>pf_Map_50081</t>
+  </si>
+  <si>
+    <t>pf_Map_50082</t>
+  </si>
+  <si>
+    <t>pf_Map_50083</t>
+  </si>
+  <si>
+    <t>pf_Map_50084</t>
+  </si>
+  <si>
+    <t>pf_Map_50085</t>
+  </si>
+  <si>
+    <t>pf_Map_50086</t>
+  </si>
+  <si>
+    <t>pf_Map_50087</t>
+  </si>
+  <si>
+    <t>pf_Map_50088</t>
+  </si>
+  <si>
+    <t>pf_Map_50089</t>
+  </si>
+  <si>
+    <t>pf_Map_50090</t>
+  </si>
+  <si>
+    <t>pf_Map_50091</t>
+  </si>
+  <si>
+    <t>pf_Map_50092</t>
+  </si>
+  <si>
+    <t>pf_Map_50093</t>
+  </si>
+  <si>
+    <t>pf_Map_50094</t>
+  </si>
+  <si>
+    <t>pf_Map_50095</t>
+  </si>
+  <si>
+    <t>pf_Map_50096</t>
+  </si>
+  <si>
+    <t>pf_Map_50097</t>
+  </si>
+  <si>
+    <t>pf_Map_50098</t>
+  </si>
+  <si>
+    <t>pf_Map_50099</t>
+  </si>
+  <si>
+    <t>pf_Map_50100</t>
+  </si>
+  <si>
+    <t>pf_Map_50101</t>
+  </si>
+  <si>
+    <t>pf_Map_50102</t>
+  </si>
+  <si>
+    <t>pf_Map_50103</t>
+  </si>
+  <si>
+    <t>pf_Map_50104</t>
+  </si>
+  <si>
+    <t>pf_Map_50105</t>
+  </si>
+  <si>
+    <t>pf_Map_50106</t>
+  </si>
+  <si>
+    <t>pf_Map_50107</t>
+  </si>
+  <si>
+    <t>pf_Map_50108</t>
+  </si>
+  <si>
+    <t>pf_Map_50109</t>
+  </si>
+  <si>
+    <t>pf_Map_50110</t>
+  </si>
+  <si>
+    <t>pf_Map_50111</t>
+  </si>
+  <si>
+    <t>pf_Map_50130</t>
+  </si>
+  <si>
+    <t>pf_Map_50131</t>
+  </si>
+  <si>
+    <t>pf_Map_50132</t>
+  </si>
+  <si>
+    <t>pf_Map_50133</t>
+  </si>
+  <si>
+    <t>img_map_0038</t>
+  </si>
+  <si>
+    <t>icon_map_0038</t>
+  </si>
+  <si>
+    <t>img_map_0039</t>
+  </si>
+  <si>
+    <t>icon_map_0039</t>
+  </si>
+  <si>
+    <t>img_map_0040</t>
+  </si>
+  <si>
+    <t>icon_map_0040</t>
+  </si>
+  <si>
+    <t>img_map_0041</t>
+  </si>
+  <si>
+    <t>icon_map_0041</t>
+  </si>
+  <si>
+    <t>img_map_0004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>img_map_0042</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0042</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>img_map_0043</t>
+  </si>
+  <si>
+    <t>icon_map_0043</t>
+  </si>
+  <si>
+    <t>img_map_0044</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0044</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>img_map_0045</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0045</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>img_map_0046</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0046</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>묘지로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>img_map_0047</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0047</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>img_map_0050</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0050</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>img_map_0051</t>
+  </si>
+  <si>
+    <t>icon_map_0051</t>
+  </si>
+  <si>
+    <t>img_map_0052</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0052</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>img_map_0053</t>
+  </si>
+  <si>
+    <t>icon_map_0053</t>
+  </si>
+  <si>
+    <t>탐사 캠프로</t>
+  </si>
+  <si>
+    <t>황무지 탐사대</t>
+  </si>
+  <si>
+    <t>전갈 퇴치</t>
+  </si>
+  <si>
+    <t>전갈 퇴치 보고</t>
+  </si>
+  <si>
+    <t>유적지의 망령</t>
+  </si>
+  <si>
+    <t>유적지 조사</t>
+  </si>
+  <si>
+    <t>유적지 조사 보고</t>
+  </si>
+  <si>
+    <t>폐광 조사 의뢰</t>
+  </si>
+  <si>
+    <t>폐광 조사</t>
+  </si>
+  <si>
+    <t>폐광 조사 보고</t>
+  </si>
+  <si>
+    <t>지룡 안타라스</t>
+  </si>
+  <si>
+    <t>지룡의 둥지로 1</t>
+  </si>
+  <si>
+    <t>지룡의 둥지로 2</t>
+  </si>
+  <si>
+    <t>지룡 안타라스 퇴치</t>
+  </si>
+  <si>
+    <t>지룡 퇴치 보고</t>
+  </si>
+  <si>
+    <t>고대 유적</t>
+  </si>
+  <si>
+    <t>광산 마을로</t>
+  </si>
+  <si>
+    <t>지룡의 둥지로 3</t>
+  </si>
+  <si>
+    <t>지룡의 둥지로 4</t>
+  </si>
+  <si>
+    <t>안타라스의 보물</t>
+  </si>
+  <si>
+    <t>폐광으로</t>
+  </si>
+  <si>
+    <t>폐광 입구</t>
+  </si>
+  <si>
+    <t>map_s6_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map_s6_002</t>
+  </si>
+  <si>
+    <t>map_s6_003</t>
+  </si>
+  <si>
+    <t>map_s6_004</t>
+  </si>
+  <si>
+    <t>map_s6_005</t>
+  </si>
+  <si>
+    <t>map_s6_006</t>
+  </si>
+  <si>
+    <t>map_s6_007</t>
+  </si>
+  <si>
+    <t>map_s6_008</t>
+  </si>
+  <si>
+    <t>map_s6_009</t>
+  </si>
+  <si>
+    <t>map_s6_010</t>
+  </si>
+  <si>
+    <t>map_s6_011</t>
+  </si>
+  <si>
+    <t>map_s6_012</t>
+  </si>
+  <si>
+    <t>map_s6_013</t>
+  </si>
+  <si>
+    <t>map_s6_014</t>
+  </si>
+  <si>
+    <t>map_s6_015</t>
+  </si>
+  <si>
+    <t>map_s6_016</t>
+  </si>
+  <si>
+    <t>map_s6_017</t>
+  </si>
+  <si>
+    <t>map_s6_018</t>
+  </si>
+  <si>
+    <t>map_s6_019</t>
+  </si>
+  <si>
+    <t>map_s6_020</t>
+  </si>
+  <si>
+    <t>map_s6_021</t>
+  </si>
+  <si>
+    <t>map_s6_022</t>
+  </si>
+  <si>
+    <t>map_s6_023</t>
+  </si>
+  <si>
+    <t>map_s6_024</t>
+  </si>
+  <si>
+    <t>map_s6_025</t>
+  </si>
+  <si>
+    <t>pf_Map_50112</t>
+  </si>
+  <si>
+    <t>pf_Map_50113</t>
+  </si>
+  <si>
+    <t>pf_Map_50114</t>
+  </si>
+  <si>
+    <t>pf_Map_50115</t>
+  </si>
+  <si>
+    <t>pf_Map_50116</t>
+  </si>
+  <si>
+    <t>pf_Map_50117</t>
+  </si>
+  <si>
+    <t>pf_Map_50118</t>
+  </si>
+  <si>
+    <t>pf_Map_50119</t>
+  </si>
+  <si>
+    <t>pf_Map_50120</t>
+  </si>
+  <si>
+    <t>pf_Map_50121</t>
+  </si>
+  <si>
+    <t>pf_Map_50122</t>
+  </si>
+  <si>
+    <t>pf_Map_50123</t>
+  </si>
+  <si>
+    <t>pf_Map_50124</t>
+  </si>
+  <si>
+    <t>pf_Map_50125</t>
+  </si>
+  <si>
+    <t>pf_Map_50126</t>
+  </si>
+  <si>
+    <t>pf_Map_50127</t>
+  </si>
+  <si>
+    <t>pf_Map_50128</t>
+  </si>
+  <si>
+    <t>pf_Map_50129</t>
+  </si>
+  <si>
+    <t>pf_Map_50134</t>
+  </si>
+  <si>
+    <t>pf_Map_50135</t>
+  </si>
+  <si>
+    <t>pf_Map_50136</t>
+  </si>
+  <si>
+    <t>만든 사람들</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map_s0_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pf_Map_59000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>img_map_0054</t>
+  </si>
+  <si>
+    <t>icon_map_0054</t>
+  </si>
+  <si>
+    <t>img_map_0055</t>
+  </si>
+  <si>
+    <t>icon_map_0055</t>
+  </si>
+  <si>
+    <t>img_map_0057</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0057</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>img_map_0060</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0060</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>img_map_0059</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>img_map_0061</t>
+  </si>
+  <si>
+    <t>img_map_0056</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0059</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0056</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0061</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>img_map_0058</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0058</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>img_map_0028</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0028</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>img_map_0062</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0062</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>img_map_9000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_9000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5630,7 +6338,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:V81"/>
+  <dimension ref="A1:V139"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" style="36" bestFit="1" customWidth="1"/>
@@ -11136,6 +11844,3196 @@
       </c>
       <c r="U81" s="34"/>
       <c r="V81" s="34"/>
+    </row>
+    <row r="82" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A82" s="36">
+        <v>50080</v>
+      </c>
+      <c r="B82" s="36" t="s">
+        <v>473</v>
+      </c>
+      <c r="C82" s="34" t="s">
+        <v>500</v>
+      </c>
+      <c r="D82" s="34" t="str">
+        <f t="shared" ref="D82:D113" si="38">"STR_"&amp;UPPER(C82)</f>
+        <v>STR_MAP_S5_001</v>
+      </c>
+      <c r="E82" s="34" t="str">
+        <f t="shared" ref="E82:E113" si="39">D82&amp;"_DESC"</f>
+        <v>STR_MAP_S5_001_DESC</v>
+      </c>
+      <c r="F82" s="36">
+        <v>5</v>
+      </c>
+      <c r="G82" s="36">
+        <v>2</v>
+      </c>
+      <c r="H82" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="I82" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J82" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K82" s="34">
+        <v>0</v>
+      </c>
+      <c r="L82" s="34" t="s">
+        <v>532</v>
+      </c>
+      <c r="M82" s="34" t="s">
+        <v>568</v>
+      </c>
+      <c r="N82" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O82" s="34" t="s">
+        <v>569</v>
+      </c>
+      <c r="P82" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q82" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A83" s="36">
+        <v>50081</v>
+      </c>
+      <c r="B83" s="36" t="s">
+        <v>469</v>
+      </c>
+      <c r="C83" s="34" t="s">
+        <v>501</v>
+      </c>
+      <c r="D83" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_002</v>
+      </c>
+      <c r="E83" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_002_DESC</v>
+      </c>
+      <c r="F83" s="36">
+        <v>5</v>
+      </c>
+      <c r="G83" s="36">
+        <v>2</v>
+      </c>
+      <c r="H83" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="I83" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J83" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K83" s="34">
+        <v>0</v>
+      </c>
+      <c r="L83" s="34" t="s">
+        <v>533</v>
+      </c>
+      <c r="M83" s="34" t="s">
+        <v>568</v>
+      </c>
+      <c r="N83" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O83" s="34" t="s">
+        <v>569</v>
+      </c>
+      <c r="P83" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q83" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A84" s="36">
+        <v>50082</v>
+      </c>
+      <c r="B84" s="36" t="s">
+        <v>474</v>
+      </c>
+      <c r="C84" s="34" t="s">
+        <v>502</v>
+      </c>
+      <c r="D84" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_003</v>
+      </c>
+      <c r="E84" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_003_DESC</v>
+      </c>
+      <c r="F84" s="36">
+        <v>5</v>
+      </c>
+      <c r="G84" s="36">
+        <v>2</v>
+      </c>
+      <c r="H84" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="I84" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J84" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K84" s="34">
+        <v>0</v>
+      </c>
+      <c r="L84" s="34" t="s">
+        <v>534</v>
+      </c>
+      <c r="M84" s="34" t="s">
+        <v>570</v>
+      </c>
+      <c r="N84" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O84" s="34" t="s">
+        <v>571</v>
+      </c>
+      <c r="P84" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q84" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A85" s="36">
+        <v>50083</v>
+      </c>
+      <c r="B85" s="36" t="s">
+        <v>475</v>
+      </c>
+      <c r="C85" s="34" t="s">
+        <v>503</v>
+      </c>
+      <c r="D85" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_004</v>
+      </c>
+      <c r="E85" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_004_DESC</v>
+      </c>
+      <c r="F85" s="36">
+        <v>5</v>
+      </c>
+      <c r="G85" s="36">
+        <v>2</v>
+      </c>
+      <c r="H85" s="36" t="s">
+        <v>451</v>
+      </c>
+      <c r="I85" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J85" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K85" s="34">
+        <v>0</v>
+      </c>
+      <c r="L85" s="34" t="s">
+        <v>535</v>
+      </c>
+      <c r="M85" s="34" t="s">
+        <v>572</v>
+      </c>
+      <c r="N85" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O85" s="34" t="s">
+        <v>573</v>
+      </c>
+      <c r="P85" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q85" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A86" s="36">
+        <v>50084</v>
+      </c>
+      <c r="B86" s="36" t="s">
+        <v>476</v>
+      </c>
+      <c r="C86" s="34" t="s">
+        <v>504</v>
+      </c>
+      <c r="D86" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_005</v>
+      </c>
+      <c r="E86" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_005_DESC</v>
+      </c>
+      <c r="F86" s="36">
+        <v>5</v>
+      </c>
+      <c r="G86" s="36">
+        <v>2</v>
+      </c>
+      <c r="H86" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="I86" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J86" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K86" s="34">
+        <v>0</v>
+      </c>
+      <c r="L86" s="34" t="s">
+        <v>536</v>
+      </c>
+      <c r="M86" s="34" t="s">
+        <v>574</v>
+      </c>
+      <c r="N86" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O86" s="34" t="s">
+        <v>575</v>
+      </c>
+      <c r="P86" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q86" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A87" s="36">
+        <v>50085</v>
+      </c>
+      <c r="B87" s="36" t="s">
+        <v>477</v>
+      </c>
+      <c r="C87" s="34" t="s">
+        <v>505</v>
+      </c>
+      <c r="D87" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_006</v>
+      </c>
+      <c r="E87" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_006_DESC</v>
+      </c>
+      <c r="F87" s="36">
+        <v>5</v>
+      </c>
+      <c r="G87" s="36">
+        <v>2</v>
+      </c>
+      <c r="H87" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="I87" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J87" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K87" s="34">
+        <v>0</v>
+      </c>
+      <c r="L87" s="34" t="s">
+        <v>537</v>
+      </c>
+      <c r="M87" s="34" t="s">
+        <v>576</v>
+      </c>
+      <c r="N87" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O87" s="34" t="s">
+        <v>577</v>
+      </c>
+      <c r="P87" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q87" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A88" s="36">
+        <v>50086</v>
+      </c>
+      <c r="B88" s="36" t="s">
+        <v>470</v>
+      </c>
+      <c r="C88" s="34" t="s">
+        <v>506</v>
+      </c>
+      <c r="D88" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_007</v>
+      </c>
+      <c r="E88" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_007_DESC</v>
+      </c>
+      <c r="F88" s="36">
+        <v>5</v>
+      </c>
+      <c r="G88" s="36">
+        <v>2</v>
+      </c>
+      <c r="H88" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="I88" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J88" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K88" s="34">
+        <v>0</v>
+      </c>
+      <c r="L88" s="34" t="s">
+        <v>538</v>
+      </c>
+      <c r="M88" s="34" t="s">
+        <v>576</v>
+      </c>
+      <c r="N88" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O88" s="34" t="s">
+        <v>577</v>
+      </c>
+      <c r="P88" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q88" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A89" s="36">
+        <v>50087</v>
+      </c>
+      <c r="B89" s="36" t="s">
+        <v>478</v>
+      </c>
+      <c r="C89" s="34" t="s">
+        <v>507</v>
+      </c>
+      <c r="D89" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_008</v>
+      </c>
+      <c r="E89" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_008_DESC</v>
+      </c>
+      <c r="F89" s="36">
+        <v>5</v>
+      </c>
+      <c r="G89" s="36">
+        <v>2</v>
+      </c>
+      <c r="H89" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="I89" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J89" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K89" s="34">
+        <v>0</v>
+      </c>
+      <c r="L89" s="34" t="s">
+        <v>539</v>
+      </c>
+      <c r="M89" s="34" t="s">
+        <v>570</v>
+      </c>
+      <c r="N89" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O89" s="34" t="s">
+        <v>571</v>
+      </c>
+      <c r="P89" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q89" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A90" s="36">
+        <v>50088</v>
+      </c>
+      <c r="B90" s="36" t="s">
+        <v>471</v>
+      </c>
+      <c r="C90" s="34" t="s">
+        <v>508</v>
+      </c>
+      <c r="D90" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_009</v>
+      </c>
+      <c r="E90" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_009_DESC</v>
+      </c>
+      <c r="F90" s="36">
+        <v>5</v>
+      </c>
+      <c r="G90" s="36">
+        <v>2</v>
+      </c>
+      <c r="H90" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="I90" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J90" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K90" s="34">
+        <v>0</v>
+      </c>
+      <c r="L90" s="34" t="s">
+        <v>540</v>
+      </c>
+      <c r="M90" s="34" t="s">
+        <v>572</v>
+      </c>
+      <c r="N90" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O90" s="34" t="s">
+        <v>573</v>
+      </c>
+      <c r="P90" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q90" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A91" s="36">
+        <v>50089</v>
+      </c>
+      <c r="B91" s="36" t="s">
+        <v>479</v>
+      </c>
+      <c r="C91" s="34" t="s">
+        <v>509</v>
+      </c>
+      <c r="D91" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_010</v>
+      </c>
+      <c r="E91" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_010_DESC</v>
+      </c>
+      <c r="F91" s="36">
+        <v>5</v>
+      </c>
+      <c r="G91" s="36">
+        <v>2</v>
+      </c>
+      <c r="H91" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="I91" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J91" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K91" s="34">
+        <v>0</v>
+      </c>
+      <c r="L91" s="34" t="s">
+        <v>541</v>
+      </c>
+      <c r="M91" s="34" t="s">
+        <v>578</v>
+      </c>
+      <c r="N91" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O91" s="34" t="s">
+        <v>579</v>
+      </c>
+      <c r="P91" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q91" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A92" s="36">
+        <v>50090</v>
+      </c>
+      <c r="B92" s="36" t="s">
+        <v>480</v>
+      </c>
+      <c r="C92" s="34" t="s">
+        <v>510</v>
+      </c>
+      <c r="D92" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_011</v>
+      </c>
+      <c r="E92" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_011_DESC</v>
+      </c>
+      <c r="F92" s="36">
+        <v>5</v>
+      </c>
+      <c r="G92" s="36">
+        <v>2</v>
+      </c>
+      <c r="H92" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="I92" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J92" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K92" s="34">
+        <v>0</v>
+      </c>
+      <c r="L92" s="34" t="s">
+        <v>542</v>
+      </c>
+      <c r="M92" s="34" t="s">
+        <v>578</v>
+      </c>
+      <c r="N92" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O92" s="34" t="s">
+        <v>579</v>
+      </c>
+      <c r="P92" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q92" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A93" s="36">
+        <v>50091</v>
+      </c>
+      <c r="B93" s="36" t="s">
+        <v>481</v>
+      </c>
+      <c r="C93" s="34" t="s">
+        <v>511</v>
+      </c>
+      <c r="D93" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_012</v>
+      </c>
+      <c r="E93" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_012_DESC</v>
+      </c>
+      <c r="F93" s="36">
+        <v>5</v>
+      </c>
+      <c r="G93" s="36">
+        <v>2</v>
+      </c>
+      <c r="H93" s="34" t="s">
+        <v>453</v>
+      </c>
+      <c r="I93" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J93" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K93" s="34">
+        <v>0</v>
+      </c>
+      <c r="L93" s="34" t="s">
+        <v>543</v>
+      </c>
+      <c r="M93" s="34" t="s">
+        <v>582</v>
+      </c>
+      <c r="N93" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O93" s="34" t="s">
+        <v>583</v>
+      </c>
+      <c r="P93" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q93" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A94" s="36">
+        <v>50092</v>
+      </c>
+      <c r="B94" s="36" t="s">
+        <v>482</v>
+      </c>
+      <c r="C94" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="D94" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_013</v>
+      </c>
+      <c r="E94" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_013_DESC</v>
+      </c>
+      <c r="F94" s="36">
+        <v>5</v>
+      </c>
+      <c r="G94" s="36">
+        <v>2</v>
+      </c>
+      <c r="H94" s="36" t="s">
+        <v>451</v>
+      </c>
+      <c r="I94" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J94" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K94" s="34">
+        <v>0</v>
+      </c>
+      <c r="L94" s="34" t="s">
+        <v>544</v>
+      </c>
+      <c r="M94" s="34" t="s">
+        <v>578</v>
+      </c>
+      <c r="N94" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O94" s="34" t="s">
+        <v>579</v>
+      </c>
+      <c r="P94" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q94" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A95" s="36">
+        <v>50093</v>
+      </c>
+      <c r="B95" s="36" t="s">
+        <v>483</v>
+      </c>
+      <c r="C95" s="34" t="s">
+        <v>513</v>
+      </c>
+      <c r="D95" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_014</v>
+      </c>
+      <c r="E95" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_014_DESC</v>
+      </c>
+      <c r="F95" s="36">
+        <v>5</v>
+      </c>
+      <c r="G95" s="36">
+        <v>2</v>
+      </c>
+      <c r="H95" s="34" t="s">
+        <v>453</v>
+      </c>
+      <c r="I95" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J95" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K95" s="34">
+        <v>0</v>
+      </c>
+      <c r="L95" s="34" t="s">
+        <v>545</v>
+      </c>
+      <c r="M95" s="34" t="s">
+        <v>584</v>
+      </c>
+      <c r="N95" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O95" s="34" t="s">
+        <v>585</v>
+      </c>
+      <c r="P95" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q95" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A96" s="36">
+        <v>50094</v>
+      </c>
+      <c r="B96" s="36" t="s">
+        <v>484</v>
+      </c>
+      <c r="C96" s="34" t="s">
+        <v>514</v>
+      </c>
+      <c r="D96" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_015</v>
+      </c>
+      <c r="E96" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_015_DESC</v>
+      </c>
+      <c r="F96" s="36">
+        <v>5</v>
+      </c>
+      <c r="G96" s="36">
+        <v>2</v>
+      </c>
+      <c r="H96" s="36" t="s">
+        <v>451</v>
+      </c>
+      <c r="I96" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J96" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K96" s="34">
+        <v>0</v>
+      </c>
+      <c r="L96" s="34" t="s">
+        <v>546</v>
+      </c>
+      <c r="M96" s="34" t="s">
+        <v>578</v>
+      </c>
+      <c r="N96" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O96" s="34" t="s">
+        <v>579</v>
+      </c>
+      <c r="P96" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q96" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A97" s="36">
+        <v>50095</v>
+      </c>
+      <c r="B97" s="36" t="s">
+        <v>485</v>
+      </c>
+      <c r="C97" s="34" t="s">
+        <v>515</v>
+      </c>
+      <c r="D97" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_016</v>
+      </c>
+      <c r="E97" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_016_DESC</v>
+      </c>
+      <c r="F97" s="36">
+        <v>5</v>
+      </c>
+      <c r="G97" s="36">
+        <v>2</v>
+      </c>
+      <c r="H97" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="I97" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J97" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K97" s="34">
+        <v>0</v>
+      </c>
+      <c r="L97" s="34" t="s">
+        <v>547</v>
+      </c>
+      <c r="M97" s="34" t="s">
+        <v>580</v>
+      </c>
+      <c r="N97" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O97" s="34" t="s">
+        <v>581</v>
+      </c>
+      <c r="P97" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q97" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A98" s="36">
+        <v>50096</v>
+      </c>
+      <c r="B98" s="36" t="s">
+        <v>486</v>
+      </c>
+      <c r="C98" s="34" t="s">
+        <v>516</v>
+      </c>
+      <c r="D98" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_017</v>
+      </c>
+      <c r="E98" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_017_DESC</v>
+      </c>
+      <c r="F98" s="36">
+        <v>5</v>
+      </c>
+      <c r="G98" s="36">
+        <v>2</v>
+      </c>
+      <c r="H98" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="I98" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J98" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K98" s="34">
+        <v>0</v>
+      </c>
+      <c r="L98" s="34" t="s">
+        <v>548</v>
+      </c>
+      <c r="M98" s="34" t="s">
+        <v>586</v>
+      </c>
+      <c r="N98" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O98" s="34" t="s">
+        <v>587</v>
+      </c>
+      <c r="P98" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q98" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A99" s="36">
+        <v>50097</v>
+      </c>
+      <c r="B99" s="36" t="s">
+        <v>472</v>
+      </c>
+      <c r="C99" s="34" t="s">
+        <v>517</v>
+      </c>
+      <c r="D99" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_018</v>
+      </c>
+      <c r="E99" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_018_DESC</v>
+      </c>
+      <c r="F99" s="36">
+        <v>5</v>
+      </c>
+      <c r="G99" s="36">
+        <v>2</v>
+      </c>
+      <c r="H99" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="I99" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J99" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K99" s="34">
+        <v>0</v>
+      </c>
+      <c r="L99" s="34" t="s">
+        <v>549</v>
+      </c>
+      <c r="M99" s="34" t="s">
+        <v>586</v>
+      </c>
+      <c r="N99" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O99" s="34" t="s">
+        <v>587</v>
+      </c>
+      <c r="P99" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q99" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A100" s="36">
+        <v>50098</v>
+      </c>
+      <c r="B100" s="36" t="s">
+        <v>588</v>
+      </c>
+      <c r="C100" s="34" t="s">
+        <v>518</v>
+      </c>
+      <c r="D100" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_019</v>
+      </c>
+      <c r="E100" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_019_DESC</v>
+      </c>
+      <c r="F100" s="36">
+        <v>5</v>
+      </c>
+      <c r="G100" s="36">
+        <v>2</v>
+      </c>
+      <c r="H100" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="I100" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J100" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K100" s="34">
+        <v>0</v>
+      </c>
+      <c r="L100" s="34" t="s">
+        <v>550</v>
+      </c>
+      <c r="M100" s="34" t="s">
+        <v>580</v>
+      </c>
+      <c r="N100" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O100" s="34" t="s">
+        <v>581</v>
+      </c>
+      <c r="P100" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q100" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A101" s="36">
+        <v>50099</v>
+      </c>
+      <c r="B101" s="36" t="s">
+        <v>487</v>
+      </c>
+      <c r="C101" s="34" t="s">
+        <v>519</v>
+      </c>
+      <c r="D101" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_020</v>
+      </c>
+      <c r="E101" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_020_DESC</v>
+      </c>
+      <c r="F101" s="36">
+        <v>5</v>
+      </c>
+      <c r="G101" s="36">
+        <v>2</v>
+      </c>
+      <c r="H101" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="I101" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J101" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K101" s="34">
+        <v>0</v>
+      </c>
+      <c r="L101" s="34" t="s">
+        <v>551</v>
+      </c>
+      <c r="M101" s="34" t="s">
+        <v>589</v>
+      </c>
+      <c r="N101" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O101" s="34" t="s">
+        <v>590</v>
+      </c>
+      <c r="P101" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q101" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A102" s="36">
+        <v>50100</v>
+      </c>
+      <c r="B102" s="36" t="s">
+        <v>488</v>
+      </c>
+      <c r="C102" s="34" t="s">
+        <v>520</v>
+      </c>
+      <c r="D102" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_021</v>
+      </c>
+      <c r="E102" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_021_DESC</v>
+      </c>
+      <c r="F102" s="36">
+        <v>5</v>
+      </c>
+      <c r="G102" s="36">
+        <v>2</v>
+      </c>
+      <c r="H102" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="I102" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J102" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K102" s="34">
+        <v>0</v>
+      </c>
+      <c r="L102" s="34" t="s">
+        <v>552</v>
+      </c>
+      <c r="M102" s="34" t="s">
+        <v>580</v>
+      </c>
+      <c r="N102" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O102" s="34" t="s">
+        <v>581</v>
+      </c>
+      <c r="P102" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q102" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A103" s="36">
+        <v>50101</v>
+      </c>
+      <c r="B103" s="36" t="s">
+        <v>489</v>
+      </c>
+      <c r="C103" s="34" t="s">
+        <v>521</v>
+      </c>
+      <c r="D103" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_022</v>
+      </c>
+      <c r="E103" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_022_DESC</v>
+      </c>
+      <c r="F103" s="36">
+        <v>5</v>
+      </c>
+      <c r="G103" s="36">
+        <v>2</v>
+      </c>
+      <c r="H103" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="I103" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J103" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K103" s="34">
+        <v>0</v>
+      </c>
+      <c r="L103" s="34" t="s">
+        <v>553</v>
+      </c>
+      <c r="M103" s="34" t="s">
+        <v>586</v>
+      </c>
+      <c r="N103" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O103" s="34" t="s">
+        <v>587</v>
+      </c>
+      <c r="P103" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q103" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A104" s="36">
+        <v>50102</v>
+      </c>
+      <c r="B104" s="36" t="s">
+        <v>490</v>
+      </c>
+      <c r="C104" s="34" t="s">
+        <v>522</v>
+      </c>
+      <c r="D104" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_023</v>
+      </c>
+      <c r="E104" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_023_DESC</v>
+      </c>
+      <c r="F104" s="36">
+        <v>5</v>
+      </c>
+      <c r="G104" s="36">
+        <v>2</v>
+      </c>
+      <c r="H104" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="I104" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J104" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K104" s="34">
+        <v>0</v>
+      </c>
+      <c r="L104" s="34" t="s">
+        <v>554</v>
+      </c>
+      <c r="M104" s="34" t="s">
+        <v>586</v>
+      </c>
+      <c r="N104" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O104" s="34" t="s">
+        <v>587</v>
+      </c>
+      <c r="P104" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q104" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A105" s="36">
+        <v>50103</v>
+      </c>
+      <c r="B105" s="36" t="s">
+        <v>491</v>
+      </c>
+      <c r="C105" s="34" t="s">
+        <v>523</v>
+      </c>
+      <c r="D105" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_024</v>
+      </c>
+      <c r="E105" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_024_DESC</v>
+      </c>
+      <c r="F105" s="36">
+        <v>5</v>
+      </c>
+      <c r="G105" s="36">
+        <v>2</v>
+      </c>
+      <c r="H105" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="I105" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J105" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K105" s="34">
+        <v>0</v>
+      </c>
+      <c r="L105" s="34" t="s">
+        <v>555</v>
+      </c>
+      <c r="M105" s="34" t="s">
+        <v>580</v>
+      </c>
+      <c r="N105" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O105" s="34" t="s">
+        <v>581</v>
+      </c>
+      <c r="P105" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q105" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A106" s="36">
+        <v>50104</v>
+      </c>
+      <c r="B106" s="36" t="s">
+        <v>492</v>
+      </c>
+      <c r="C106" s="34" t="s">
+        <v>524</v>
+      </c>
+      <c r="D106" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_025</v>
+      </c>
+      <c r="E106" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_025_DESC</v>
+      </c>
+      <c r="F106" s="36">
+        <v>5</v>
+      </c>
+      <c r="G106" s="36">
+        <v>2</v>
+      </c>
+      <c r="H106" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="I106" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J106" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K106" s="34">
+        <v>0</v>
+      </c>
+      <c r="L106" s="34" t="s">
+        <v>556</v>
+      </c>
+      <c r="M106" s="34" t="s">
+        <v>591</v>
+      </c>
+      <c r="N106" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O106" s="34" t="s">
+        <v>592</v>
+      </c>
+      <c r="P106" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q106" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A107" s="36">
+        <v>50105</v>
+      </c>
+      <c r="B107" s="36" t="s">
+        <v>493</v>
+      </c>
+      <c r="C107" s="34" t="s">
+        <v>525</v>
+      </c>
+      <c r="D107" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_026</v>
+      </c>
+      <c r="E107" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_026_DESC</v>
+      </c>
+      <c r="F107" s="36">
+        <v>5</v>
+      </c>
+      <c r="G107" s="36">
+        <v>2</v>
+      </c>
+      <c r="H107" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="I107" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J107" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K107" s="34">
+        <v>0</v>
+      </c>
+      <c r="L107" s="34" t="s">
+        <v>557</v>
+      </c>
+      <c r="M107" s="34" t="s">
+        <v>591</v>
+      </c>
+      <c r="N107" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O107" s="34" t="s">
+        <v>592</v>
+      </c>
+      <c r="P107" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q107" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A108" s="36">
+        <v>50106</v>
+      </c>
+      <c r="B108" s="36" t="s">
+        <v>494</v>
+      </c>
+      <c r="C108" s="34" t="s">
+        <v>526</v>
+      </c>
+      <c r="D108" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_027</v>
+      </c>
+      <c r="E108" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_027_DESC</v>
+      </c>
+      <c r="F108" s="36">
+        <v>5</v>
+      </c>
+      <c r="G108" s="36">
+        <v>2</v>
+      </c>
+      <c r="H108" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="I108" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J108" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K108" s="34">
+        <v>0</v>
+      </c>
+      <c r="L108" s="34" t="s">
+        <v>558</v>
+      </c>
+      <c r="M108" s="34" t="s">
+        <v>591</v>
+      </c>
+      <c r="N108" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O108" s="34" t="s">
+        <v>592</v>
+      </c>
+      <c r="P108" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q108" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A109" s="36">
+        <v>50107</v>
+      </c>
+      <c r="B109" s="36" t="s">
+        <v>495</v>
+      </c>
+      <c r="C109" s="34" t="s">
+        <v>527</v>
+      </c>
+      <c r="D109" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_028</v>
+      </c>
+      <c r="E109" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_028_DESC</v>
+      </c>
+      <c r="F109" s="36">
+        <v>5</v>
+      </c>
+      <c r="G109" s="36">
+        <v>2</v>
+      </c>
+      <c r="H109" s="36" t="s">
+        <v>179</v>
+      </c>
+      <c r="I109" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J109" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K109" s="34">
+        <v>0</v>
+      </c>
+      <c r="L109" s="34" t="s">
+        <v>559</v>
+      </c>
+      <c r="M109" s="34" t="s">
+        <v>593</v>
+      </c>
+      <c r="N109" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O109" s="34" t="s">
+        <v>594</v>
+      </c>
+      <c r="P109" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q109" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A110" s="36">
+        <v>50108</v>
+      </c>
+      <c r="B110" s="36" t="s">
+        <v>496</v>
+      </c>
+      <c r="C110" s="34" t="s">
+        <v>528</v>
+      </c>
+      <c r="D110" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_029</v>
+      </c>
+      <c r="E110" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_029_DESC</v>
+      </c>
+      <c r="F110" s="36">
+        <v>5</v>
+      </c>
+      <c r="G110" s="36">
+        <v>3</v>
+      </c>
+      <c r="H110" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="I110" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J110" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K110" s="34">
+        <v>0</v>
+      </c>
+      <c r="L110" s="34" t="s">
+        <v>560</v>
+      </c>
+      <c r="M110" s="34" t="s">
+        <v>572</v>
+      </c>
+      <c r="N110" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O110" s="34" t="s">
+        <v>573</v>
+      </c>
+      <c r="P110" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q110" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A111" s="36">
+        <v>50109</v>
+      </c>
+      <c r="B111" s="36" t="s">
+        <v>497</v>
+      </c>
+      <c r="C111" s="34" t="s">
+        <v>529</v>
+      </c>
+      <c r="D111" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_030</v>
+      </c>
+      <c r="E111" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_030_DESC</v>
+      </c>
+      <c r="F111" s="36">
+        <v>5</v>
+      </c>
+      <c r="G111" s="36">
+        <v>3</v>
+      </c>
+      <c r="H111" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="I111" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J111" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K111" s="34">
+        <v>0</v>
+      </c>
+      <c r="L111" s="34" t="s">
+        <v>561</v>
+      </c>
+      <c r="M111" s="34" t="s">
+        <v>595</v>
+      </c>
+      <c r="N111" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O111" s="34" t="s">
+        <v>596</v>
+      </c>
+      <c r="P111" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q111" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A112" s="36">
+        <v>50110</v>
+      </c>
+      <c r="B112" s="36" t="s">
+        <v>498</v>
+      </c>
+      <c r="C112" s="34" t="s">
+        <v>530</v>
+      </c>
+      <c r="D112" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_031</v>
+      </c>
+      <c r="E112" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_031_DESC</v>
+      </c>
+      <c r="F112" s="36">
+        <v>5</v>
+      </c>
+      <c r="G112" s="36">
+        <v>3</v>
+      </c>
+      <c r="H112" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="I112" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J112" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K112" s="34">
+        <v>0</v>
+      </c>
+      <c r="L112" s="34" t="s">
+        <v>562</v>
+      </c>
+      <c r="M112" s="34" t="s">
+        <v>597</v>
+      </c>
+      <c r="N112" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O112" s="34" t="s">
+        <v>598</v>
+      </c>
+      <c r="P112" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q112" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A113" s="36">
+        <v>50111</v>
+      </c>
+      <c r="B113" s="36" t="s">
+        <v>499</v>
+      </c>
+      <c r="C113" s="34" t="s">
+        <v>531</v>
+      </c>
+      <c r="D113" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v>STR_MAP_S5_032</v>
+      </c>
+      <c r="E113" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v>STR_MAP_S5_032_DESC</v>
+      </c>
+      <c r="F113" s="36">
+        <v>5</v>
+      </c>
+      <c r="G113" s="36">
+        <v>3</v>
+      </c>
+      <c r="H113" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="I113" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J113" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K113" s="34">
+        <v>0</v>
+      </c>
+      <c r="L113" s="34" t="s">
+        <v>563</v>
+      </c>
+      <c r="M113" s="34" t="s">
+        <v>597</v>
+      </c>
+      <c r="N113" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O113" s="34" t="s">
+        <v>598</v>
+      </c>
+      <c r="P113" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q113" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A114" s="36">
+        <v>50112</v>
+      </c>
+      <c r="B114" s="36" t="s">
+        <v>599</v>
+      </c>
+      <c r="C114" s="34" t="s">
+        <v>621</v>
+      </c>
+      <c r="D114" s="34" t="str">
+        <f t="shared" ref="D114" si="40">"STR_"&amp;UPPER(C114)</f>
+        <v>STR_MAP_S6_001</v>
+      </c>
+      <c r="E114" s="34" t="str">
+        <f t="shared" ref="E114" si="41">D114&amp;"_DESC"</f>
+        <v>STR_MAP_S6_001_DESC</v>
+      </c>
+      <c r="F114" s="36">
+        <v>6</v>
+      </c>
+      <c r="G114" s="36">
+        <v>3</v>
+      </c>
+      <c r="H114" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="I114" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J114" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K114" s="34">
+        <v>0</v>
+      </c>
+      <c r="L114" s="34" t="s">
+        <v>646</v>
+      </c>
+      <c r="M114" s="34" t="s">
+        <v>670</v>
+      </c>
+      <c r="N114" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O114" s="34" t="s">
+        <v>671</v>
+      </c>
+      <c r="P114" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q114" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A115" s="36">
+        <v>50113</v>
+      </c>
+      <c r="B115" s="36" t="s">
+        <v>600</v>
+      </c>
+      <c r="C115" s="34" t="s">
+        <v>622</v>
+      </c>
+      <c r="D115" s="34" t="str">
+        <f t="shared" ref="D115:D138" si="42">"STR_"&amp;UPPER(C115)</f>
+        <v>STR_MAP_S6_002</v>
+      </c>
+      <c r="E115" s="34" t="str">
+        <f t="shared" ref="E115:E138" si="43">D115&amp;"_DESC"</f>
+        <v>STR_MAP_S6_002_DESC</v>
+      </c>
+      <c r="F115" s="36">
+        <v>6</v>
+      </c>
+      <c r="G115" s="36">
+        <v>3</v>
+      </c>
+      <c r="H115" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="I115" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J115" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K115" s="34">
+        <v>0</v>
+      </c>
+      <c r="L115" s="34" t="s">
+        <v>647</v>
+      </c>
+      <c r="M115" s="34" t="s">
+        <v>672</v>
+      </c>
+      <c r="N115" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O115" s="34" t="s">
+        <v>673</v>
+      </c>
+      <c r="P115" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q115" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A116" s="36">
+        <v>50114</v>
+      </c>
+      <c r="B116" s="36" t="s">
+        <v>601</v>
+      </c>
+      <c r="C116" s="34" t="s">
+        <v>623</v>
+      </c>
+      <c r="D116" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v>STR_MAP_S6_003</v>
+      </c>
+      <c r="E116" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>STR_MAP_S6_003_DESC</v>
+      </c>
+      <c r="F116" s="36">
+        <v>6</v>
+      </c>
+      <c r="G116" s="36">
+        <v>3</v>
+      </c>
+      <c r="H116" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="I116" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J116" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K116" s="34">
+        <v>0</v>
+      </c>
+      <c r="L116" s="34" t="s">
+        <v>648</v>
+      </c>
+      <c r="M116" s="34" t="s">
+        <v>670</v>
+      </c>
+      <c r="N116" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O116" s="34" t="s">
+        <v>671</v>
+      </c>
+      <c r="P116" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q116" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A117" s="36">
+        <v>50115</v>
+      </c>
+      <c r="B117" s="36" t="s">
+        <v>602</v>
+      </c>
+      <c r="C117" s="34" t="s">
+        <v>624</v>
+      </c>
+      <c r="D117" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v>STR_MAP_S6_004</v>
+      </c>
+      <c r="E117" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>STR_MAP_S6_004_DESC</v>
+      </c>
+      <c r="F117" s="36">
+        <v>6</v>
+      </c>
+      <c r="G117" s="36">
+        <v>3</v>
+      </c>
+      <c r="H117" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="I117" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J117" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K117" s="34">
+        <v>0</v>
+      </c>
+      <c r="L117" s="34" t="s">
+        <v>649</v>
+      </c>
+      <c r="M117" s="34" t="s">
+        <v>672</v>
+      </c>
+      <c r="N117" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O117" s="34" t="s">
+        <v>673</v>
+      </c>
+      <c r="P117" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q117" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A118" s="36">
+        <v>50116</v>
+      </c>
+      <c r="B118" s="36" t="s">
+        <v>603</v>
+      </c>
+      <c r="C118" s="34" t="s">
+        <v>625</v>
+      </c>
+      <c r="D118" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v>STR_MAP_S6_005</v>
+      </c>
+      <c r="E118" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>STR_MAP_S6_005_DESC</v>
+      </c>
+      <c r="F118" s="36">
+        <v>6</v>
+      </c>
+      <c r="G118" s="36">
+        <v>3</v>
+      </c>
+      <c r="H118" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="I118" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J118" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K118" s="34">
+        <v>0</v>
+      </c>
+      <c r="L118" s="34" t="s">
+        <v>650</v>
+      </c>
+      <c r="M118" s="34" t="s">
+        <v>672</v>
+      </c>
+      <c r="N118" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O118" s="34" t="s">
+        <v>673</v>
+      </c>
+      <c r="P118" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q118" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A119" s="36">
+        <v>50117</v>
+      </c>
+      <c r="B119" s="36" t="s">
+        <v>604</v>
+      </c>
+      <c r="C119" s="34" t="s">
+        <v>626</v>
+      </c>
+      <c r="D119" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v>STR_MAP_S6_006</v>
+      </c>
+      <c r="E119" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>STR_MAP_S6_006_DESC</v>
+      </c>
+      <c r="F119" s="36">
+        <v>6</v>
+      </c>
+      <c r="G119" s="36">
+        <v>3</v>
+      </c>
+      <c r="H119" s="36" t="s">
+        <v>453</v>
+      </c>
+      <c r="I119" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J119" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K119" s="34">
+        <v>0</v>
+      </c>
+      <c r="L119" s="34" t="s">
+        <v>651</v>
+      </c>
+      <c r="M119" s="34" t="s">
+        <v>674</v>
+      </c>
+      <c r="N119" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O119" s="34" t="s">
+        <v>675</v>
+      </c>
+      <c r="P119" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q119" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A120" s="36">
+        <v>50118</v>
+      </c>
+      <c r="B120" s="36" t="s">
+        <v>605</v>
+      </c>
+      <c r="C120" s="34" t="s">
+        <v>627</v>
+      </c>
+      <c r="D120" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v>STR_MAP_S6_007</v>
+      </c>
+      <c r="E120" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>STR_MAP_S6_007_DESC</v>
+      </c>
+      <c r="F120" s="36">
+        <v>6</v>
+      </c>
+      <c r="G120" s="36">
+        <v>3</v>
+      </c>
+      <c r="H120" s="36" t="s">
+        <v>451</v>
+      </c>
+      <c r="I120" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J120" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K120" s="34">
+        <v>0</v>
+      </c>
+      <c r="L120" s="34" t="s">
+        <v>652</v>
+      </c>
+      <c r="M120" s="34" t="s">
+        <v>672</v>
+      </c>
+      <c r="N120" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O120" s="34" t="s">
+        <v>673</v>
+      </c>
+      <c r="P120" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q120" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A121" s="36">
+        <v>50119</v>
+      </c>
+      <c r="B121" s="36" t="s">
+        <v>606</v>
+      </c>
+      <c r="C121" s="34" t="s">
+        <v>628</v>
+      </c>
+      <c r="D121" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v>STR_MAP_S6_008</v>
+      </c>
+      <c r="E121" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>STR_MAP_S6_008_DESC</v>
+      </c>
+      <c r="F121" s="36">
+        <v>6</v>
+      </c>
+      <c r="G121" s="36">
+        <v>3</v>
+      </c>
+      <c r="H121" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="I121" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J121" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K121" s="34">
+        <v>0</v>
+      </c>
+      <c r="L121" s="34" t="s">
+        <v>653</v>
+      </c>
+      <c r="M121" s="34" t="s">
+        <v>672</v>
+      </c>
+      <c r="N121" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O121" s="34" t="s">
+        <v>673</v>
+      </c>
+      <c r="P121" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q121" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A122" s="36">
+        <v>50120</v>
+      </c>
+      <c r="B122" s="36" t="s">
+        <v>607</v>
+      </c>
+      <c r="C122" s="34" t="s">
+        <v>629</v>
+      </c>
+      <c r="D122" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v>STR_MAP_S6_009</v>
+      </c>
+      <c r="E122" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>STR_MAP_S6_009_DESC</v>
+      </c>
+      <c r="F122" s="36">
+        <v>6</v>
+      </c>
+      <c r="G122" s="36">
+        <v>3</v>
+      </c>
+      <c r="H122" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="I122" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J122" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K122" s="34">
+        <v>0</v>
+      </c>
+      <c r="L122" s="34" t="s">
+        <v>654</v>
+      </c>
+      <c r="M122" s="34" t="s">
+        <v>676</v>
+      </c>
+      <c r="N122" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O122" s="34" t="s">
+        <v>677</v>
+      </c>
+      <c r="P122" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q122" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A123" s="36">
+        <v>50121</v>
+      </c>
+      <c r="B123" s="36" t="s">
+        <v>608</v>
+      </c>
+      <c r="C123" s="34" t="s">
+        <v>630</v>
+      </c>
+      <c r="D123" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v>STR_MAP_S6_010</v>
+      </c>
+      <c r="E123" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>STR_MAP_S6_010_DESC</v>
+      </c>
+      <c r="F123" s="36">
+        <v>6</v>
+      </c>
+      <c r="G123" s="36">
+        <v>3</v>
+      </c>
+      <c r="H123" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="I123" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J123" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K123" s="34">
+        <v>0</v>
+      </c>
+      <c r="L123" s="34" t="s">
+        <v>655</v>
+      </c>
+      <c r="M123" s="34" t="s">
+        <v>672</v>
+      </c>
+      <c r="N123" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O123" s="34" t="s">
+        <v>673</v>
+      </c>
+      <c r="P123" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q123" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A124" s="36">
+        <v>50122</v>
+      </c>
+      <c r="B124" s="36" t="s">
+        <v>609</v>
+      </c>
+      <c r="C124" s="34" t="s">
+        <v>631</v>
+      </c>
+      <c r="D124" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v>STR_MAP_S6_011</v>
+      </c>
+      <c r="E124" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>STR_MAP_S6_011_DESC</v>
+      </c>
+      <c r="F124" s="36">
+        <v>6</v>
+      </c>
+      <c r="G124" s="36">
+        <v>3</v>
+      </c>
+      <c r="H124" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="I124" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J124" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K124" s="34">
+        <v>0</v>
+      </c>
+      <c r="L124" s="34" t="s">
+        <v>656</v>
+      </c>
+      <c r="M124" s="34" t="s">
+        <v>672</v>
+      </c>
+      <c r="N124" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O124" s="34" t="s">
+        <v>673</v>
+      </c>
+      <c r="P124" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q124" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A125" s="36">
+        <v>50123</v>
+      </c>
+      <c r="B125" s="36" t="s">
+        <v>610</v>
+      </c>
+      <c r="C125" s="34" t="s">
+        <v>632</v>
+      </c>
+      <c r="D125" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v>STR_MAP_S6_012</v>
+      </c>
+      <c r="E125" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>STR_MAP_S6_012_DESC</v>
+      </c>
+      <c r="F125" s="36">
+        <v>6</v>
+      </c>
+      <c r="G125" s="36">
+        <v>3</v>
+      </c>
+      <c r="H125" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="I125" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J125" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K125" s="34">
+        <v>0</v>
+      </c>
+      <c r="L125" s="34" t="s">
+        <v>657</v>
+      </c>
+      <c r="M125" s="34" t="s">
+        <v>678</v>
+      </c>
+      <c r="N125" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O125" s="34" t="s">
+        <v>681</v>
+      </c>
+      <c r="P125" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q125" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A126" s="36">
+        <v>50124</v>
+      </c>
+      <c r="B126" s="36" t="s">
+        <v>611</v>
+      </c>
+      <c r="C126" s="34" t="s">
+        <v>633</v>
+      </c>
+      <c r="D126" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v>STR_MAP_S6_013</v>
+      </c>
+      <c r="E126" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>STR_MAP_S6_013_DESC</v>
+      </c>
+      <c r="F126" s="36">
+        <v>6</v>
+      </c>
+      <c r="G126" s="36">
+        <v>3</v>
+      </c>
+      <c r="H126" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="I126" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J126" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K126" s="34">
+        <v>0</v>
+      </c>
+      <c r="L126" s="34" t="s">
+        <v>658</v>
+      </c>
+      <c r="M126" s="34" t="s">
+        <v>680</v>
+      </c>
+      <c r="N126" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O126" s="34" t="s">
+        <v>682</v>
+      </c>
+      <c r="P126" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q126" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A127" s="36">
+        <v>50125</v>
+      </c>
+      <c r="B127" s="36" t="s">
+        <v>612</v>
+      </c>
+      <c r="C127" s="34" t="s">
+        <v>634</v>
+      </c>
+      <c r="D127" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v>STR_MAP_S6_014</v>
+      </c>
+      <c r="E127" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>STR_MAP_S6_014_DESC</v>
+      </c>
+      <c r="F127" s="36">
+        <v>6</v>
+      </c>
+      <c r="G127" s="36">
+        <v>3</v>
+      </c>
+      <c r="H127" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="I127" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J127" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K127" s="34">
+        <v>0</v>
+      </c>
+      <c r="L127" s="34" t="s">
+        <v>659</v>
+      </c>
+      <c r="M127" s="34" t="s">
+        <v>679</v>
+      </c>
+      <c r="N127" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O127" s="34" t="s">
+        <v>683</v>
+      </c>
+      <c r="P127" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q127" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A128" s="36">
+        <v>50126</v>
+      </c>
+      <c r="B128" s="36" t="s">
+        <v>613</v>
+      </c>
+      <c r="C128" s="34" t="s">
+        <v>635</v>
+      </c>
+      <c r="D128" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v>STR_MAP_S6_015</v>
+      </c>
+      <c r="E128" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>STR_MAP_S6_015_DESC</v>
+      </c>
+      <c r="F128" s="36">
+        <v>6</v>
+      </c>
+      <c r="G128" s="36">
+        <v>3</v>
+      </c>
+      <c r="H128" s="36" t="s">
+        <v>451</v>
+      </c>
+      <c r="I128" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J128" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K128" s="34">
+        <v>0</v>
+      </c>
+      <c r="L128" s="34" t="s">
+        <v>660</v>
+      </c>
+      <c r="M128" s="34" t="s">
+        <v>672</v>
+      </c>
+      <c r="N128" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O128" s="34" t="s">
+        <v>673</v>
+      </c>
+      <c r="P128" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q128" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A129" s="36">
+        <v>50127</v>
+      </c>
+      <c r="B129" s="36" t="s">
+        <v>614</v>
+      </c>
+      <c r="C129" s="34" t="s">
+        <v>636</v>
+      </c>
+      <c r="D129" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v>STR_MAP_S6_016</v>
+      </c>
+      <c r="E129" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>STR_MAP_S6_016_DESC</v>
+      </c>
+      <c r="F129" s="36">
+        <v>6</v>
+      </c>
+      <c r="G129" s="36">
+        <v>3</v>
+      </c>
+      <c r="H129" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="I129" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J129" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K129" s="34">
+        <v>0</v>
+      </c>
+      <c r="L129" s="34" t="s">
+        <v>661</v>
+      </c>
+      <c r="M129" s="34" t="s">
+        <v>672</v>
+      </c>
+      <c r="N129" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O129" s="34" t="s">
+        <v>673</v>
+      </c>
+      <c r="P129" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q129" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A130" s="36">
+        <v>50128</v>
+      </c>
+      <c r="B130" s="36" t="s">
+        <v>494</v>
+      </c>
+      <c r="C130" s="34" t="s">
+        <v>637</v>
+      </c>
+      <c r="D130" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v>STR_MAP_S6_017</v>
+      </c>
+      <c r="E130" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>STR_MAP_S6_017_DESC</v>
+      </c>
+      <c r="F130" s="36">
+        <v>6</v>
+      </c>
+      <c r="G130" s="36">
+        <v>3</v>
+      </c>
+      <c r="H130" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="I130" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J130" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K130" s="34">
+        <v>0</v>
+      </c>
+      <c r="L130" s="34" t="s">
+        <v>662</v>
+      </c>
+      <c r="M130" s="34" t="s">
+        <v>684</v>
+      </c>
+      <c r="N130" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O130" s="34" t="s">
+        <v>685</v>
+      </c>
+      <c r="P130" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q130" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A131" s="36">
+        <v>50129</v>
+      </c>
+      <c r="B131" s="36" t="s">
+        <v>495</v>
+      </c>
+      <c r="C131" s="34" t="s">
+        <v>638</v>
+      </c>
+      <c r="D131" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v>STR_MAP_S6_018</v>
+      </c>
+      <c r="E131" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>STR_MAP_S6_018_DESC</v>
+      </c>
+      <c r="F131" s="36">
+        <v>6</v>
+      </c>
+      <c r="G131" s="36">
+        <v>3</v>
+      </c>
+      <c r="H131" s="36" t="s">
+        <v>179</v>
+      </c>
+      <c r="I131" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J131" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K131" s="34">
+        <v>0</v>
+      </c>
+      <c r="L131" s="34" t="s">
+        <v>663</v>
+      </c>
+      <c r="M131" s="34" t="s">
+        <v>686</v>
+      </c>
+      <c r="N131" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O131" s="34" t="s">
+        <v>687</v>
+      </c>
+      <c r="P131" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q131" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A132" s="36">
+        <v>50130</v>
+      </c>
+      <c r="B132" s="36" t="s">
+        <v>615</v>
+      </c>
+      <c r="C132" s="34" t="s">
+        <v>639</v>
+      </c>
+      <c r="D132" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v>STR_MAP_S6_019</v>
+      </c>
+      <c r="E132" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>STR_MAP_S6_019_DESC</v>
+      </c>
+      <c r="F132" s="36">
+        <v>6</v>
+      </c>
+      <c r="G132" s="36">
+        <v>3</v>
+      </c>
+      <c r="H132" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="I132" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J132" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K132" s="34">
+        <v>0</v>
+      </c>
+      <c r="L132" s="34" t="s">
+        <v>564</v>
+      </c>
+      <c r="M132" s="34" t="s">
+        <v>672</v>
+      </c>
+      <c r="N132" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O132" s="34" t="s">
+        <v>673</v>
+      </c>
+      <c r="P132" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q132" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A133" s="36">
+        <v>50131</v>
+      </c>
+      <c r="B133" s="36" t="s">
+        <v>616</v>
+      </c>
+      <c r="C133" s="34" t="s">
+        <v>640</v>
+      </c>
+      <c r="D133" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v>STR_MAP_S6_020</v>
+      </c>
+      <c r="E133" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>STR_MAP_S6_020_DESC</v>
+      </c>
+      <c r="F133" s="36">
+        <v>6</v>
+      </c>
+      <c r="G133" s="36">
+        <v>3</v>
+      </c>
+      <c r="H133" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="I133" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J133" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K133" s="34">
+        <v>0</v>
+      </c>
+      <c r="L133" s="34" t="s">
+        <v>565</v>
+      </c>
+      <c r="M133" s="34" t="s">
+        <v>678</v>
+      </c>
+      <c r="N133" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O133" s="34" t="s">
+        <v>681</v>
+      </c>
+      <c r="P133" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q133" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A134" s="36">
+        <v>50132</v>
+      </c>
+      <c r="B134" s="36" t="s">
+        <v>617</v>
+      </c>
+      <c r="C134" s="34" t="s">
+        <v>641</v>
+      </c>
+      <c r="D134" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v>STR_MAP_S6_021</v>
+      </c>
+      <c r="E134" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>STR_MAP_S6_021_DESC</v>
+      </c>
+      <c r="F134" s="36">
+        <v>6</v>
+      </c>
+      <c r="G134" s="36">
+        <v>3</v>
+      </c>
+      <c r="H134" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="I134" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J134" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K134" s="34">
+        <v>0</v>
+      </c>
+      <c r="L134" s="34" t="s">
+        <v>566</v>
+      </c>
+      <c r="M134" s="34" t="s">
+        <v>680</v>
+      </c>
+      <c r="N134" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O134" s="34" t="s">
+        <v>682</v>
+      </c>
+      <c r="P134" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q134" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A135" s="36">
+        <v>50133</v>
+      </c>
+      <c r="B135" s="36" t="s">
+        <v>618</v>
+      </c>
+      <c r="C135" s="34" t="s">
+        <v>642</v>
+      </c>
+      <c r="D135" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v>STR_MAP_S6_022</v>
+      </c>
+      <c r="E135" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>STR_MAP_S6_022_DESC</v>
+      </c>
+      <c r="F135" s="36">
+        <v>6</v>
+      </c>
+      <c r="G135" s="36">
+        <v>3</v>
+      </c>
+      <c r="H135" s="36" t="s">
+        <v>453</v>
+      </c>
+      <c r="I135" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J135" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K135" s="34">
+        <v>0</v>
+      </c>
+      <c r="L135" s="34" t="s">
+        <v>567</v>
+      </c>
+      <c r="M135" s="34" t="s">
+        <v>679</v>
+      </c>
+      <c r="N135" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O135" s="34" t="s">
+        <v>683</v>
+      </c>
+      <c r="P135" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q135" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A136" s="36">
+        <v>50134</v>
+      </c>
+      <c r="B136" s="36" t="s">
+        <v>607</v>
+      </c>
+      <c r="C136" s="34" t="s">
+        <v>643</v>
+      </c>
+      <c r="D136" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v>STR_MAP_S6_023</v>
+      </c>
+      <c r="E136" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>STR_MAP_S6_023_DESC</v>
+      </c>
+      <c r="F136" s="36">
+        <v>6</v>
+      </c>
+      <c r="G136" s="36">
+        <v>3</v>
+      </c>
+      <c r="H136" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="I136" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J136" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K136" s="34">
+        <v>0</v>
+      </c>
+      <c r="L136" s="34" t="s">
+        <v>664</v>
+      </c>
+      <c r="M136" s="34" t="s">
+        <v>672</v>
+      </c>
+      <c r="N136" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O136" s="34" t="s">
+        <v>673</v>
+      </c>
+      <c r="P136" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q136" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A137" s="36">
+        <v>50135</v>
+      </c>
+      <c r="B137" s="36" t="s">
+        <v>619</v>
+      </c>
+      <c r="C137" s="34" t="s">
+        <v>644</v>
+      </c>
+      <c r="D137" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v>STR_MAP_S6_024</v>
+      </c>
+      <c r="E137" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>STR_MAP_S6_024_DESC</v>
+      </c>
+      <c r="F137" s="36">
+        <v>6</v>
+      </c>
+      <c r="G137" s="36">
+        <v>3</v>
+      </c>
+      <c r="H137" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="I137" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J137" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K137" s="34">
+        <v>0</v>
+      </c>
+      <c r="L137" s="34" t="s">
+        <v>665</v>
+      </c>
+      <c r="M137" s="34" t="s">
+        <v>680</v>
+      </c>
+      <c r="N137" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O137" s="34" t="s">
+        <v>682</v>
+      </c>
+      <c r="P137" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q137" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A138" s="36">
+        <v>50136</v>
+      </c>
+      <c r="B138" s="36" t="s">
+        <v>620</v>
+      </c>
+      <c r="C138" s="34" t="s">
+        <v>645</v>
+      </c>
+      <c r="D138" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v>STR_MAP_S6_025</v>
+      </c>
+      <c r="E138" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>STR_MAP_S6_025_DESC</v>
+      </c>
+      <c r="F138" s="36">
+        <v>6</v>
+      </c>
+      <c r="G138" s="36">
+        <v>3</v>
+      </c>
+      <c r="H138" s="36" t="s">
+        <v>433</v>
+      </c>
+      <c r="I138" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J138" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K138" s="34">
+        <v>0</v>
+      </c>
+      <c r="L138" s="34" t="s">
+        <v>666</v>
+      </c>
+      <c r="M138" s="34" t="s">
+        <v>688</v>
+      </c>
+      <c r="N138" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O138" s="34" t="s">
+        <v>689</v>
+      </c>
+      <c r="P138" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q138" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A139" s="36">
+        <v>59000</v>
+      </c>
+      <c r="B139" s="36" t="s">
+        <v>667</v>
+      </c>
+      <c r="C139" s="34" t="s">
+        <v>668</v>
+      </c>
+      <c r="D139" s="34" t="str">
+        <f t="shared" ref="D139" si="44">"STR_"&amp;UPPER(C139)</f>
+        <v>STR_MAP_S0_001</v>
+      </c>
+      <c r="E139" s="34" t="str">
+        <f t="shared" ref="E139" si="45">D139&amp;"_DESC"</f>
+        <v>STR_MAP_S0_001_DESC</v>
+      </c>
+      <c r="F139" s="36">
+        <v>99</v>
+      </c>
+      <c r="G139" s="36">
+        <v>99</v>
+      </c>
+      <c r="H139" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="I139" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J139" s="34">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K139" s="34">
+        <v>0</v>
+      </c>
+      <c r="L139" s="34" t="s">
+        <v>669</v>
+      </c>
+      <c r="M139" s="34" t="s">
+        <v>690</v>
+      </c>
+      <c r="N139" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="O139" s="34" t="s">
+        <v>691</v>
+      </c>
+      <c r="P139" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q139" s="34">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:T2"/>
@@ -11194,7 +15092,7 @@
           <x14:formula2>
             <xm:f>Definition!G70</xm:f>
           </x14:formula2>
-          <xm:sqref>I63:I81</xm:sqref>
+          <xm:sqref>I63:I139</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>

--- a/30_table/01_테스트버전/Table_Data_Map.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Map.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="692">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="692">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -11899,6 +11899,9 @@
       <c r="Q82" s="34">
         <v>0</v>
       </c>
+      <c r="R82" s="36" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A83" s="36">
@@ -11954,6 +11957,9 @@
       <c r="Q83" s="34">
         <v>0</v>
       </c>
+      <c r="R83" s="36" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="84" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A84" s="36">
@@ -12009,6 +12015,15 @@
       <c r="Q84" s="34">
         <v>0</v>
       </c>
+      <c r="R84" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="U84" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V84" s="36" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A85" s="36">
@@ -12064,6 +12079,9 @@
       <c r="Q85" s="34">
         <v>0</v>
       </c>
+      <c r="R85" s="36" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A86" s="36">
@@ -12119,6 +12137,15 @@
       <c r="Q86" s="34">
         <v>0</v>
       </c>
+      <c r="R86" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="U86" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V86" s="36" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="87" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A87" s="36">
@@ -12174,6 +12201,9 @@
       <c r="Q87" s="34">
         <v>0</v>
       </c>
+      <c r="R87" s="36" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="88" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A88" s="36">
@@ -12229,6 +12259,9 @@
       <c r="Q88" s="34">
         <v>0</v>
       </c>
+      <c r="R88" s="36" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="89" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A89" s="36">
@@ -12284,6 +12317,15 @@
       <c r="Q89" s="34">
         <v>0</v>
       </c>
+      <c r="R89" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="U89" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V89" s="36" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="90" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A90" s="36">
@@ -12339,6 +12381,9 @@
       <c r="Q90" s="34">
         <v>0</v>
       </c>
+      <c r="R90" s="36" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A91" s="36">
@@ -12394,6 +12439,15 @@
       <c r="Q91" s="34">
         <v>0</v>
       </c>
+      <c r="R91" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="U91" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V91" s="36" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="92" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A92" s="36">
@@ -12449,6 +12503,15 @@
       <c r="Q92" s="34">
         <v>0</v>
       </c>
+      <c r="R92" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="U92" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V92" s="36" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="93" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A93" s="36">
@@ -12504,6 +12567,15 @@
       <c r="Q93" s="34">
         <v>0</v>
       </c>
+      <c r="R93" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="U93" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V93" s="36" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="94" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A94" s="36">
@@ -12559,6 +12631,9 @@
       <c r="Q94" s="34">
         <v>0</v>
       </c>
+      <c r="R94" s="36" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="95" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A95" s="36">
@@ -12614,6 +12689,15 @@
       <c r="Q95" s="34">
         <v>0</v>
       </c>
+      <c r="R95" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="U95" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V95" s="36" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="96" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A96" s="36">
@@ -12669,8 +12753,11 @@
       <c r="Q96" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R96" s="36" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="97" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A97" s="36">
         <v>50095</v>
       </c>
@@ -12724,8 +12811,17 @@
       <c r="Q97" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R97" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="U97" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V97" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="98" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A98" s="36">
         <v>50096</v>
       </c>
@@ -12779,8 +12875,11 @@
       <c r="Q98" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R98" s="36" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="99" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A99" s="36">
         <v>50097</v>
       </c>
@@ -12834,8 +12933,11 @@
       <c r="Q99" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R99" s="36" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="100" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A100" s="36">
         <v>50098</v>
       </c>
@@ -12889,8 +12991,17 @@
       <c r="Q100" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R100" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="U100" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V100" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="101" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A101" s="36">
         <v>50099</v>
       </c>
@@ -12944,8 +13055,11 @@
       <c r="Q101" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R101" s="36" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="102" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A102" s="36">
         <v>50100</v>
       </c>
@@ -12999,8 +13113,11 @@
       <c r="Q102" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R102" s="36" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="103" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A103" s="36">
         <v>50101</v>
       </c>
@@ -13054,8 +13171,11 @@
       <c r="Q103" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R103" s="36" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="104" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A104" s="36">
         <v>50102</v>
       </c>
@@ -13109,8 +13229,11 @@
       <c r="Q104" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R104" s="36" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="105" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A105" s="36">
         <v>50103</v>
       </c>
@@ -13164,8 +13287,17 @@
       <c r="Q105" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R105" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="U105" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V105" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="106" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A106" s="36">
         <v>50104</v>
       </c>
@@ -13219,8 +13351,11 @@
       <c r="Q106" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R106" s="36" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="107" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A107" s="36">
         <v>50105</v>
       </c>
@@ -13274,8 +13409,17 @@
       <c r="Q107" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R107" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="U107" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V107" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="108" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A108" s="36">
         <v>50106</v>
       </c>
@@ -13329,8 +13473,17 @@
       <c r="Q108" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R108" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="U108" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="V108" s="36" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="109" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A109" s="36">
         <v>50107</v>
       </c>
@@ -13384,8 +13537,11 @@
       <c r="Q109" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R109" s="36" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="110" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A110" s="36">
         <v>50108</v>
       </c>
@@ -13439,8 +13595,11 @@
       <c r="Q110" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R110" s="36" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="111" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A111" s="36">
         <v>50109</v>
       </c>
@@ -13494,8 +13653,17 @@
       <c r="Q111" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R111" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="U111" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="V111" s="34" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="112" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A112" s="36">
         <v>50110</v>
       </c>
@@ -13549,8 +13717,17 @@
       <c r="Q112" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R112" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="U112" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="V112" s="34" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="113" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A113" s="36">
         <v>50111</v>
       </c>
@@ -13604,8 +13781,17 @@
       <c r="Q113" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R113" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="U113" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="V113" s="34" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="114" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A114" s="36">
         <v>50112</v>
       </c>
@@ -13659,8 +13845,17 @@
       <c r="Q114" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R114" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="U114" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="V114" s="34" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="115" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A115" s="36">
         <v>50113</v>
       </c>
@@ -13714,8 +13909,11 @@
       <c r="Q115" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R115" s="36" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="116" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A116" s="36">
         <v>50114</v>
       </c>
@@ -13769,8 +13967,17 @@
       <c r="Q116" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R116" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="U116" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="V116" s="34" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="117" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A117" s="36">
         <v>50115</v>
       </c>
@@ -13824,8 +14031,11 @@
       <c r="Q117" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R117" s="36" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="118" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A118" s="36">
         <v>50116</v>
       </c>
@@ -13879,8 +14089,11 @@
       <c r="Q118" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R118" s="36" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="119" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A119" s="36">
         <v>50117</v>
       </c>
@@ -13934,8 +14147,17 @@
       <c r="Q119" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R119" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="U119" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="V119" s="34" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="120" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A120" s="36">
         <v>50118</v>
       </c>
@@ -13989,8 +14211,11 @@
       <c r="Q120" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R120" s="36" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="121" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A121" s="36">
         <v>50119</v>
       </c>
@@ -14044,8 +14269,11 @@
       <c r="Q121" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R121" s="36" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="122" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A122" s="36">
         <v>50120</v>
       </c>
@@ -14099,8 +14327,17 @@
       <c r="Q122" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R122" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="U122" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="V122" s="34" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="123" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A123" s="36">
         <v>50121</v>
       </c>
@@ -14154,8 +14391,11 @@
       <c r="Q123" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R123" s="36" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="124" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A124" s="36">
         <v>50122</v>
       </c>
@@ -14209,8 +14449,11 @@
       <c r="Q124" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R124" s="36" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="125" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A125" s="36">
         <v>50123</v>
       </c>
@@ -14264,8 +14507,17 @@
       <c r="Q125" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R125" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="U125" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="V125" s="34" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="126" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A126" s="36">
         <v>50124</v>
       </c>
@@ -14319,8 +14571,17 @@
       <c r="Q126" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R126" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="U126" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="V126" s="34" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="127" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A127" s="36">
         <v>50125</v>
       </c>
@@ -14374,8 +14635,17 @@
       <c r="Q127" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R127" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="U127" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="V127" s="34" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="128" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A128" s="36">
         <v>50126</v>
       </c>
@@ -14429,8 +14699,11 @@
       <c r="Q128" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R128" s="36" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="129" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A129" s="36">
         <v>50127</v>
       </c>
@@ -14484,8 +14757,11 @@
       <c r="Q129" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R129" s="36" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="130" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A130" s="36">
         <v>50128</v>
       </c>
@@ -14539,8 +14815,17 @@
       <c r="Q130" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R130" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="U130" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="V130" s="34" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="131" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A131" s="36">
         <v>50129</v>
       </c>
@@ -14594,8 +14879,11 @@
       <c r="Q131" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R131" s="36" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="132" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A132" s="36">
         <v>50130</v>
       </c>
@@ -14649,8 +14937,11 @@
       <c r="Q132" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R132" s="36" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="133" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A133" s="36">
         <v>50131</v>
       </c>
@@ -14704,8 +14995,17 @@
       <c r="Q133" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R133" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="U133" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="V133" s="34" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="134" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A134" s="36">
         <v>50132</v>
       </c>
@@ -14759,8 +15059,17 @@
       <c r="Q134" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R134" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="U134" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="V134" s="34" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="135" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A135" s="36">
         <v>50133</v>
       </c>
@@ -14814,8 +15123,17 @@
       <c r="Q135" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R135" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="U135" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="V135" s="34" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="136" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A136" s="36">
         <v>50134</v>
       </c>
@@ -14869,8 +15187,11 @@
       <c r="Q136" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R136" s="36" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="137" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A137" s="36">
         <v>50135</v>
       </c>
@@ -14924,8 +15245,17 @@
       <c r="Q137" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R137" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="U137" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="V137" s="34" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="138" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A138" s="36">
         <v>50136</v>
       </c>
@@ -14979,8 +15309,17 @@
       <c r="Q138" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R138" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="U138" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="V138" s="34" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="139" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A139" s="36">
         <v>59000</v>
       </c>
@@ -15033,6 +15372,9 @@
       </c>
       <c r="Q139" s="34">
         <v>0</v>
+      </c>
+      <c r="R139" s="36" t="s">
+        <v>230</v>
       </c>
     </row>
   </sheetData>
